--- a/vitestro_phlebotomy_safety/outputs/019f8cc8-9802-7b01-8b3a-7fe5ef10eaa5/vitestro_wearable_device_scorecard_2026-07-23.xlsx
+++ b/vitestro_phlebotomy_safety/outputs/019f8cc8-9802-7b01-8b3a-7fe5ef10eaa5/vitestro_wearable_device_scorecard_2026-07-23.xlsx
@@ -2,12 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="1" r:id="R153d4fe0c7994e8b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="2" r:id="Re82a39bf732949c3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Access" sheetId="3" r:id="R6ef7a762fd0e4b58"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evaluation Protocol" sheetId="4" r:id="Ref1b848a61794166"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codebook" sheetId="5" r:id="R90607c641a794a1a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Registry" sheetId="6" r:id="Rddc1b832d2d94bf9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="1" r:id="R8fcf294d4708480d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Matrix" sheetId="2" r:id="Raa4dfec9730e4f0a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Access" sheetId="3" r:id="Rfe1fd4b305304891"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Signal Evidence" sheetId="4" r:id="R7be968c0962a4c56"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evaluation Protocol" sheetId="5" r:id="Rb64d1652fbb8448f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codebook" sheetId="6" r:id="R5755f42a137d4a3e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Registry" sheetId="7" r:id="Rf2ebff17717f478d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -423,7 +424,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="217">
+  <x:cellXfs count="242">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -506,6 +507,16 @@
     <x:xf numFmtId="202" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
@@ -574,39 +585,84 @@
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1023,7 +1079,7 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>'Executive Summary'!$A$26:$A$40</c:f>
+              <c:f>'Executive Summary'!$A$29:$A$46</c:f>
               <c:strCache>
                 <c:ptCount val="0"/>
               </c:strCache>
@@ -1031,7 +1087,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Executive Summary'!$B$26:$B$40</c:f>
+              <c:f>'Executive Summary'!$B$29:$B$46</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="0"/>
@@ -1122,13 +1178,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>43</xdr:row>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -1142,7 +1198,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ref3a3833e9be449e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R4c389e987483485d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1152,7 +1208,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="DeviceFeatureMatrix" displayName="DeviceFeatureMatrix" ref="A1:AD16" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="DeviceFeatureMatrix" displayName="DeviceFeatureMatrix" ref="A1:AD19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="30">
     <x:tableColumn id="1" name="evaluation_order"/>
     <x:tableColumn id="2" name="device"/>
@@ -1190,7 +1246,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DataAccessTable" displayName="DataAccessTable" ref="A5:G20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DataAccessTable" displayName="DataAccessTable" ref="A5:G23" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="Device"/>
     <x:tableColumn id="2" name="Programmatic live path"/>
@@ -1205,7 +1261,21 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="ProtocolGateTable" displayName="ProtocolGateTable" ref="A5:F14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="SignalEvidenceTable" displayName="SignalEvidenceTable" ref="A5:F17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="6">
+    <x:tableColumn id="1" name="modality"/>
+    <x:tableColumn id="2" name="deployment_class"/>
+    <x:tableColumn id="3" name="vitestro_role"/>
+    <x:tableColumn id="4" name="evidence_summary"/>
+    <x:tableColumn id="5" name="main_failure_mode"/>
+    <x:tableColumn id="6" name="source_ids"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="ProtocolGateTable" displayName="ProtocolGateTable" ref="A5:F15" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="6">
     <x:tableColumn id="1" name="Gate"/>
     <x:tableColumn id="2" name="Objective"/>
@@ -1218,8 +1288,8 @@
 </x:table>
 </file>
 
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EvidenceRegistryTable" displayName="EvidenceRegistryTable" ref="A1:J74" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="EvidenceRegistryTable" displayName="EvidenceRegistryTable" ref="A1:J96" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="source_id"/>
     <x:tableColumn id="2" name="category"/>
@@ -1446,208 +1516,208 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="86" t="str">
+      <x:c r="A1" s="111" t="str">
         <x:v>Vitestro Wearable Device Evaluation</x:v>
       </x:c>
-      <x:c r="B1" s="86"/>
-      <x:c r="C1" s="86"/>
-      <x:c r="D1" s="86"/>
-      <x:c r="E1" s="86"/>
-      <x:c r="F1" s="86"/>
-      <x:c r="G1" s="86"/>
-      <x:c r="H1" s="86"/>
-      <x:c r="I1" s="86"/>
-      <x:c r="J1" s="86"/>
-      <x:c r="K1" s="86"/>
-      <x:c r="L1" s="86"/>
+      <x:c r="B1" s="111"/>
+      <x:c r="C1" s="111"/>
+      <x:c r="D1" s="111"/>
+      <x:c r="E1" s="111"/>
+      <x:c r="F1" s="111"/>
+      <x:c r="G1" s="111"/>
+      <x:c r="H1" s="111"/>
+      <x:c r="I1" s="111"/>
+      <x:c r="J1" s="111"/>
+      <x:c r="K1" s="111"/>
+      <x:c r="L1" s="111"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="86"/>
-      <x:c r="B2" s="86"/>
-      <x:c r="C2" s="86"/>
-      <x:c r="D2" s="86"/>
-      <x:c r="E2" s="86"/>
-      <x:c r="F2" s="86"/>
-      <x:c r="G2" s="86"/>
-      <x:c r="H2" s="86"/>
-      <x:c r="I2" s="86"/>
-      <x:c r="J2" s="86"/>
-      <x:c r="K2" s="86"/>
-      <x:c r="L2" s="86"/>
+      <x:c r="A2" s="111"/>
+      <x:c r="B2" s="111"/>
+      <x:c r="C2" s="111"/>
+      <x:c r="D2" s="111"/>
+      <x:c r="E2" s="111"/>
+      <x:c r="F2" s="111"/>
+      <x:c r="G2" s="111"/>
+      <x:c r="H2" s="111"/>
+      <x:c r="I2" s="111"/>
+      <x:c r="J2" s="111"/>
+      <x:c r="K2" s="111"/>
+      <x:c r="L2" s="111"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="88" t="str">
+      <x:c r="A3" s="113" t="str">
         <x:v>Mayo–Vitestro presyncope sensing | US-first device pool | Evidence reviewed 2026-07-23</x:v>
       </x:c>
-      <x:c r="B3" s="88"/>
-      <x:c r="C3" s="88"/>
-      <x:c r="D3" s="88"/>
-      <x:c r="E3" s="88"/>
-      <x:c r="F3" s="88"/>
-      <x:c r="G3" s="88"/>
-      <x:c r="H3" s="88"/>
-      <x:c r="I3" s="88"/>
-      <x:c r="J3" s="88"/>
-      <x:c r="K3" s="88"/>
-      <x:c r="L3" s="88"/>
+      <x:c r="B3" s="113"/>
+      <x:c r="C3" s="113"/>
+      <x:c r="D3" s="113"/>
+      <x:c r="E3" s="113"/>
+      <x:c r="F3" s="113"/>
+      <x:c r="G3" s="113"/>
+      <x:c r="H3" s="113"/>
+      <x:c r="I3" s="113"/>
+      <x:c r="J3" s="113"/>
+      <x:c r="K3" s="113"/>
+      <x:c r="L3" s="113"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="92" t="str">
+      <x:c r="A5" s="117" t="str">
         <x:v>Devices assessed</x:v>
       </x:c>
-      <x:c r="B5" s="92"/>
-      <x:c r="C5" s="92"/>
-      <x:c r="D5" s="92" t="str">
+      <x:c r="B5" s="117"/>
+      <x:c r="C5" s="117"/>
+      <x:c r="D5" s="117" t="str">
         <x:v>US / US-HQ products</x:v>
       </x:c>
-      <x:c r="E5" s="92"/>
-      <x:c r="F5" s="92"/>
-      <x:c r="G5" s="92" t="str">
-        <x:v>US bench-now devices</x:v>
-      </x:c>
-      <x:c r="H5" s="92"/>
-      <x:c r="I5" s="92"/>
-      <x:c r="J5" s="92" t="str">
+      <x:c r="E5" s="117"/>
+      <x:c r="F5" s="117"/>
+      <x:c r="G5" s="117" t="str">
+        <x:v>US wrist bench-now</x:v>
+      </x:c>
+      <x:c r="H5" s="117"/>
+      <x:c r="I5" s="117"/>
+      <x:c r="J5" s="117" t="str">
         <x:v>Clinical-ready today</x:v>
       </x:c>
-      <x:c r="K5" s="92"/>
-      <x:c r="L5" s="92"/>
+      <x:c r="K5" s="117"/>
+      <x:c r="L5" s="117"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="112" t="str">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="B6" s="113"/>
-      <x:c r="C6" s="114"/>
-      <x:c r="D6" s="112" t="str">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="E6" s="113"/>
-      <x:c r="F6" s="114"/>
-      <x:c r="G6" s="112" t="str">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="H6" s="113"/>
-      <x:c r="I6" s="114"/>
-      <x:c r="J6" s="112" t="str">
+      <x:c r="A6" s="137" t="str">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B6" s="138"/>
+      <x:c r="C6" s="139"/>
+      <x:c r="D6" s="137" t="str">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E6" s="138"/>
+      <x:c r="F6" s="139"/>
+      <x:c r="G6" s="137" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H6" s="138"/>
+      <x:c r="I6" s="139"/>
+      <x:c r="J6" s="137" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K6" s="113"/>
-      <x:c r="L6" s="114"/>
+      <x:c r="K6" s="138"/>
+      <x:c r="L6" s="139"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="115"/>
-      <x:c r="B7" s="116"/>
-      <x:c r="C7" s="117"/>
-      <x:c r="D7" s="115"/>
-      <x:c r="E7" s="116"/>
-      <x:c r="F7" s="117"/>
-      <x:c r="G7" s="115"/>
-      <x:c r="H7" s="116"/>
-      <x:c r="I7" s="117"/>
-      <x:c r="J7" s="115"/>
-      <x:c r="K7" s="116"/>
-      <x:c r="L7" s="117"/>
+      <x:c r="A7" s="140"/>
+      <x:c r="B7" s="141"/>
+      <x:c r="C7" s="142"/>
+      <x:c r="D7" s="140"/>
+      <x:c r="E7" s="141"/>
+      <x:c r="F7" s="142"/>
+      <x:c r="G7" s="140"/>
+      <x:c r="H7" s="141"/>
+      <x:c r="I7" s="142"/>
+      <x:c r="J7" s="140"/>
+      <x:c r="K7" s="141"/>
+      <x:c r="L7" s="142"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="118"/>
-      <x:c r="B8" s="119"/>
-      <x:c r="C8" s="120"/>
-      <x:c r="D8" s="118"/>
-      <x:c r="E8" s="119"/>
-      <x:c r="F8" s="120"/>
-      <x:c r="G8" s="118"/>
-      <x:c r="H8" s="119"/>
-      <x:c r="I8" s="120"/>
-      <x:c r="J8" s="118"/>
-      <x:c r="K8" s="119"/>
-      <x:c r="L8" s="120"/>
+      <x:c r="A8" s="143"/>
+      <x:c r="B8" s="144"/>
+      <x:c r="C8" s="145"/>
+      <x:c r="D8" s="143"/>
+      <x:c r="E8" s="144"/>
+      <x:c r="F8" s="145"/>
+      <x:c r="G8" s="143"/>
+      <x:c r="H8" s="144"/>
+      <x:c r="I8" s="145"/>
+      <x:c r="J8" s="143"/>
+      <x:c r="K8" s="144"/>
+      <x:c r="L8" s="145"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="121" t="str">
+      <x:c r="A10" s="146" t="str">
         <x:v>Decision</x:v>
       </x:c>
-      <x:c r="B10" s="121"/>
-      <x:c r="C10" s="121"/>
-      <x:c r="D10" s="121"/>
-      <x:c r="E10" s="121"/>
-      <x:c r="F10" s="121"/>
-      <x:c r="G10" s="121"/>
-      <x:c r="H10" s="121"/>
-      <x:c r="I10" s="121"/>
-      <x:c r="J10" s="121"/>
-      <x:c r="K10" s="121"/>
-      <x:c r="L10" s="121"/>
+      <x:c r="B10" s="146"/>
+      <x:c r="C10" s="146"/>
+      <x:c r="D10" s="146"/>
+      <x:c r="E10" s="146"/>
+      <x:c r="F10" s="146"/>
+      <x:c r="G10" s="146"/>
+      <x:c r="H10" s="146"/>
+      <x:c r="I10" s="146"/>
+      <x:c r="J10" s="146"/>
+      <x:c r="K10" s="146"/>
+      <x:c r="L10" s="146"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="138" t="str">
-        <x:v>Use a US-first bench set: Apple Watch Series 11, ActiGraph LEAP, Biostrap Kairos, and VitalConnect VitalPatch RTM. Add one Samsung Galaxy Watch8 to reproduce the strongest direct smartwatch-VVS paper and add Empatica EmbracePlus only if raw EDA remains in scope. Treat Corsano as BP diligence, not truth. No reviewed device is authorized for patient alerts or robot control.</x:v>
-      </x:c>
-      <x:c r="B11" s="139"/>
-      <x:c r="C11" s="139"/>
-      <x:c r="D11" s="139"/>
-      <x:c r="E11" s="139"/>
-      <x:c r="F11" s="139"/>
-      <x:c r="G11" s="139"/>
-      <x:c r="H11" s="139"/>
-      <x:c r="I11" s="139"/>
-      <x:c r="J11" s="139"/>
-      <x:c r="K11" s="139"/>
-      <x:c r="L11" s="140"/>
+      <x:c r="A11" s="163" t="str">
+        <x:v>Bench Apple Watch Series 11, ActiGraph LEAP, and Biostrap Kairos. Run a payload/contract/workflow bake-off among VitalPatch RTM, Vivalink VV330/VV350, and Sibel ANNE One, then select one US reference platform. Add Galaxy Watch8 as the direct-evidence control and EmbracePlus only if EDA remains in scope. Facial RGB/thermal is optional auxiliary research, not a wearable replacement.</x:v>
+      </x:c>
+      <x:c r="B11" s="164"/>
+      <x:c r="C11" s="164"/>
+      <x:c r="D11" s="164"/>
+      <x:c r="E11" s="164"/>
+      <x:c r="F11" s="164"/>
+      <x:c r="G11" s="164"/>
+      <x:c r="H11" s="164"/>
+      <x:c r="I11" s="164"/>
+      <x:c r="J11" s="164"/>
+      <x:c r="K11" s="164"/>
+      <x:c r="L11" s="165"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="141"/>
-      <x:c r="B12" s="142"/>
-      <x:c r="C12" s="142"/>
-      <x:c r="D12" s="142"/>
-      <x:c r="E12" s="142"/>
-      <x:c r="F12" s="142"/>
-      <x:c r="G12" s="142"/>
-      <x:c r="H12" s="142"/>
-      <x:c r="I12" s="142"/>
-      <x:c r="J12" s="142"/>
-      <x:c r="K12" s="142"/>
-      <x:c r="L12" s="143"/>
+      <x:c r="A12" s="166"/>
+      <x:c r="B12" s="167"/>
+      <x:c r="C12" s="167"/>
+      <x:c r="D12" s="167"/>
+      <x:c r="E12" s="167"/>
+      <x:c r="F12" s="167"/>
+      <x:c r="G12" s="167"/>
+      <x:c r="H12" s="167"/>
+      <x:c r="I12" s="167"/>
+      <x:c r="J12" s="167"/>
+      <x:c r="K12" s="167"/>
+      <x:c r="L12" s="168"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="141"/>
-      <x:c r="B13" s="142"/>
-      <x:c r="C13" s="142"/>
-      <x:c r="D13" s="142"/>
-      <x:c r="E13" s="142"/>
-      <x:c r="F13" s="142"/>
-      <x:c r="G13" s="142"/>
-      <x:c r="H13" s="142"/>
-      <x:c r="I13" s="142"/>
-      <x:c r="J13" s="142"/>
-      <x:c r="K13" s="142"/>
-      <x:c r="L13" s="143"/>
+      <x:c r="A13" s="166"/>
+      <x:c r="B13" s="167"/>
+      <x:c r="C13" s="167"/>
+      <x:c r="D13" s="167"/>
+      <x:c r="E13" s="167"/>
+      <x:c r="F13" s="167"/>
+      <x:c r="G13" s="167"/>
+      <x:c r="H13" s="167"/>
+      <x:c r="I13" s="167"/>
+      <x:c r="J13" s="167"/>
+      <x:c r="K13" s="167"/>
+      <x:c r="L13" s="168"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="144"/>
-      <x:c r="B14" s="145"/>
-      <x:c r="C14" s="145"/>
-      <x:c r="D14" s="145"/>
-      <x:c r="E14" s="145"/>
-      <x:c r="F14" s="145"/>
-      <x:c r="G14" s="145"/>
-      <x:c r="H14" s="145"/>
-      <x:c r="I14" s="145"/>
-      <x:c r="J14" s="145"/>
-      <x:c r="K14" s="145"/>
-      <x:c r="L14" s="146"/>
+      <x:c r="A14" s="169"/>
+      <x:c r="B14" s="170"/>
+      <x:c r="C14" s="170"/>
+      <x:c r="D14" s="170"/>
+      <x:c r="E14" s="170"/>
+      <x:c r="F14" s="170"/>
+      <x:c r="G14" s="170"/>
+      <x:c r="H14" s="170"/>
+      <x:c r="I14" s="170"/>
+      <x:c r="J14" s="170"/>
+      <x:c r="K14" s="170"/>
+      <x:c r="L14" s="171"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="147" t="str">
+      <x:c r="A16" s="172" t="str">
         <x:v>Device</x:v>
       </x:c>
-      <x:c r="B16" s="147" t="str">
+      <x:c r="B16" s="172" t="str">
         <x:v>Role</x:v>
       </x:c>
-      <x:c r="C16" s="147" t="str">
+      <x:c r="C16" s="172" t="str">
         <x:v>Capability score</x:v>
       </x:c>
-      <x:c r="D16" s="147" t="str">
+      <x:c r="D16" s="172" t="str">
         <x:v>Action</x:v>
       </x:c>
       <x:c r="F16" s="5" t="str">
@@ -1661,392 +1731,488 @@
       <x:c r="L16" s="5"/>
     </x:row>
     <x:row r="17" ht="38" customHeight="1">
-      <x:c r="A17" s="175" t="str">
+      <x:c r="A17" s="200" t="str">
         <x:v>Apple Watch Series 11</x:v>
       </x:c>
-      <x:c r="B17" s="176" t="str">
+      <x:c r="B17" s="201" t="str">
         <x:v>Ecosystem baseline</x:v>
       </x:c>
-      <x:c r="C17" s="177" t="n">
+      <x:c r="C17" s="202" t="n">
         <x:f>'Feature Matrix'!AA2</x:f>
         <x:v>44</x:v>
       </x:c>
-      <x:c r="D17" s="178" t="str">
+      <x:c r="D17" s="203" t="str">
         <x:v>Bench now</x:v>
       </x:c>
-      <x:c r="F17" s="201" t="str">
+      <x:c r="F17" s="226" t="str">
         <x:v>Apple provides a strong user experience, live processed HR/motion in a watchOS session, saved ECG voltage, HealthKit, and XML export. It does not expose continuous raw PPG, EDA, or actual blood pressure. Hypertension notifications analyze long-term patterns and cannot represent rapid presyncope hypotension.</x:v>
       </x:c>
-      <x:c r="G17" s="202"/>
-      <x:c r="H17" s="202"/>
-      <x:c r="I17" s="202"/>
-      <x:c r="J17" s="202"/>
-      <x:c r="K17" s="202"/>
-      <x:c r="L17" s="203"/>
+      <x:c r="G17" s="227"/>
+      <x:c r="H17" s="227"/>
+      <x:c r="I17" s="227"/>
+      <x:c r="J17" s="227"/>
+      <x:c r="K17" s="227"/>
+      <x:c r="L17" s="228"/>
     </x:row>
     <x:row r="18" ht="38" customHeight="1">
-      <x:c r="A18" s="179" t="str">
+      <x:c r="A18" s="204" t="str">
         <x:v>ActiGraph LEAP</x:v>
       </x:c>
-      <x:c r="B18" s="180" t="str">
+      <x:c r="B18" s="205" t="str">
         <x:v>Primary US wrist research</x:v>
       </x:c>
-      <x:c r="C18" s="181" t="n">
+      <x:c r="C18" s="206" t="n">
         <x:f>'Feature Matrix'!AA3</x:f>
         <x:v>64</x:v>
       </x:c>
-      <x:c r="D18" s="182" t="str">
+      <x:c r="D18" s="207" t="str">
         <x:v>Bench now</x:v>
       </x:c>
-      <x:c r="F18" s="204"/>
-      <x:c r="G18" s="205"/>
-      <x:c r="H18" s="205"/>
-      <x:c r="I18" s="205"/>
-      <x:c r="J18" s="205"/>
-      <x:c r="K18" s="205"/>
-      <x:c r="L18" s="206"/>
+      <x:c r="F18" s="229"/>
+      <x:c r="G18" s="230"/>
+      <x:c r="H18" s="230"/>
+      <x:c r="I18" s="230"/>
+      <x:c r="J18" s="230"/>
+      <x:c r="K18" s="230"/>
+      <x:c r="L18" s="231"/>
     </x:row>
     <x:row r="19" ht="38" customHeight="1">
-      <x:c r="A19" s="179" t="str">
+      <x:c r="A19" s="204" t="str">
         <x:v>Biostrap Kairos</x:v>
       </x:c>
-      <x:c r="B19" s="180" t="str">
+      <x:c r="B19" s="205" t="str">
         <x:v>Independent US raw-PPG/IBI</x:v>
       </x:c>
-      <x:c r="C19" s="181" t="n">
+      <x:c r="C19" s="206" t="n">
         <x:f>'Feature Matrix'!AA4</x:f>
         <x:v>59.5</x:v>
       </x:c>
-      <x:c r="D19" s="182" t="str">
+      <x:c r="D19" s="207" t="str">
         <x:v>Bench now</x:v>
       </x:c>
-      <x:c r="F19" s="204"/>
-      <x:c r="G19" s="205"/>
-      <x:c r="H19" s="205"/>
-      <x:c r="I19" s="205"/>
-      <x:c r="J19" s="205"/>
-      <x:c r="K19" s="205"/>
-      <x:c r="L19" s="206"/>
+      <x:c r="F19" s="229"/>
+      <x:c r="G19" s="230"/>
+      <x:c r="H19" s="230"/>
+      <x:c r="I19" s="230"/>
+      <x:c r="J19" s="230"/>
+      <x:c r="K19" s="230"/>
+      <x:c r="L19" s="231"/>
     </x:row>
     <x:row r="20" ht="38" customHeight="1">
-      <x:c r="A20" s="179" t="str">
+      <x:c r="A20" s="204" t="str">
         <x:v>VitalConnect VitalPatch RTM</x:v>
       </x:c>
-      <x:c r="B20" s="180" t="str">
-        <x:v>Clinical ECG/R-R reference</x:v>
-      </x:c>
-      <x:c r="C20" s="181" t="n">
+      <x:c r="B20" s="205" t="str">
+        <x:v>US reference finalist</x:v>
+      </x:c>
+      <x:c r="C20" s="206" t="n">
         <x:f>'Feature Matrix'!AA5</x:f>
         <x:v>60</x:v>
       </x:c>
-      <x:c r="D20" s="182" t="str">
-        <x:v>Bench now</x:v>
-      </x:c>
-      <x:c r="F20" s="204"/>
-      <x:c r="G20" s="205"/>
-      <x:c r="H20" s="205"/>
-      <x:c r="I20" s="205"/>
-      <x:c r="J20" s="205"/>
-      <x:c r="K20" s="205"/>
-      <x:c r="L20" s="206"/>
+      <x:c r="D20" s="207" t="str">
+        <x:v>Bake-off</x:v>
+      </x:c>
+      <x:c r="F20" s="229"/>
+      <x:c r="G20" s="230"/>
+      <x:c r="H20" s="230"/>
+      <x:c r="I20" s="230"/>
+      <x:c r="J20" s="230"/>
+      <x:c r="K20" s="230"/>
+      <x:c r="L20" s="231"/>
     </x:row>
     <x:row r="21" ht="38" customHeight="1">
-      <x:c r="A21" s="163" t="str">
+      <x:c r="A21" s="204" t="str">
+        <x:v>Vivalink VV330/VV350</x:v>
+      </x:c>
+      <x:c r="B21" s="205" t="str">
+        <x:v>US open-integration finalist</x:v>
+      </x:c>
+      <x:c r="C21" s="206" t="n">
+        <x:f>'Feature Matrix'!AA17</x:f>
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="D21" s="207" t="str">
+        <x:v>Bake-off</x:v>
+      </x:c>
+      <x:c r="F21" s="229"/>
+      <x:c r="G21" s="230"/>
+      <x:c r="H21" s="230"/>
+      <x:c r="I21" s="230"/>
+      <x:c r="J21" s="230"/>
+      <x:c r="K21" s="230"/>
+      <x:c r="L21" s="231"/>
+    </x:row>
+    <x:row r="22" ht="38" customHeight="1">
+      <x:c r="A22" s="204" t="str">
+        <x:v>Sibel ANNE One</x:v>
+      </x:c>
+      <x:c r="B22" s="205" t="str">
+        <x:v>US multimodal finalist</x:v>
+      </x:c>
+      <x:c r="C22" s="206" t="n">
+        <x:f>'Feature Matrix'!AA18</x:f>
+        <x:v>69.5</x:v>
+      </x:c>
+      <x:c r="D22" s="207" t="str">
+        <x:v>Bake-off</x:v>
+      </x:c>
+      <x:c r="F22" s="229"/>
+      <x:c r="G22" s="230"/>
+      <x:c r="H22" s="230"/>
+      <x:c r="I22" s="230"/>
+      <x:c r="J22" s="230"/>
+      <x:c r="K22" s="230"/>
+      <x:c r="L22" s="231"/>
+    </x:row>
+    <x:row r="23" ht="38" customHeight="1">
+      <x:c r="A23" s="188" t="str">
         <x:v>Samsung Galaxy Watch8</x:v>
       </x:c>
-      <x:c r="B21" s="164" t="str">
+      <x:c r="B23" s="189" t="str">
         <x:v>Direct-evidence control</x:v>
       </x:c>
-      <x:c r="C21" s="173" t="n">
+      <x:c r="C23" s="198" t="n">
         <x:f>'Feature Matrix'!AA13</x:f>
         <x:v>75</x:v>
       </x:c>
-      <x:c r="D21" s="165" t="str">
+      <x:c r="D23" s="190" t="str">
         <x:v>Control unit</x:v>
       </x:c>
-      <x:c r="F21" s="204"/>
-      <x:c r="G21" s="205"/>
-      <x:c r="H21" s="205"/>
-      <x:c r="I21" s="205"/>
-      <x:c r="J21" s="205"/>
-      <x:c r="K21" s="205"/>
-      <x:c r="L21" s="206"/>
-    </x:row>
-    <x:row r="22" ht="38" customHeight="1">
-      <x:c r="A22" s="163" t="str">
+      <x:c r="F23" s="229"/>
+      <x:c r="G23" s="230"/>
+      <x:c r="H23" s="230"/>
+      <x:c r="I23" s="230"/>
+      <x:c r="J23" s="230"/>
+      <x:c r="K23" s="230"/>
+      <x:c r="L23" s="231"/>
+    </x:row>
+    <x:row r="24" ht="38" customHeight="1">
+      <x:c r="A24" s="188" t="str">
         <x:v>Empatica EmbracePlus</x:v>
       </x:c>
-      <x:c r="B22" s="164" t="str">
+      <x:c r="B24" s="189" t="str">
         <x:v>Raw EDA/BVP control</x:v>
       </x:c>
-      <x:c r="C22" s="173" t="n">
+      <x:c r="C24" s="198" t="n">
         <x:f>'Feature Matrix'!AA14</x:f>
         <x:v>68.5</x:v>
       </x:c>
-      <x:c r="D22" s="165" t="str">
+      <x:c r="D24" s="190" t="str">
         <x:v>Conditional</x:v>
       </x:c>
-      <x:c r="F22" s="204"/>
-      <x:c r="G22" s="205"/>
-      <x:c r="H22" s="205"/>
-      <x:c r="I22" s="205"/>
-      <x:c r="J22" s="205"/>
-      <x:c r="K22" s="205"/>
-      <x:c r="L22" s="206"/>
-    </x:row>
-    <x:row r="23" ht="38" customHeight="1">
-      <x:c r="A23" s="166" t="str">
+      <x:c r="F24" s="229"/>
+      <x:c r="G24" s="230"/>
+      <x:c r="H24" s="230"/>
+      <x:c r="I24" s="230"/>
+      <x:c r="J24" s="230"/>
+      <x:c r="K24" s="230"/>
+      <x:c r="L24" s="231"/>
+    </x:row>
+    <x:row r="25" ht="38" customHeight="1">
+      <x:c r="A25" s="188" t="str">
+        <x:v>Medidata BioStamp nPoint</x:v>
+      </x:c>
+      <x:c r="B25" s="189" t="str">
+        <x:v>US research comparator</x:v>
+      </x:c>
+      <x:c r="C25" s="198" t="n">
+        <x:f>'Feature Matrix'!AA19</x:f>
+        <x:v>47.5</x:v>
+      </x:c>
+      <x:c r="D25" s="190" t="str">
+        <x:v>Diligence</x:v>
+      </x:c>
+      <x:c r="F25" s="229"/>
+      <x:c r="G25" s="230"/>
+      <x:c r="H25" s="230"/>
+      <x:c r="I25" s="230"/>
+      <x:c r="J25" s="230"/>
+      <x:c r="K25" s="230"/>
+      <x:c r="L25" s="231"/>
+    </x:row>
+    <x:row r="26" ht="38" customHeight="1">
+      <x:c r="A26" s="191" t="str">
         <x:v>Corsano CardioWatch 287-2</x:v>
       </x:c>
-      <x:c r="B23" s="167" t="str">
+      <x:c r="B26" s="192" t="str">
         <x:v>Cuffless-BP diligence</x:v>
       </x:c>
-      <x:c r="C23" s="174" t="n">
+      <x:c r="C26" s="199" t="n">
         <x:f>'Feature Matrix'!AA15</x:f>
         <x:v>98.5</x:v>
       </x:c>
-      <x:c r="D23" s="168" t="str">
+      <x:c r="D26" s="193" t="str">
         <x:v>Vendor diligence</x:v>
       </x:c>
-      <x:c r="F23" s="207"/>
-      <x:c r="G23" s="208"/>
-      <x:c r="H23" s="208"/>
-      <x:c r="I23" s="208"/>
-      <x:c r="J23" s="208"/>
-      <x:c r="K23" s="208"/>
-      <x:c r="L23" s="209"/>
-    </x:row>
-    <x:row r="25">
-      <x:c r="A25" s="210" t="str">
+      <x:c r="F26" s="232"/>
+      <x:c r="G26" s="233"/>
+      <x:c r="H26" s="233"/>
+      <x:c r="I26" s="233"/>
+      <x:c r="J26" s="233"/>
+      <x:c r="K26" s="233"/>
+      <x:c r="L26" s="234"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="235" t="str">
         <x:v>Device</x:v>
       </x:c>
-      <x:c r="B25" s="210" t="str">
+      <x:c r="B28" s="235" t="str">
         <x:v>Capability score</x:v>
       </x:c>
     </x:row>
-    <x:row r="26">
-      <x:c r="A26" s="210" t="str">
+    <x:row r="29">
+      <x:c r="A29" s="235" t="str">
         <x:f>'Feature Matrix'!B2</x:f>
         <x:v>Apple Watch Series 11</x:v>
       </x:c>
-      <x:c r="B26" s="211" t="n">
+      <x:c r="B29" s="236" t="n">
         <x:f>'Feature Matrix'!AA2</x:f>
         <x:v>44</x:v>
       </x:c>
     </x:row>
-    <x:row r="27">
-      <x:c r="A27" s="210" t="str">
+    <x:row r="30">
+      <x:c r="A30" s="235" t="str">
         <x:f>'Feature Matrix'!B3</x:f>
         <x:v>ActiGraph LEAP</x:v>
       </x:c>
-      <x:c r="B27" s="211" t="n">
+      <x:c r="B30" s="236" t="n">
         <x:f>'Feature Matrix'!AA3</x:f>
         <x:v>64</x:v>
       </x:c>
     </x:row>
-    <x:row r="28">
-      <x:c r="A28" s="210" t="str">
+    <x:row r="31">
+      <x:c r="A31" s="235" t="str">
         <x:f>'Feature Matrix'!B4</x:f>
         <x:v>Biostrap Kairos</x:v>
       </x:c>
-      <x:c r="B28" s="211" t="n">
+      <x:c r="B31" s="236" t="n">
         <x:f>'Feature Matrix'!AA4</x:f>
         <x:v>59.5</x:v>
       </x:c>
     </x:row>
-    <x:row r="29">
-      <x:c r="A29" s="210" t="str">
+    <x:row r="32">
+      <x:c r="A32" s="235" t="str">
         <x:f>'Feature Matrix'!B5</x:f>
         <x:v>VitalConnect VitalPatch RTM</x:v>
       </x:c>
-      <x:c r="B29" s="211" t="n">
+      <x:c r="B32" s="236" t="n">
         <x:f>'Feature Matrix'!AA5</x:f>
         <x:v>60</x:v>
       </x:c>
     </x:row>
-    <x:row r="30">
-      <x:c r="A30" s="210" t="str">
+    <x:row r="33">
+      <x:c r="A33" s="235" t="str">
         <x:f>'Feature Matrix'!B6</x:f>
         <x:v>Google Pixel Watch 4</x:v>
       </x:c>
-      <x:c r="B30" s="211" t="n">
+      <x:c r="B33" s="236" t="n">
         <x:f>'Feature Matrix'!AA6</x:f>
         <x:v>47</x:v>
       </x:c>
     </x:row>
-    <x:row r="31">
-      <x:c r="A31" s="210" t="str">
+    <x:row r="34">
+      <x:c r="A34" s="235" t="str">
         <x:f>'Feature Matrix'!B7</x:f>
         <x:v>Fitbit Sense 2</x:v>
       </x:c>
-      <x:c r="B31" s="211" t="n">
+      <x:c r="B34" s="236" t="n">
         <x:f>'Feature Matrix'!AA7</x:f>
         <x:v>37.5</x:v>
       </x:c>
     </x:row>
-    <x:row r="32">
-      <x:c r="A32" s="210" t="str">
+    <x:row r="35">
+      <x:c r="A35" s="235" t="str">
         <x:f>'Feature Matrix'!B8</x:f>
         <x:v>Garmin Venu 4</x:v>
       </x:c>
-      <x:c r="B32" s="211" t="n">
+      <x:c r="B35" s="236" t="n">
         <x:f>'Feature Matrix'!AA8</x:f>
         <x:v>46.5</x:v>
       </x:c>
     </x:row>
-    <x:row r="33">
-      <x:c r="A33" s="210" t="str">
+    <x:row r="36">
+      <x:c r="A36" s="235" t="str">
         <x:f>'Feature Matrix'!B9</x:f>
         <x:v>WHOOP MG</x:v>
       </x:c>
-      <x:c r="B33" s="211" t="n">
+      <x:c r="B36" s="236" t="n">
         <x:f>'Feature Matrix'!AA9</x:f>
         <x:v>36.5</x:v>
       </x:c>
     </x:row>
-    <x:row r="34">
-      <x:c r="A34" s="210" t="str">
+    <x:row r="37">
+      <x:c r="A37" s="235" t="str">
         <x:f>'Feature Matrix'!B10</x:f>
         <x:v>BioIntelliSense BioButton Rechargeable</x:v>
       </x:c>
-      <x:c r="B34" s="211" t="n">
+      <x:c r="B37" s="236" t="n">
         <x:f>'Feature Matrix'!AA10</x:f>
         <x:v>31</x:v>
       </x:c>
     </x:row>
-    <x:row r="35">
-      <x:c r="A35" s="210" t="str">
+    <x:row r="38">
+      <x:c r="A38" s="235" t="str">
         <x:f>'Feature Matrix'!B11</x:f>
         <x:v>Masimo W1 Medical</x:v>
       </x:c>
-      <x:c r="B35" s="211" t="n">
+      <x:c r="B38" s="236" t="n">
         <x:f>'Feature Matrix'!AA11</x:f>
         <x:v>34</x:v>
       </x:c>
     </x:row>
-    <x:row r="36">
-      <x:c r="A36" s="210" t="str">
+    <x:row r="39">
+      <x:c r="A39" s="235" t="str">
         <x:f>'Feature Matrix'!B12</x:f>
         <x:v>iRhythm Zio AT</x:v>
       </x:c>
-      <x:c r="B36" s="211" t="n">
+      <x:c r="B39" s="236" t="n">
         <x:f>'Feature Matrix'!AA12</x:f>
         <x:v>37.5</x:v>
       </x:c>
     </x:row>
-    <x:row r="37">
-      <x:c r="A37" s="210" t="str">
+    <x:row r="40">
+      <x:c r="A40" s="235" t="str">
         <x:f>'Feature Matrix'!B13</x:f>
         <x:v>Samsung Galaxy Watch8</x:v>
       </x:c>
-      <x:c r="B37" s="211" t="n">
+      <x:c r="B40" s="236" t="n">
         <x:f>'Feature Matrix'!AA13</x:f>
         <x:v>75</x:v>
       </x:c>
     </x:row>
-    <x:row r="38">
-      <x:c r="A38" s="210" t="str">
+    <x:row r="41">
+      <x:c r="A41" s="235" t="str">
         <x:f>'Feature Matrix'!B14</x:f>
         <x:v>Empatica EmbracePlus</x:v>
       </x:c>
-      <x:c r="B38" s="211" t="n">
+      <x:c r="B41" s="236" t="n">
         <x:f>'Feature Matrix'!AA14</x:f>
         <x:v>68.5</x:v>
       </x:c>
     </x:row>
-    <x:row r="39">
-      <x:c r="A39" s="210" t="str">
+    <x:row r="42">
+      <x:c r="A42" s="235" t="str">
         <x:f>'Feature Matrix'!B15</x:f>
         <x:v>Corsano CardioWatch 287-2</x:v>
       </x:c>
-      <x:c r="B39" s="211" t="n">
+      <x:c r="B42" s="236" t="n">
         <x:f>'Feature Matrix'!AA15</x:f>
         <x:v>98.5</x:v>
       </x:c>
     </x:row>
-    <x:row r="40">
-      <x:c r="A40" s="210" t="str">
+    <x:row r="43">
+      <x:c r="A43" s="235" t="str">
         <x:f>'Feature Matrix'!B16</x:f>
         <x:v>Huawei Watch D2</x:v>
       </x:c>
-      <x:c r="B40" s="211" t="n">
+      <x:c r="B43" s="236" t="n">
         <x:f>'Feature Matrix'!AA16</x:f>
         <x:v>44.5</x:v>
       </x:c>
     </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="235" t="str">
+        <x:f>'Feature Matrix'!B17</x:f>
+        <x:v>Vivalink VV330/VV350 Continuous ECG Platform</x:v>
+      </x:c>
+      <x:c r="B44" s="236" t="n">
+        <x:f>'Feature Matrix'!AA17</x:f>
+        <x:v>60</x:v>
+      </x:c>
+    </x:row>
     <x:row r="45">
-      <x:c r="A45" s="213" t="str">
+      <x:c r="A45" s="235" t="str">
+        <x:f>'Feature Matrix'!B18</x:f>
+        <x:v>Sibel ANNE One</x:v>
+      </x:c>
+      <x:c r="B45" s="236" t="n">
+        <x:f>'Feature Matrix'!AA18</x:f>
+        <x:v>69.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="235" t="str">
+        <x:f>'Feature Matrix'!B19</x:f>
+        <x:v>Medidata BioStamp nPoint</x:v>
+      </x:c>
+      <x:c r="B46" s="236" t="n">
+        <x:f>'Feature Matrix'!AA19</x:f>
+        <x:v>47.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="238" t="str">
         <x:v>Critical boundary</x:v>
       </x:c>
-      <x:c r="B45" s="213"/>
-      <x:c r="C45" s="213"/>
-      <x:c r="D45" s="213"/>
-      <x:c r="E45" s="213"/>
-      <x:c r="F45" s="213"/>
-      <x:c r="G45" s="213"/>
-      <x:c r="H45" s="213"/>
-      <x:c r="I45" s="213"/>
-      <x:c r="J45" s="213"/>
-      <x:c r="K45" s="213"/>
-      <x:c r="L45" s="213"/>
-    </x:row>
-    <x:row r="46">
-      <x:c r="A46" s="216" t="str">
+      <x:c r="B50" s="238"/>
+      <x:c r="C50" s="238"/>
+      <x:c r="D50" s="238"/>
+      <x:c r="E50" s="238"/>
+      <x:c r="F50" s="238"/>
+      <x:c r="G50" s="238"/>
+      <x:c r="H50" s="238"/>
+      <x:c r="I50" s="238"/>
+      <x:c r="J50" s="238"/>
+      <x:c r="K50" s="238"/>
+      <x:c r="L50" s="238"/>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="241" t="str">
         <x:v>A check mark means a capability exists, not that it is accurate or validated for venipuncture presyncope. Fast cuffless BP must be compared with a synchronized continuous reference. Optical signals must be stratified by motion, perfusion, fit, wrist circumference, and objectively measured skin pigmentation.</x:v>
       </x:c>
-      <x:c r="B46" s="216"/>
-      <x:c r="C46" s="216"/>
-      <x:c r="D46" s="216"/>
-      <x:c r="E46" s="216"/>
-      <x:c r="F46" s="216"/>
-      <x:c r="G46" s="216"/>
-      <x:c r="H46" s="216"/>
-      <x:c r="I46" s="216"/>
-      <x:c r="J46" s="216"/>
-      <x:c r="K46" s="216"/>
-      <x:c r="L46" s="216"/>
-    </x:row>
-    <x:row r="47">
-      <x:c r="A47" s="216"/>
-      <x:c r="B47" s="216"/>
-      <x:c r="C47" s="216"/>
-      <x:c r="D47" s="216"/>
-      <x:c r="E47" s="216"/>
-      <x:c r="F47" s="216"/>
-      <x:c r="G47" s="216"/>
-      <x:c r="H47" s="216"/>
-      <x:c r="I47" s="216"/>
-      <x:c r="J47" s="216"/>
-      <x:c r="K47" s="216"/>
-      <x:c r="L47" s="216"/>
-    </x:row>
-    <x:row r="48">
-      <x:c r="A48" s="216"/>
-      <x:c r="B48" s="216"/>
-      <x:c r="C48" s="216"/>
-      <x:c r="D48" s="216"/>
-      <x:c r="E48" s="216"/>
-      <x:c r="F48" s="216"/>
-      <x:c r="G48" s="216"/>
-      <x:c r="H48" s="216"/>
-      <x:c r="I48" s="216"/>
-      <x:c r="J48" s="216"/>
-      <x:c r="K48" s="216"/>
-      <x:c r="L48" s="216"/>
-    </x:row>
-    <x:row r="49">
-      <x:c r="A49" s="216"/>
-      <x:c r="B49" s="216"/>
-      <x:c r="C49" s="216"/>
-      <x:c r="D49" s="216"/>
-      <x:c r="E49" s="216"/>
-      <x:c r="F49" s="216"/>
-      <x:c r="G49" s="216"/>
-      <x:c r="H49" s="216"/>
-      <x:c r="I49" s="216"/>
-      <x:c r="J49" s="216"/>
-      <x:c r="K49" s="216"/>
-      <x:c r="L49" s="216"/>
+      <x:c r="B51" s="241"/>
+      <x:c r="C51" s="241"/>
+      <x:c r="D51" s="241"/>
+      <x:c r="E51" s="241"/>
+      <x:c r="F51" s="241"/>
+      <x:c r="G51" s="241"/>
+      <x:c r="H51" s="241"/>
+      <x:c r="I51" s="241"/>
+      <x:c r="J51" s="241"/>
+      <x:c r="K51" s="241"/>
+      <x:c r="L51" s="241"/>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="241"/>
+      <x:c r="B52" s="241"/>
+      <x:c r="C52" s="241"/>
+      <x:c r="D52" s="241"/>
+      <x:c r="E52" s="241"/>
+      <x:c r="F52" s="241"/>
+      <x:c r="G52" s="241"/>
+      <x:c r="H52" s="241"/>
+      <x:c r="I52" s="241"/>
+      <x:c r="J52" s="241"/>
+      <x:c r="K52" s="241"/>
+      <x:c r="L52" s="241"/>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="241"/>
+      <x:c r="B53" s="241"/>
+      <x:c r="C53" s="241"/>
+      <x:c r="D53" s="241"/>
+      <x:c r="E53" s="241"/>
+      <x:c r="F53" s="241"/>
+      <x:c r="G53" s="241"/>
+      <x:c r="H53" s="241"/>
+      <x:c r="I53" s="241"/>
+      <x:c r="J53" s="241"/>
+      <x:c r="K53" s="241"/>
+      <x:c r="L53" s="241"/>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="241"/>
+      <x:c r="B54" s="241"/>
+      <x:c r="C54" s="241"/>
+      <x:c r="D54" s="241"/>
+      <x:c r="E54" s="241"/>
+      <x:c r="F54" s="241"/>
+      <x:c r="G54" s="241"/>
+      <x:c r="H54" s="241"/>
+      <x:c r="I54" s="241"/>
+      <x:c r="J54" s="241"/>
+      <x:c r="K54" s="241"/>
+      <x:c r="L54" s="241"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -2063,12 +2229,12 @@
     <x:mergeCell ref="A10:L10"/>
     <x:mergeCell ref="A11:L14"/>
     <x:mergeCell ref="F16:L16"/>
-    <x:mergeCell ref="F17:L23"/>
-    <x:mergeCell ref="A45:L45"/>
-    <x:mergeCell ref="A46:L49"/>
+    <x:mergeCell ref="F17:L26"/>
+    <x:mergeCell ref="A50:L50"/>
+    <x:mergeCell ref="A51:L54"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd0abf5eb3bc24b5b"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re59aca7cc4f041e2"/>
 </x:worksheet>
 </file>
 
@@ -3649,8 +3815,297 @@
         <x:v>BP comparator</x:v>
       </x:c>
     </x:row>
+    <x:row r="17" ht="50" customHeight="1">
+      <x:c r="A17" s="42" t="str">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B17" s="43" t="str">
+        <x:v>Vivalink VV330/VV350 Continuous ECG Platform</x:v>
+      </x:c>
+      <x:c r="C17" s="43" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="D17" s="43" t="str">
+        <x:v>chest patch — US open-integration reference finalist</x:v>
+      </x:c>
+      <x:c r="E17" s="44" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F17" s="44" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G17" s="44" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H17" s="44" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I17" s="44" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J17" s="44" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K17" s="44" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L17" s="44" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M17" s="44" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N17" s="44" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O17" s="44" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P17" s="44" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q17" s="44" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R17" s="44" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S17" s="44" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T17" s="44" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U17" s="42" t="str">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="V17" s="43" t="str">
+        <x:v>Vivalink mobile SDK; cloud API; file download; BLE</x:v>
+      </x:c>
+      <x:c r="W17" s="43" t="str">
+        <x:v>128 Hz raw ECG plus R-R, HR, respiration, skin temperature, posture, and accelerometry; confirm exact VV330/VV350 configuration and contracted data fields</x:v>
+      </x:c>
+      <x:c r="X17" s="43" t="str">
+        <x:v>VIV01;VIV02;VIV03;VAL13</x:v>
+      </x:c>
+      <x:c r="Y17" s="45" t="n">
+        <x:f>E17*'Codebook'!$B$5+F17*'Codebook'!$B$6+G17*'Codebook'!$B$7+H17*'Codebook'!$B$8+I17*'Codebook'!$B$9+J17*'Codebook'!$B$10+K17*'Codebook'!$B$11+L17*'Codebook'!$B$12+M17*'Codebook'!$B$13+N17*'Codebook'!$B$14+O17*'Codebook'!$B$15</x:f>
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="Z17" s="45" t="n">
+        <x:f>P17*'Codebook'!$E$5+Q17*'Codebook'!$E$6+R17*'Codebook'!$E$7+S17*'Codebook'!$E$8+T17*'Codebook'!$E$9</x:f>
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="AA17" s="45" t="n">
+        <x:f>Y17+Z17</x:f>
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="AB17" s="45" t="n">
+        <x:f>AA17-$AA$2</x:f>
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="AC17" s="43" t="str">
+        <x:f>IF(AA17&gt;=70,"High data potential",IF(AA17&gt;=50,"Pilot potential","Comparator"))</x:f>
+        <x:v>Pilot potential</x:v>
+      </x:c>
+      <x:c r="AD17" s="43" t="str">
+        <x:v>Reference finalist</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="50" customHeight="1">
+      <x:c r="A18" s="42" t="str">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B18" s="43" t="str">
+        <x:v>Sibel ANNE One</x:v>
+      </x:c>
+      <x:c r="C18" s="43" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="D18" s="43" t="str">
+        <x:v>dual chest/finger skin sensors — US multimodal reference finalist</x:v>
+      </x:c>
+      <x:c r="E18" s="44" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F18" s="44" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G18" s="44" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H18" s="44" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I18" s="44" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J18" s="44" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K18" s="44" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L18" s="44" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M18" s="44" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N18" s="44" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O18" s="44" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P18" s="44" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q18" s="44" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R18" s="44" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S18" s="44" t="str">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="T18" s="44" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U18" s="42" t="str"/>
+      <x:c r="V18" s="43" t="str">
+        <x:v>ANNE View/Discovery; synchronized Bluetooth tablet; contract-gated research export</x:v>
+      </x:c>
+      <x:c r="W18" s="43" t="str">
+        <x:v>High-rate synchronized ECG and finger PPG are unusually relevant, but the finger module and adhesives may interfere with workflow; public SDK terms are not established</x:v>
+      </x:c>
+      <x:c r="X18" s="43" t="str">
+        <x:v>SIB01;SIB02;SIB03;VAL14</x:v>
+      </x:c>
+      <x:c r="Y18" s="45" t="n">
+        <x:f>E18*'Codebook'!$B$5+F18*'Codebook'!$B$6+G18*'Codebook'!$B$7+H18*'Codebook'!$B$8+I18*'Codebook'!$B$9+J18*'Codebook'!$B$10+K18*'Codebook'!$B$11+L18*'Codebook'!$B$12+M18*'Codebook'!$B$13+N18*'Codebook'!$B$14+O18*'Codebook'!$B$15</x:f>
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="Z18" s="45" t="n">
+        <x:f>P18*'Codebook'!$E$5+Q18*'Codebook'!$E$6+R18*'Codebook'!$E$7+S18*'Codebook'!$E$8+T18*'Codebook'!$E$9</x:f>
+        <x:v>31.5</x:v>
+      </x:c>
+      <x:c r="AA18" s="45" t="n">
+        <x:f>Y18+Z18</x:f>
+        <x:v>69.5</x:v>
+      </x:c>
+      <x:c r="AB18" s="45" t="n">
+        <x:f>AA18-$AA$2</x:f>
+        <x:v>25.5</x:v>
+      </x:c>
+      <x:c r="AC18" s="43" t="str">
+        <x:f>IF(AA18&gt;=70,"High data potential",IF(AA18&gt;=50,"Pilot potential","Comparator"))</x:f>
+        <x:v>Pilot potential</x:v>
+      </x:c>
+      <x:c r="AD18" s="43" t="str">
+        <x:v>Reference finalist</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="50" customHeight="1">
+      <x:c r="A19" s="42" t="str">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B19" s="43" t="str">
+        <x:v>Medidata BioStamp nPoint</x:v>
+      </x:c>
+      <x:c r="C19" s="43" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="D19" s="43" t="str">
+        <x:v>multi-site skin patch — US clinical-research comparator</x:v>
+      </x:c>
+      <x:c r="E19" s="44" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F19" s="44" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G19" s="44" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H19" s="44" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I19" s="44" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J19" s="44" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K19" s="44" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L19" s="44" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M19" s="44" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N19" s="44" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O19" s="44" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P19" s="44" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q19" s="44" t="str">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="R19" s="44" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S19" s="44" t="str">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="T19" s="44" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U19" s="42" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V19" s="43" t="str">
+        <x:v>Medidata Sensor Cloud; Investigator Portal; Link Hub/mobile transfer</x:v>
+      </x:c>
+      <x:c r="W19" s="43" t="str">
+        <x:v>Raw biopotential and motion data are available for research, but synchronization is platform-based rather than a confirmed low-latency alert stream and daily charging creates gaps</x:v>
+      </x:c>
+      <x:c r="X19" s="43" t="str">
+        <x:v>BST01;BST02;VAL15</x:v>
+      </x:c>
+      <x:c r="Y19" s="45" t="n">
+        <x:f>E19*'Codebook'!$B$5+F19*'Codebook'!$B$6+G19*'Codebook'!$B$7+H19*'Codebook'!$B$8+I19*'Codebook'!$B$9+J19*'Codebook'!$B$10+K19*'Codebook'!$B$11+L19*'Codebook'!$B$12+M19*'Codebook'!$B$13+N19*'Codebook'!$B$14+O19*'Codebook'!$B$15</x:f>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="Z19" s="45" t="n">
+        <x:f>P19*'Codebook'!$E$5+Q19*'Codebook'!$E$6+R19*'Codebook'!$E$7+S19*'Codebook'!$E$8+T19*'Codebook'!$E$9</x:f>
+        <x:v>25.5</x:v>
+      </x:c>
+      <x:c r="AA19" s="45" t="n">
+        <x:f>Y19+Z19</x:f>
+        <x:v>47.5</x:v>
+      </x:c>
+      <x:c r="AB19" s="45" t="n">
+        <x:f>AA19-$AA$2</x:f>
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="AC19" s="43" t="str">
+        <x:f>IF(AA19&gt;=70,"High data potential",IF(AA19&gt;=50,"Pilot potential","Comparator"))</x:f>
+        <x:v>Comparator</x:v>
+      </x:c>
+      <x:c r="AD19" s="43" t="str">
+        <x:v>Research comparator</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="E2:T16">
+  <x:conditionalFormatting sqref="E2:T19">
     <x:cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <x:formula>1</x:formula>
     </x:cfRule>
@@ -3661,7 +4116,7 @@
       <x:formula>0</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="AA2:AA16">
+  <x:conditionalFormatting sqref="AA2:AA19">
     <x:cfRule type="dataBar" priority="4">
       <x:dataBar>
         <x:cfvo type="min"/>
@@ -3670,7 +4125,7 @@
       </x:dataBar>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="AB2:AB16">
+  <x:conditionalFormatting sqref="AB2:AB19">
     <x:cfRule type="colorScale" priority="5">
       <x:colorScale>
         <x:cfvo type="min"/>
@@ -3684,7 +4139,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb14e2aa4b30d408b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7f0f2700707d427f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3723,382 +4178,451 @@
       <x:c r="G2" s="3"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="43" t="str">
+      <x:c r="A3" s="47" t="str">
         <x:v>Real-time = a study app can programmatically receive timestamped samples. A live number visible only in a vendor app is not counted.</x:v>
       </x:c>
-      <x:c r="B3" s="43"/>
-      <x:c r="C3" s="43"/>
-      <x:c r="D3" s="43"/>
-      <x:c r="E3" s="43"/>
-      <x:c r="F3" s="43"/>
-      <x:c r="G3" s="43"/>
+      <x:c r="B3" s="47"/>
+      <x:c r="C3" s="47"/>
+      <x:c r="D3" s="47"/>
+      <x:c r="E3" s="47"/>
+      <x:c r="F3" s="47"/>
+      <x:c r="G3" s="47"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="46" t="str">
+      <x:c r="A5" s="50" t="str">
         <x:v>Device</x:v>
       </x:c>
-      <x:c r="B5" s="46" t="str">
+      <x:c r="B5" s="50" t="str">
         <x:v>Programmatic live path</x:v>
       </x:c>
-      <x:c r="C5" s="46" t="str">
+      <x:c r="C5" s="50" t="str">
         <x:v>Raw export</x:v>
       </x:c>
-      <x:c r="D5" s="46" t="str">
+      <x:c r="D5" s="50" t="str">
         <x:v>Manual export</x:v>
       </x:c>
-      <x:c r="E5" s="46" t="str">
+      <x:c r="E5" s="50" t="str">
         <x:v>Typical data shape</x:v>
       </x:c>
-      <x:c r="F5" s="46" t="str">
+      <x:c r="F5" s="50" t="str">
         <x:v>Primary gate</x:v>
       </x:c>
-      <x:c r="G5" s="46" t="str">
+      <x:c r="G5" s="50" t="str">
         <x:v>Vitestro role</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="52" customHeight="1">
-      <x:c r="A6" s="57" t="str">
+      <x:c r="A6" s="61" t="str">
         <x:v>Apple Watch Series 11</x:v>
       </x:c>
-      <x:c r="B6" s="58" t="str">
+      <x:c r="B6" s="62" t="str">
         <x:v>△ HR + motion in watchOS session</x:v>
       </x:c>
-      <x:c r="C6" s="58" t="str">
+      <x:c r="C6" s="62" t="str">
         <x:v>△ Saved ECG voltage only</x:v>
       </x:c>
-      <x:c r="D6" s="58" t="str">
+      <x:c r="D6" s="62" t="str">
         <x:v>✓ Health XML</x:v>
       </x:c>
-      <x:c r="E6" s="58" t="str">
+      <x:c r="E6" s="62" t="str">
         <x:v>HealthKit samples; Core Motion; XML</x:v>
       </x:c>
-      <x:c r="F6" s="58" t="str">
+      <x:c r="F6" s="62" t="str">
         <x:v>No raw PPG/EDA/BP</x:v>
       </x:c>
-      <x:c r="G6" s="59" t="str">
+      <x:c r="G6" s="63" t="str">
         <x:v>iOS/UX baseline</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="52" customHeight="1">
-      <x:c r="A7" s="51" t="str">
+      <x:c r="A7" s="55" t="str">
         <x:v>ActiGraph LEAP</x:v>
       </x:c>
-      <x:c r="B7" s="52" t="str">
+      <x:c r="B7" s="56" t="str">
         <x:v>△ Device-to-platform transfer; latency to measure</x:v>
       </x:c>
-      <x:c r="C7" s="52" t="str">
+      <x:c r="C7" s="56" t="str">
         <x:v>✓ Raw PPG + motion through platform</x:v>
       </x:c>
-      <x:c r="D7" s="52" t="str">
+      <x:c r="D7" s="56" t="str">
         <x:v>✓</x:v>
       </x:c>
-      <x:c r="E7" s="52" t="str">
+      <x:c r="E7" s="56" t="str">
         <x:v>CentrePoint/API/ActiLife records</x:v>
       </x:c>
-      <x:c r="F7" s="52" t="str">
+      <x:c r="F7" s="56" t="str">
         <x:v>Confirm live latency and enabled sensors</x:v>
       </x:c>
-      <x:c r="G7" s="53" t="str">
+      <x:c r="G7" s="57" t="str">
         <x:v>Primary US wrist research</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="52" customHeight="1">
-      <x:c r="A8" s="51" t="str">
+      <x:c r="A8" s="55" t="str">
         <x:v>Biostrap Kairos</x:v>
       </x:c>
-      <x:c r="B8" s="52" t="str">
+      <x:c r="B8" s="56" t="str">
         <x:v>△ Cloud live path and Bluetooth SDK by contract</x:v>
       </x:c>
-      <x:c r="C8" s="52" t="str">
+      <x:c r="C8" s="56" t="str">
         <x:v>✓ Raw PPG/IBI + motion</x:v>
       </x:c>
-      <x:c r="D8" s="52" t="str">
+      <x:c r="D8" s="56" t="str">
         <x:v>✓</x:v>
       </x:c>
-      <x:c r="E8" s="52" t="str">
+      <x:c r="E8" s="56" t="str">
         <x:v>Raw/processed cloud data</x:v>
       </x:c>
-      <x:c r="F8" s="52" t="str">
+      <x:c r="F8" s="56" t="str">
         <x:v>Contract, sample rate, and latency</x:v>
       </x:c>
-      <x:c r="G8" s="53" t="str">
+      <x:c r="G8" s="57" t="str">
         <x:v>Independent US wrist research</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="52" customHeight="1">
-      <x:c r="A9" s="51" t="str">
+      <x:c r="A9" s="55" t="str">
         <x:v>VitalConnect VitalPatch RTM</x:v>
       </x:c>
-      <x:c r="B9" s="52" t="str">
+      <x:c r="B9" s="56" t="str">
         <x:v>✓ Clinical platform and relay APIs</x:v>
       </x:c>
-      <x:c r="C9" s="52" t="str">
+      <x:c r="C9" s="56" t="str">
         <x:v>✓ ECG/R-R and processed channels</x:v>
       </x:c>
-      <x:c r="D9" s="52" t="str">
+      <x:c r="D9" s="56" t="str">
         <x:v>✓ CSV</x:v>
       </x:c>
-      <x:c r="E9" s="52" t="str">
+      <x:c r="E9" s="56" t="str">
         <x:v>Continuous ECG/HR/RR/temp/posture</x:v>
       </x:c>
-      <x:c r="F9" s="52" t="str">
+      <x:c r="F9" s="56" t="str">
         <x:v>Chest placement and adhesive workflow</x:v>
       </x:c>
-      <x:c r="G9" s="53" t="str">
+      <x:c r="G9" s="57" t="str">
         <x:v>Clinical signal reference</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="52" customHeight="1">
-      <x:c r="A10" s="51" t="str">
+      <x:c r="A10" s="55" t="str">
         <x:v>Google Pixel Watch 4</x:v>
       </x:c>
-      <x:c r="B10" s="52" t="str">
+      <x:c r="B10" s="56" t="str">
         <x:v>△ Processed HR via Wear OS Health Services</x:v>
       </x:c>
-      <x:c r="C10" s="52" t="str">
+      <x:c r="C10" s="56" t="str">
         <x:v>✗</x:v>
       </x:c>
-      <x:c r="D10" s="52" t="str">
+      <x:c r="D10" s="56" t="str">
         <x:v>✓ Fitbit/Google archive</x:v>
       </x:c>
-      <x:c r="E10" s="52" t="str">
+      <x:c r="E10" s="56" t="str">
         <x:v>~1 Hz exercise HR; passive batches</x:v>
       </x:c>
-      <x:c r="F10" s="52" t="str">
+      <x:c r="F10" s="56" t="str">
         <x:v>No raw PPG/EDA export</x:v>
       </x:c>
-      <x:c r="G10" s="53" t="str">
+      <x:c r="G10" s="57" t="str">
         <x:v>Android integration comparator</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="52" customHeight="1">
-      <x:c r="A11" s="51" t="str">
+      <x:c r="A11" s="55" t="str">
         <x:v>Fitbit Sense 2</x:v>
       </x:c>
-      <x:c r="B11" s="52" t="str">
+      <x:c r="B11" s="56" t="str">
         <x:v>✗ Public API is not low-latency live</x:v>
       </x:c>
-      <x:c r="C11" s="52" t="str">
+      <x:c r="C11" s="56" t="str">
         <x:v>✗</x:v>
       </x:c>
-      <x:c r="D11" s="52" t="str">
+      <x:c r="D11" s="56" t="str">
         <x:v>✓ CSV/archive</x:v>
       </x:c>
-      <x:c r="E11" s="52" t="str">
+      <x:c r="E11" s="56" t="str">
         <x:v>Processed JSON/CSV</x:v>
       </x:c>
-      <x:c r="F11" s="52" t="str">
+      <x:c r="F11" s="56" t="str">
         <x:v>Multi-user intraday approval</x:v>
       </x:c>
-      <x:c r="G11" s="53" t="str">
+      <x:c r="G11" s="57" t="str">
         <x:v>Fitbit stress comparator</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="52" customHeight="1">
-      <x:c r="A12" s="51" t="str">
+      <x:c r="A12" s="55" t="str">
         <x:v>Garmin Venu 4</x:v>
       </x:c>
-      <x:c r="B12" s="52" t="str">
+      <x:c r="B12" s="56" t="str">
         <x:v>△ Garmin Health SDK partner stream</x:v>
       </x:c>
-      <x:c r="C12" s="52" t="str">
+      <x:c r="C12" s="56" t="str">
         <x:v>△ Processed/B2B + motion</x:v>
       </x:c>
-      <x:c r="D12" s="52" t="str">
+      <x:c r="D12" s="56" t="str">
         <x:v>✓</x:v>
       </x:c>
-      <x:c r="E12" s="52" t="str">
+      <x:c r="E12" s="56" t="str">
         <x:v>Partner SDK + cloud JSON/FIT</x:v>
       </x:c>
-      <x:c r="F12" s="52" t="str">
+      <x:c r="F12" s="56" t="str">
         <x:v>Enterprise contract</x:v>
       </x:c>
-      <x:c r="G12" s="53" t="str">
+      <x:c r="G12" s="57" t="str">
         <x:v>Long-wear processed stream</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="52" customHeight="1">
-      <x:c r="A13" s="51" t="str">
+      <x:c r="A13" s="55" t="str">
         <x:v>WHOOP MG</x:v>
       </x:c>
-      <x:c r="B13" s="52" t="str">
+      <x:c r="B13" s="56" t="str">
         <x:v>✗ Public API is aggregate/post-sync</x:v>
       </x:c>
-      <x:c r="C13" s="52" t="str">
+      <x:c r="C13" s="56" t="str">
         <x:v>✗</x:v>
       </x:c>
-      <x:c r="D13" s="52" t="str">
+      <x:c r="D13" s="56" t="str">
         <x:v>✓ CSV</x:v>
       </x:c>
-      <x:c r="E13" s="52" t="str">
+      <x:c r="E13" s="56" t="str">
         <x:v>Cycle/recovery/workout/sleep objects</x:v>
       </x:c>
-      <x:c r="F13" s="52" t="str">
+      <x:c r="F13" s="56" t="str">
         <x:v>No raw optical stream</x:v>
       </x:c>
-      <x:c r="G13" s="53" t="str">
+      <x:c r="G13" s="57" t="str">
         <x:v>Longitudinal baseline only</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="52" customHeight="1">
-      <x:c r="A14" s="51" t="str">
+      <x:c r="A14" s="55" t="str">
         <x:v>BioButton Rechargeable</x:v>
       </x:c>
-      <x:c r="B14" s="52" t="str">
+      <x:c r="B14" s="56" t="str">
         <x:v>△ Platform transfer of resting values</x:v>
       </x:c>
-      <x:c r="C14" s="52" t="str">
+      <x:c r="C14" s="56" t="str">
         <x:v>✗</x:v>
       </x:c>
-      <x:c r="D14" s="52" t="str">
+      <x:c r="D14" s="56" t="str">
         <x:v>△</x:v>
       </x:c>
-      <x:c r="E14" s="52" t="str">
+      <x:c r="E14" s="56" t="str">
         <x:v>Resting HR/RR/temp/activity</x:v>
       </x:c>
-      <x:c r="F14" s="52" t="str">
+      <x:c r="F14" s="56" t="str">
         <x:v>HR/RR suppressed during motion</x:v>
       </x:c>
-      <x:c r="G14" s="53" t="str">
+      <x:c r="G14" s="57" t="str">
         <x:v>Ward-monitoring comparator</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="52" customHeight="1">
-      <x:c r="A15" s="51" t="str">
+      <x:c r="A15" s="55" t="str">
         <x:v>Masimo W1 Medical</x:v>
       </x:c>
-      <x:c r="B15" s="52" t="str">
+      <x:c r="B15" s="56" t="str">
         <x:v>△ Clinical/UI pathway; public API unconfirmed</x:v>
       </x:c>
-      <x:c r="C15" s="52" t="str">
+      <x:c r="C15" s="56" t="str">
         <x:v>✗</x:v>
       </x:c>
-      <x:c r="D15" s="52" t="str">
+      <x:c r="D15" s="56" t="str">
         <x:v>△</x:v>
       </x:c>
-      <x:c r="E15" s="52" t="str">
+      <x:c r="E15" s="56" t="str">
         <x:v>SpO2/PR/HR/perfusion-index records</x:v>
       </x:c>
-      <x:c r="F15" s="52" t="str">
+      <x:c r="F15" s="56" t="str">
         <x:v>No open raw optical stream</x:v>
       </x:c>
-      <x:c r="G15" s="53" t="str">
+      <x:c r="G15" s="57" t="str">
         <x:v>Medical SpO2 comparator</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="52" customHeight="1">
-      <x:c r="A16" s="51" t="str">
+      <x:c r="A16" s="55" t="str">
         <x:v>iRhythm Zio AT</x:v>
       </x:c>
-      <x:c r="B16" s="52" t="str">
+      <x:c r="B16" s="56" t="str">
         <x:v>△ Event transmissions through clinical service</x:v>
       </x:c>
-      <x:c r="C16" s="52" t="str">
+      <x:c r="C16" s="56" t="str">
         <x:v>△ Contract-dependent ECG access</x:v>
       </x:c>
-      <x:c r="D16" s="52" t="str">
+      <x:c r="D16" s="56" t="str">
         <x:v>△ Reports</x:v>
       </x:c>
-      <x:c r="E16" s="52" t="str">
+      <x:c r="E16" s="56" t="str">
         <x:v>Continuous ECG + event transmissions</x:v>
       </x:c>
-      <x:c r="F16" s="52" t="str">
+      <x:c r="F16" s="56" t="str">
         <x:v>Not an open research stream</x:v>
       </x:c>
-      <x:c r="G16" s="53" t="str">
+      <x:c r="G16" s="57" t="str">
         <x:v>Cardiac comparator</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="52" customHeight="1">
-      <x:c r="A17" s="60" t="str">
+      <x:c r="A17" s="64" t="str">
         <x:v>Samsung Galaxy Watch8</x:v>
       </x:c>
-      <x:c r="B17" s="61" t="str">
+      <x:c r="B17" s="65" t="str">
         <x:v>✓ Sensor SDK: PPG/IBI/EDA/temp/ACC</x:v>
       </x:c>
-      <x:c r="C17" s="61" t="str">
+      <x:c r="C17" s="65" t="str">
         <x:v>✓ App-controlled raw samples</x:v>
       </x:c>
-      <x:c r="D17" s="61" t="str">
+      <x:c r="D17" s="65" t="str">
         <x:v>✓ Account download</x:v>
       </x:c>
-      <x:c r="E17" s="61" t="str">
+      <x:c r="E17" s="65" t="str">
         <x:v>25 Hz PPG/ACC; 1 Hz HR/IBI/EDA</x:v>
       </x:c>
-      <x:c r="F17" s="61" t="str">
+      <x:c r="F17" s="65" t="str">
         <x:v>Partner approval for distribution</x:v>
       </x:c>
-      <x:c r="G17" s="62" t="str">
+      <x:c r="G17" s="66" t="str">
         <x:v>Direct-evidence control</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="52" customHeight="1">
-      <x:c r="A18" s="60" t="str">
+      <x:c r="A18" s="64" t="str">
         <x:v>Empatica EmbracePlus</x:v>
       </x:c>
-      <x:c r="B18" s="61" t="str">
+      <x:c r="B18" s="65" t="str">
         <x:v>△ Continuous device-to-cloud; latency to test</x:v>
       </x:c>
-      <x:c r="C18" s="61" t="str">
+      <x:c r="C18" s="65" t="str">
         <x:v>✓ Avro BVP/EDA/temp/ACC/tags</x:v>
       </x:c>
-      <x:c r="D18" s="61" t="str">
+      <x:c r="D18" s="65" t="str">
         <x:v>✓</x:v>
       </x:c>
-      <x:c r="E18" s="61" t="str">
+      <x:c r="E18" s="65" t="str">
         <x:v>High-frequency Avro + cloud API</x:v>
       </x:c>
-      <x:c r="F18" s="61" t="str">
+      <x:c r="F18" s="65" t="str">
         <x:v>Contract/plan + cloud latency</x:v>
       </x:c>
-      <x:c r="G18" s="62" t="str">
+      <x:c r="G18" s="66" t="str">
         <x:v>Research autonomic reference</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="52" customHeight="1">
-      <x:c r="A19" s="60" t="str">
+      <x:c r="A19" s="64" t="str">
         <x:v>Corsano CardioWatch 287-2</x:v>
       </x:c>
-      <x:c r="B19" s="61" t="str">
+      <x:c r="B19" s="65" t="str">
         <x:v>✓ Vendor real-time cloud/API/SDK</x:v>
       </x:c>
-      <x:c r="C19" s="61" t="str">
+      <x:c r="C19" s="65" t="str">
         <x:v>✓ Raw G/R/IR PPG + CSV/API</x:v>
       </x:c>
-      <x:c r="D19" s="61" t="str">
+      <x:c r="D19" s="65" t="str">
         <x:v>✓</x:v>
       </x:c>
-      <x:c r="E19" s="61" t="str">
+      <x:c r="E19" s="65" t="str">
         <x:v>REST/SDK + raw/processed exports</x:v>
       </x:c>
-      <x:c r="F19" s="61" t="str">
+      <x:c r="F19" s="65" t="str">
         <x:v>Rx/region/endpoints + independent validation</x:v>
       </x:c>
-      <x:c r="G19" s="62" t="str">
+      <x:c r="G19" s="66" t="str">
         <x:v>Conditional all-in-one candidate</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="52" customHeight="1">
-      <x:c r="A20" s="63" t="str">
+      <x:c r="A20" s="64" t="str">
         <x:v>Huawei Watch D2</x:v>
       </x:c>
-      <x:c r="B20" s="64" t="str">
+      <x:c r="B20" s="65" t="str">
         <x:v>✗ Public real-time path not confirmed</x:v>
       </x:c>
-      <x:c r="C20" s="64" t="str">
+      <x:c r="C20" s="65" t="str">
         <x:v>✗</x:v>
       </x:c>
-      <x:c r="D20" s="64" t="str">
+      <x:c r="D20" s="65" t="str">
         <x:v>△</x:v>
       </x:c>
-      <x:c r="E20" s="64" t="str">
+      <x:c r="E20" s="65" t="str">
         <x:v>Huawei Health/Health Kit records</x:v>
       </x:c>
-      <x:c r="F20" s="64" t="str">
+      <x:c r="F20" s="65" t="str">
         <x:v>Region + Health Kit access</x:v>
       </x:c>
-      <x:c r="G20" s="65" t="str">
+      <x:c r="G20" s="66" t="str">
         <x:v>Intermittent BP comparator</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="52" customHeight="1">
+      <x:c r="A21" s="64" t="str">
+        <x:v>Vivalink VV330/VV350</x:v>
+      </x:c>
+      <x:c r="B21" s="65" t="str">
+        <x:v>✓ Local SDK/BLE and cloud integration</x:v>
+      </x:c>
+      <x:c r="C21" s="65" t="str">
+        <x:v>✓ 128 Hz ECG plus R-R/HR and motion</x:v>
+      </x:c>
+      <x:c r="D21" s="65" t="str">
+        <x:v>✓ File download</x:v>
+      </x:c>
+      <x:c r="E21" s="65" t="str">
+        <x:v>Raw ECG; R-R; HR; RR; temp; posture; ACC</x:v>
+      </x:c>
+      <x:c r="F21" s="65" t="str">
+        <x:v>Lock exact model, fields, and local/cloud latency</x:v>
+      </x:c>
+      <x:c r="G21" s="66" t="str">
+        <x:v>US reference finalist</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="52" customHeight="1">
+      <x:c r="A22" s="64" t="str">
+        <x:v>Sibel ANNE One</x:v>
+      </x:c>
+      <x:c r="B22" s="65" t="str">
+        <x:v>✓ Synchronized Bluetooth streaming to tablet</x:v>
+      </x:c>
+      <x:c r="C22" s="65" t="str">
+        <x:v>✓ 512 Hz ECG + 128 Hz finger PPG + motion/temp</x:v>
+      </x:c>
+      <x:c r="D22" s="65" t="str">
+        <x:v>✓ Research export</x:v>
+      </x:c>
+      <x:c r="E22" s="65" t="str">
+        <x:v>Time-synchronized dual-sensor raw waveforms</x:v>
+      </x:c>
+      <x:c r="F22" s="65" t="str">
+        <x:v>Contracted SDK/export plus finger and adhesive workflow</x:v>
+      </x:c>
+      <x:c r="G22" s="66" t="str">
+        <x:v>US multimodal reference finalist</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="52" customHeight="1">
+      <x:c r="A23" s="67" t="str">
+        <x:v>Medidata BioStamp nPoint</x:v>
+      </x:c>
+      <x:c r="B23" s="68" t="str">
+        <x:v>△ Device-to-mobile/cloud synchronization</x:v>
+      </x:c>
+      <x:c r="C23" s="68" t="str">
+        <x:v>✓ Raw biopotential + ACC/gyro</x:v>
+      </x:c>
+      <x:c r="D23" s="68" t="str">
+        <x:v>✓ Investigator export</x:v>
+      </x:c>
+      <x:c r="E23" s="68" t="str">
+        <x:v>Raw research files + derived HR/HRV/RR/posture</x:v>
+      </x:c>
+      <x:c r="F23" s="68" t="str">
+        <x:v>Not a confirmed low-latency alert stream; daily charging</x:v>
+      </x:c>
+      <x:c r="G23" s="69" t="str">
+        <x:v>US research comparator</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4108,12 +4632,324 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c18d402f183486a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb8e656d5a4694626"/>
   </x:tableParts>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="31" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="39" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="61" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="54" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="31" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="3" t="str">
+        <x:v>Signal Evidence &amp; Intended Role</x:v>
+      </x:c>
+      <x:c r="B1" s="3"/>
+      <x:c r="C1" s="3"/>
+      <x:c r="D1" s="3"/>
+      <x:c r="E1" s="3"/>
+      <x:c r="F1" s="3"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="3"/>
+      <x:c r="B2" s="3"/>
+      <x:c r="C2" s="3"/>
+      <x:c r="D2" s="3"/>
+      <x:c r="E2" s="3"/>
+      <x:c r="F2" s="3"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="47" t="str">
+        <x:v>Wearable-first does not mean single-signal. Continuous BP is a development reference; facial RGB/thermal are optional auxiliary channels with separate privacy and robustness gates.</x:v>
+      </x:c>
+      <x:c r="B3" s="47"/>
+      <x:c r="C3" s="47"/>
+      <x:c r="D3" s="47"/>
+      <x:c r="E3" s="47"/>
+      <x:c r="F3" s="47"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="50" t="str">
+        <x:v>modality</x:v>
+      </x:c>
+      <x:c r="B5" s="50" t="str">
+        <x:v>deployment_class</x:v>
+      </x:c>
+      <x:c r="C5" s="50" t="str">
+        <x:v>vitestro_role</x:v>
+      </x:c>
+      <x:c r="D5" s="50" t="str">
+        <x:v>evidence_summary</x:v>
+      </x:c>
+      <x:c r="E5" s="50" t="str">
+        <x:v>main_failure_mode</x:v>
+      </x:c>
+      <x:c r="F5" s="50" t="str">
+        <x:v>source_ids</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="68" customHeight="1">
+      <x:c r="A6" s="88" t="str">
+        <x:v>Continuous beat-to-beat blood pressure</x:v>
+      </x:c>
+      <x:c r="B6" s="89" t="str">
+        <x:v>Development reference only</x:v>
+      </x:c>
+      <x:c r="C6" s="89" t="str">
+        <x:v>Ground truth for rapid hemodynamic change</x:v>
+      </x:c>
+      <x:c r="D6" s="89" t="str">
+        <x:v>Joint BP/R-R models and BP-only deep learning predict tilt-induced syncope, but wearable cuffless systems have not reliably tracked the rapid presyncopal BP fall</x:v>
+      </x:c>
+      <x:c r="E6" s="89" t="str">
+        <x:v>No reviewed wrist device provides validated fast continuous BP for this use case</x:v>
+      </x:c>
+      <x:c r="F6" s="90" t="str">
+        <x:v>CLN03;CLN15;CLN16;CLN17;BP01;BP02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="68" customHeight="1">
+      <x:c r="A7" s="64" t="str">
+        <x:v>ECG and R-R intervals</x:v>
+      </x:c>
+      <x:c r="B7" s="65" t="str">
+        <x:v>Primary reference and candidate feature</x:v>
+      </x:c>
+      <x:c r="C7" s="65" t="str">
+        <x:v>Cardiac timing, rhythm, HR trend, and ECG-derived HRV</x:v>
+      </x:c>
+      <x:c r="D7" s="65" t="str">
+        <x:v>ECG-derived R-R adds mechanistic and modeling value; HRV alone is not sufficiently discriminative</x:v>
+      </x:c>
+      <x:c r="E7" s="65" t="str">
+        <x:v>Chest adhesion, motion artifact, and false equivalence between ECG HRV and PPG PRV</x:v>
+      </x:c>
+      <x:c r="F7" s="66" t="str">
+        <x:v>CLN03;CLN09;CLN12;CLN17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="68" customHeight="1">
+      <x:c r="A8" s="64" t="str">
+        <x:v>Raw wrist PPG</x:v>
+      </x:c>
+      <x:c r="B8" s="65" t="str">
+        <x:v>Primary deployable wearable candidate</x:v>
+      </x:c>
+      <x:c r="C8" s="65" t="str">
+        <x:v>Pulse waveform morphology, pulse-rate trend, PRV, perfusion proxies, and signal quality</x:v>
+      </x:c>
+      <x:c r="D8" s="65" t="str">
+        <x:v>A Galaxy Watch raw-PPG model showed direct prospective HUT prediction evidence</x:v>
+      </x:c>
+      <x:c r="E8" s="65" t="str">
+        <x:v>Controlled HUT evidence may not generalize to venipuncture; motion, low perfusion, fit, and pigmentation affect quality</x:v>
+      </x:c>
+      <x:c r="F8" s="66" t="str">
+        <x:v>VVS01;CLN08;CLN09;OPT01;OPT02;VAL02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="68" customHeight="1">
+      <x:c r="A9" s="91" t="str">
+        <x:v>Electrodermal activity</x:v>
+      </x:c>
+      <x:c r="B9" s="92" t="str">
+        <x:v>Secondary autonomic candidate</x:v>
+      </x:c>
+      <x:c r="C9" s="92" t="str">
+        <x:v>Sweating/arousal signal and potential early warning</x:v>
+      </x:c>
+      <x:c r="D9" s="92" t="str">
+        <x:v>EDA increased before syncope in 62% of syncopal HUT patients and often preceded measured hemodynamic change</x:v>
+      </x:c>
+      <x:c r="E9" s="92" t="str">
+        <x:v>Absent in 25% and strongly confounded by anxiety, pain, thermoregulation, and sensor location</x:v>
+      </x:c>
+      <x:c r="F9" s="93" t="str">
+        <x:v>CLN14;CLN04</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="68" customHeight="1">
+      <x:c r="A10" s="91" t="str">
+        <x:v>Skin temperature and peripheral perfusion</x:v>
+      </x:c>
+      <x:c r="B10" s="92" t="str">
+        <x:v>Secondary contextual candidate</x:v>
+      </x:c>
+      <x:c r="C10" s="92" t="str">
+        <x:v>Peripheral vasomotor context and optical-signal interpretation</x:v>
+      </x:c>
+      <x:c r="D10" s="92" t="str">
+        <x:v>Peripheral or facial temperature changes may contain anticipatory information</x:v>
+      </x:c>
+      <x:c r="E10" s="92" t="str">
+        <x:v>Ambient conditions, attachment site, and slow thermal dynamics limit acute specificity</x:v>
+      </x:c>
+      <x:c r="F10" s="93" t="str">
+        <x:v>VIS02;OPT01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="68" customHeight="1">
+      <x:c r="A11" s="91" t="str">
+        <x:v>Respiration</x:v>
+      </x:c>
+      <x:c r="B11" s="92" t="str">
+        <x:v>Secondary contextual candidate</x:v>
+      </x:c>
+      <x:c r="C11" s="92" t="str">
+        <x:v>Hyperventilation, anxiety, and cardiopulmonary context</x:v>
+      </x:c>
+      <x:c r="D11" s="92" t="str">
+        <x:v>Respiratory change can help distinguish discomfort or anxiety from hemodynamic collapse</x:v>
+      </x:c>
+      <x:c r="E11" s="92" t="str">
+        <x:v>Many devices expose only derived or rest-gated respiratory rate rather than a raw waveform</x:v>
+      </x:c>
+      <x:c r="F11" s="93" t="str">
+        <x:v>CLN20;VIT01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="68" customHeight="1">
+      <x:c r="A12" s="91" t="str">
+        <x:v>SpO2</x:v>
+      </x:c>
+      <x:c r="B12" s="92" t="str">
+        <x:v>Context and safety comparator</x:v>
+      </x:c>
+      <x:c r="C12" s="92" t="str">
+        <x:v>Late hypoxemia check and optical-quality context</x:v>
+      </x:c>
+      <x:c r="D12" s="92" t="str">
+        <x:v>Useful as a reference safety channel when clinically indicated</x:v>
+      </x:c>
+      <x:c r="E12" s="92" t="str">
+        <x:v>Usually intermittent or algorithmically smoothed and is not an established early VVR detector</x:v>
+      </x:c>
+      <x:c r="F12" s="93" t="str">
+        <x:v>REG03;VAL03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="68" customHeight="1">
+      <x:c r="A13" s="91" t="str">
+        <x:v>Motion, posture, and robot phase</x:v>
+      </x:c>
+      <x:c r="B13" s="92" t="str">
+        <x:v>Required context and quality channel</x:v>
+      </x:c>
+      <x:c r="C13" s="92" t="str">
+        <x:v>Artifact rejection, procedural staging, and recovery/posture annotation</x:v>
+      </x:c>
+      <x:c r="D13" s="92" t="str">
+        <x:v>Procedure phase and movement are necessary to interpret wearable physiology</x:v>
+      </x:c>
+      <x:c r="E13" s="92" t="str">
+        <x:v>Unlogged movement can create false changes that resemble acute physiology</x:v>
+      </x:c>
+      <x:c r="F13" s="93" t="str">
+        <x:v>CLN08;VAL02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="68" customHeight="1">
+      <x:c r="A14" s="91" t="str">
+        <x:v>Prodromal symptoms</x:v>
+      </x:c>
+      <x:c r="B14" s="92" t="str">
+        <x:v>Co-primary label channel</x:v>
+      </x:c>
+      <x:c r="C14" s="92" t="str">
+        <x:v>Separate presyncope from pain, anxiety, nausea, and general discomfort</x:v>
+      </x:c>
+      <x:c r="D14" s="92" t="str">
+        <x:v>Prodromes have an ordered time course; standardized donor-reaction instruments and ISBT categories improve labeling</x:v>
+      </x:c>
+      <x:c r="E14" s="92" t="str">
+        <x:v>Self-report can be delayed or absent and must not be treated as a perfect reference</x:v>
+      </x:c>
+      <x:c r="F14" s="93" t="str">
+        <x:v>CLN18;CLN19;CLN20;CLN21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="68" customHeight="1">
+      <x:c r="A15" s="94" t="str">
+        <x:v>Baseline clinical and procedural risk</x:v>
+      </x:c>
+      <x:c r="B15" s="95" t="str">
+        <x:v>Pre-procedure risk stratum</x:v>
+      </x:c>
+      <x:c r="C15" s="95" t="str">
+        <x:v>Calibrate prior probability before acute sensing</x:v>
+      </x:c>
+      <x:c r="D15" s="95" t="str">
+        <x:v>Age, first donation, blood volume, BP, fear, anxiety, prior reaction, and procedure context recur across donor studies</x:v>
+      </x:c>
+      <x:c r="E15" s="95" t="str">
+        <x:v>Baseline risk factors do not detect an acute event and can encode population bias</x:v>
+      </x:c>
+      <x:c r="F15" s="96" t="str">
+        <x:v>CLN01;CLN02;CLN13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="68" customHeight="1">
+      <x:c r="A16" s="94" t="str">
+        <x:v>Facial RGB video</x:v>
+      </x:c>
+      <x:c r="B16" s="95" t="str">
+        <x:v>Optional non-wearable auxiliary</x:v>
+      </x:c>
+      <x:c r="C16" s="95" t="str">
+        <x:v>Pre-procedure risk signal and observable pain/anxiety context</x:v>
+      </x:c>
+      <x:c r="D16" s="95" t="str">
+        <x:v>Facial-action and short-video models have shown direct blood-donation VVR classification signals</x:v>
+      </x:c>
+      <x:c r="E16" s="95" t="str">
+        <x:v>Lighting, pose, occlusion, privacy, demographic robustness, and limited external validation</x:v>
+      </x:c>
+      <x:c r="F16" s="96" t="str">
+        <x:v>VIS01;VIS03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="68" customHeight="1">
+      <x:c r="A17" s="97" t="str">
+        <x:v>Facial thermal imaging</x:v>
+      </x:c>
+      <x:c r="B17" s="98" t="str">
+        <x:v>Optional non-wearable auxiliary</x:v>
+      </x:c>
+      <x:c r="C17" s="98" t="str">
+        <x:v>Pre-procedure autonomic/perfusion signal</x:v>
+      </x:c>
+      <x:c r="D17" s="98" t="str">
+        <x:v>A 193-donor study reported sensitivity 0.87, specificity 0.84, F1 0.86, and PR-AUC 0.93</x:v>
+      </x:c>
+      <x:c r="E17" s="98" t="str">
+        <x:v>Specialized camera, ambient-temperature control, small test set, and no external Vitestro validation</x:v>
+      </x:c>
+      <x:c r="F17" s="99" t="str">
+        <x:v>VIS02;CLN13</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:F2"/>
+    <x:mergeCell ref="A3:F3"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0df86b8a0f514b97"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -4144,212 +4980,232 @@
       <x:c r="F2" s="3"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="68" t="str">
+      <x:c r="A3" s="102" t="str">
         <x:v>Research gate plan. Standard clinical observation and response remain authoritative; no unvalidated wearable alert may control the robot or patient care.</x:v>
       </x:c>
-      <x:c r="B3" s="68"/>
-      <x:c r="C3" s="68"/>
-      <x:c r="D3" s="68"/>
-      <x:c r="E3" s="68"/>
-      <x:c r="F3" s="68"/>
+      <x:c r="B3" s="102"/>
+      <x:c r="C3" s="102"/>
+      <x:c r="D3" s="102"/>
+      <x:c r="E3" s="102"/>
+      <x:c r="F3" s="102"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="46" t="str">
+      <x:c r="A5" s="50" t="str">
         <x:v>Gate</x:v>
       </x:c>
-      <x:c r="B5" s="46" t="str">
+      <x:c r="B5" s="50" t="str">
         <x:v>Objective</x:v>
       </x:c>
-      <x:c r="C5" s="46" t="str">
+      <x:c r="C5" s="50" t="str">
         <x:v>Required test</x:v>
       </x:c>
-      <x:c r="D5" s="46" t="str">
+      <x:c r="D5" s="50" t="str">
         <x:v>Required output</x:v>
       </x:c>
-      <x:c r="E5" s="46" t="str">
+      <x:c r="E5" s="50" t="str">
         <x:v>Decision rule</x:v>
       </x:c>
-      <x:c r="F5" s="46" t="str">
+      <x:c r="F5" s="50" t="str">
         <x:v>Failure disposition</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="69" customHeight="1">
-      <x:c r="A6" s="57" t="str">
+    <x:row r="6" ht="76" customHeight="1">
+      <x:c r="A6" s="61" t="str">
         <x:v>G0 Contract &amp; ownership</x:v>
       </x:c>
-      <x:c r="B6" s="58" t="str">
+      <x:c r="B6" s="62" t="str">
         <x:v>Legal right to use sample-level data for research/algorithm development</x:v>
       </x:c>
-      <x:c r="C6" s="58" t="str">
+      <x:c r="C6" s="62" t="str">
         <x:v>Review DPA, license, API terms, retention, deletion and vendor-change clauses</x:v>
       </x:c>
-      <x:c r="D6" s="58" t="str">
+      <x:c r="D6" s="62" t="str">
         <x:v>Signed data-rights matrix</x:v>
       </x:c>
-      <x:c r="E6" s="58" t="str">
+      <x:c r="E6" s="62" t="str">
         <x:v>All required signals exportable under approved terms</x:v>
       </x:c>
-      <x:c r="F6" s="59" t="str">
+      <x:c r="F6" s="63" t="str">
         <x:v>Do not procure; UI comparator only</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="69" customHeight="1">
-      <x:c r="A7" s="69" t="str">
+    <x:row r="7" ht="76" customHeight="1">
+      <x:c r="A7" s="91" t="str">
         <x:v>G1 Interface inventory</x:v>
       </x:c>
-      <x:c r="B7" s="70" t="str">
+      <x:c r="B7" s="92" t="str">
         <x:v>Prove exact device/firmware/phone/country capabilities</x:v>
       </x:c>
-      <x:c r="C7" s="70" t="str">
+      <x:c r="C7" s="92" t="str">
         <x:v>Record SDK version, permissions, runtime capability query and sample payloads</x:v>
       </x:c>
-      <x:c r="D7" s="70" t="str">
+      <x:c r="D7" s="92" t="str">
         <x:v>Version-locked interface dossier</x:v>
       </x:c>
-      <x:c r="E7" s="70" t="str">
+      <x:c r="E7" s="92" t="str">
         <x:v>No undocumented dependency for a primary signal</x:v>
       </x:c>
-      <x:c r="F7" s="71" t="str">
+      <x:c r="F7" s="93" t="str">
         <x:v>Mark blocked-by-vendor or downgrade role</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="69" customHeight="1">
-      <x:c r="A8" s="69" t="str">
+    <x:row r="8" ht="76" customHeight="1">
+      <x:c r="A8" s="91" t="str">
         <x:v>G2 Real-time behavior</x:v>
       </x:c>
-      <x:c r="B8" s="70" t="str">
+      <x:c r="B8" s="92" t="str">
         <x:v>Measure latency, batching, dropouts and clock behavior</x:v>
       </x:c>
-      <x:c r="C8" s="70" t="str">
+      <x:c r="C8" s="92" t="str">
         <x:v>60-min sessions: foreground/background/lock/low-battery/BT interruption/phone call</x:v>
       </x:c>
-      <x:c r="D8" s="70" t="str">
+      <x:c r="D8" s="92" t="str">
         <x:v>Latency CDF; dropout runs; timestamp map</x:v>
       </x:c>
-      <x:c r="E8" s="70" t="str">
-        <x:v>Predefined median/P95 latency and completeness targets met</x:v>
-      </x:c>
-      <x:c r="F8" s="71" t="str">
+      <x:c r="E8" s="92" t="str">
+        <x:v>Initial targets: ≥99% completeness; max primary gap ≤2 s; clock median ≤100 ms and P95 ≤250 ms; live-latency P95 ≤2 s</x:v>
+      </x:c>
+      <x:c r="F8" s="93" t="str">
         <x:v>Historical-data role only</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="69" customHeight="1">
-      <x:c r="A9" s="69" t="str">
+    <x:row r="9" ht="76" customHeight="1">
+      <x:c r="A9" s="91" t="str">
         <x:v>G3 Export parity</x:v>
       </x:c>
-      <x:c r="B9" s="70" t="str">
+      <x:c r="B9" s="92" t="str">
         <x:v>Ensure live, cloud and manual records reconcile</x:v>
       </x:c>
-      <x:c r="C9" s="70" t="str">
+      <x:c r="C9" s="92" t="str">
         <x:v>Export the same session by every supported route</x:v>
       </x:c>
-      <x:c r="D9" s="70" t="str">
+      <x:c r="D9" s="92" t="str">
         <x:v>Sample-count and timestamp reconciliation</x:v>
       </x:c>
-      <x:c r="E9" s="70" t="str">
+      <x:c r="E9" s="92" t="str">
         <x:v>No unexplained loss or time shift</x:v>
       </x:c>
-      <x:c r="F9" s="71" t="str">
+      <x:c r="F9" s="93" t="str">
         <x:v>Block modeling until resolved</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="69" customHeight="1">
-      <x:c r="A10" s="60" t="str">
+    <x:row r="10" ht="76" customHeight="1">
+      <x:c r="A10" s="64" t="str">
         <x:v>G4 Reference validity</x:v>
       </x:c>
-      <x:c r="B10" s="61" t="str">
+      <x:c r="B10" s="65" t="str">
         <x:v>Quantify signal accuracy in Vitestro posture/workflow</x:v>
       </x:c>
-      <x:c r="C10" s="61" t="str">
+      <x:c r="C10" s="65" t="str">
         <x:v>Synchronized 3-lead ECG, beat-to-beat BP, reference SpO2 when relevant</x:v>
       </x:c>
-      <x:c r="D10" s="61" t="str">
+      <x:c r="D10" s="65" t="str">
         <x:v>Agreement, coverage, quality and drift report</x:v>
       </x:c>
-      <x:c r="E10" s="61" t="str">
+      <x:c r="E10" s="65" t="str">
         <x:v>Pre-registered metric thresholds met</x:v>
       </x:c>
-      <x:c r="F10" s="62" t="str">
+      <x:c r="F10" s="66" t="str">
         <x:v>Remove signal/device from model inputs</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="69" customHeight="1">
-      <x:c r="A11" s="60" t="str">
+    <x:row r="11" ht="76" customHeight="1">
+      <x:c r="A11" s="64" t="str">
         <x:v>G5 Robustness</x:v>
       </x:c>
-      <x:c r="B11" s="61" t="str">
+      <x:c r="B11" s="65" t="str">
         <x:v>Detect subgroup and operating-condition failures</x:v>
       </x:c>
-      <x:c r="C11" s="61" t="str">
+      <x:c r="C11" s="65" t="str">
         <x:v>Motion, fit, wrist, wrist circumference, objective skin tone, perfusion and ambient-temperature strata</x:v>
       </x:c>
-      <x:c r="D11" s="61" t="str">
+      <x:c r="D11" s="65" t="str">
         <x:v>Stratified error and missingness audit</x:v>
       </x:c>
-      <x:c r="E11" s="61" t="str">
+      <x:c r="E11" s="65" t="str">
         <x:v>No unacceptable subgroup degradation</x:v>
       </x:c>
-      <x:c r="F11" s="62" t="str">
+      <x:c r="F11" s="66" t="str">
         <x:v>Redesign sensor/placement or restrict intended use</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="69" customHeight="1">
-      <x:c r="A12" s="72" t="str">
-        <x:v>G6 Clinical feasibility</x:v>
-      </x:c>
-      <x:c r="B12" s="73" t="str">
+    <x:row r="12" ht="76" customHeight="1">
+      <x:c r="A12" s="64" t="str">
+        <x:v>G6 Label standardization</x:v>
+      </x:c>
+      <x:c r="B12" s="65" t="str">
+        <x:v>Separate VVR/presyncope from pain, anxiety, and general discomfort</x:v>
+      </x:c>
+      <x:c r="C12" s="65" t="str">
+        <x:v>Independent adjudication using ISBT/IHN VVR categories, brief BDRI, robot phase, operator observations, and reference physiology</x:v>
+      </x:c>
+      <x:c r="D12" s="65" t="str">
+        <x:v>Timestamped label ledger with source and adjudication status</x:v>
+      </x:c>
+      <x:c r="E12" s="65" t="str">
+        <x:v>No experimental wearable output used to define its own outcome</x:v>
+      </x:c>
+      <x:c r="F12" s="66" t="str">
+        <x:v>Block model training until labels are reconciled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="76" customHeight="1">
+      <x:c r="A13" s="94" t="str">
+        <x:v>G7 Clinical feasibility</x:v>
+      </x:c>
+      <x:c r="B13" s="95" t="str">
         <x:v>Estimate event sensitivity, false alarms and warning lead time</x:v>
       </x:c>
-      <x:c r="C12" s="73" t="str">
+      <x:c r="C13" s="95" t="str">
         <x:v>Prospective blood-draw cohort with frozen labels/model and participant-level split</x:v>
       </x:c>
-      <x:c r="D12" s="73" t="str">
+      <x:c r="D13" s="95" t="str">
         <x:v>Sensitivity/specificity/PPV; false alarms per procedure/hour; lead-time distribution</x:v>
       </x:c>
-      <x:c r="E12" s="73" t="str">
+      <x:c r="E13" s="95" t="str">
         <x:v>Pre-registered confidence bounds met</x:v>
       </x:c>
-      <x:c r="F12" s="74" t="str">
+      <x:c r="F13" s="96" t="str">
         <x:v>Research only; no patient alert</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="69" customHeight="1">
-      <x:c r="A13" s="72" t="str">
-        <x:v>G7 Human factors &amp; safety</x:v>
-      </x:c>
-      <x:c r="B13" s="73" t="str">
+    <x:row r="14" ht="76" customHeight="1">
+      <x:c r="A14" s="94" t="str">
+        <x:v>G8 Human factors &amp; safety</x:v>
+      </x:c>
+      <x:c r="B14" s="95" t="str">
         <x:v>Ensure alerts do not delay standard care or create unsafe robot actions</x:v>
       </x:c>
-      <x:c r="C13" s="73" t="str">
+      <x:c r="C14" s="95" t="str">
         <x:v>Simulated-use and hazard analysis with clinicians/operators</x:v>
       </x:c>
-      <x:c r="D13" s="73" t="str">
+      <x:c r="D14" s="95" t="str">
         <x:v>Use-error report and risk controls</x:v>
       </x:c>
-      <x:c r="E13" s="73" t="str">
+      <x:c r="E14" s="95" t="str">
         <x:v>Residual risk acceptable and workflow approved</x:v>
       </x:c>
-      <x:c r="F13" s="74" t="str">
+      <x:c r="F14" s="96" t="str">
         <x:v>No patient-facing or robot integration</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="69" customHeight="1">
-      <x:c r="A14" s="75" t="str">
-        <x:v>G8 Regulatory &amp; QMS</x:v>
-      </x:c>
-      <x:c r="B14" s="76" t="str">
+    <x:row r="15" ht="76" customHeight="1">
+      <x:c r="A15" s="97" t="str">
+        <x:v>G9 Regulatory &amp; QMS</x:v>
+      </x:c>
+      <x:c r="B15" s="98" t="str">
         <x:v>Align intended use, software lifecycle and vendor controls</x:v>
       </x:c>
-      <x:c r="C14" s="76" t="str">
+      <x:c r="C15" s="98" t="str">
         <x:v>Regulatory classification, cybersecurity, change control, traceability and post-market plan</x:v>
       </x:c>
-      <x:c r="D14" s="76" t="str">
+      <x:c r="D15" s="98" t="str">
         <x:v>Approved regulatory/quality strategy</x:v>
       </x:c>
-      <x:c r="E14" s="76" t="str">
+      <x:c r="E15" s="98" t="str">
         <x:v>All launch prerequisites satisfied</x:v>
       </x:c>
-      <x:c r="F14" s="77" t="str">
+      <x:c r="F15" s="99" t="str">
         <x:v>Keep as non-device research prototype</x:v>
       </x:c>
     </x:row>
@@ -4360,12 +5216,12 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rda8bd6225a6e4041"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6b60165d28e841e6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -4697,7 +5553,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -4714,2377 +5570,3081 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="38" customHeight="1">
-      <x:c r="A1" s="81" t="str">
+      <x:c r="A1" s="106" t="str">
         <x:v>source_id</x:v>
       </x:c>
-      <x:c r="B1" s="81" t="str">
+      <x:c r="B1" s="106" t="str">
         <x:v>category</x:v>
       </x:c>
-      <x:c r="C1" s="81" t="str">
+      <x:c r="C1" s="106" t="str">
         <x:v>entity</x:v>
       </x:c>
-      <x:c r="D1" s="81" t="str">
+      <x:c r="D1" s="106" t="str">
         <x:v>claim_supported</x:v>
       </x:c>
-      <x:c r="E1" s="81" t="str">
+      <x:c r="E1" s="106" t="str">
         <x:v>source_type</x:v>
       </x:c>
-      <x:c r="F1" s="81" t="str">
+      <x:c r="F1" s="106" t="str">
         <x:v>url</x:v>
       </x:c>
-      <x:c r="G1" s="81" t="str">
+      <x:c r="G1" s="106" t="str">
         <x:v>published_or_updated</x:v>
       </x:c>
-      <x:c r="H1" s="81" t="str">
+      <x:c r="H1" s="106" t="str">
         <x:v>accessed_at</x:v>
       </x:c>
-      <x:c r="I1" s="81" t="str">
+      <x:c r="I1" s="106" t="str">
         <x:v>confidence</x:v>
       </x:c>
-      <x:c r="J1" s="81" t="str">
+      <x:c r="J1" s="106" t="str">
         <x:v>notes</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="84" t="str">
+      <x:c r="A2" s="109" t="str">
         <x:v>CLN01</x:v>
       </x:c>
-      <x:c r="B2" s="84" t="str">
+      <x:c r="B2" s="109" t="str">
         <x:v>clinical</x:v>
       </x:c>
-      <x:c r="C2" s="84" t="str">
+      <x:c r="C2" s="109" t="str">
         <x:v>Blood-donation vasovagal reactions</x:v>
       </x:c>
-      <x:c r="D2" s="84" t="str">
+      <x:c r="D2" s="109" t="str">
         <x:v>Younger age, first donation, smaller blood volume, lower BP, fear, and anxiety are associated with vasovagal-reaction risk</x:v>
       </x:c>
-      <x:c r="E2" s="84" t="str">
+      <x:c r="E2" s="109" t="str">
         <x:v>peer-reviewed systematic review and meta-analysis</x:v>
       </x:c>
-      <x:c r="F2" s="84" t="str">
+      <x:c r="F2" s="109" t="str">
         <x:v>https://pubmed.ncbi.nlm.nih.gov/39587929/</x:v>
       </x:c>
-      <x:c r="G2" s="84" t="str">
+      <x:c r="G2" s="109" t="str">
         <x:v>2025</x:v>
       </x:c>
-      <x:c r="H2" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I2" s="84" t="str">
+      <x:c r="H2" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I2" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J2" s="84" t="str">
+      <x:c r="J2" s="109" t="str">
         <x:v>71 studies and approximately 19 million donations; risk association is not an acute detector</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="84" t="str">
+      <x:c r="A3" s="109" t="str">
         <x:v>CLN02</x:v>
       </x:c>
-      <x:c r="B3" s="84" t="str">
+      <x:c r="B3" s="109" t="str">
         <x:v>clinical</x:v>
       </x:c>
-      <x:c r="C3" s="84" t="str">
+      <x:c r="C3" s="109" t="str">
         <x:v>Blood-donation syncope predictors</x:v>
       </x:c>
-      <x:c r="D3" s="84" t="str">
+      <x:c r="D3" s="109" t="str">
         <x:v>Age, sex, blood volume, donor status, BP, HR, prior reaction, caffeine, sleep, weight, and setting recur as predictors</x:v>
       </x:c>
-      <x:c r="E3" s="84" t="str">
+      <x:c r="E3" s="109" t="str">
         <x:v>peer-reviewed systematic review</x:v>
       </x:c>
-      <x:c r="F3" s="84" t="str">
+      <x:c r="F3" s="109" t="str">
         <x:v>https://pubmed.ncbi.nlm.nih.gov/31276216/</x:v>
       </x:c>
-      <x:c r="G3" s="84" t="str">
+      <x:c r="G3" s="109" t="str">
         <x:v>2019</x:v>
       </x:c>
-      <x:c r="H3" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I3" s="84" t="str">
+      <x:c r="H3" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I3" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J3" s="84" t="str">
+      <x:c r="J3" s="109" t="str">
         <x:v>Baseline risk factors should remain separate from acute sensing</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="84" t="str">
+      <x:c r="A4" s="109" t="str">
         <x:v>CLN03</x:v>
       </x:c>
-      <x:c r="B4" s="84" t="str">
+      <x:c r="B4" s="109" t="str">
         <x:v>clinical</x:v>
       </x:c>
-      <x:c r="C4" s="84" t="str">
+      <x:c r="C4" s="109" t="str">
         <x:v>Vasovagal syncope prediction</x:v>
       </x:c>
-      <x:c r="D4" s="84" t="str">
+      <x:c r="D4" s="109" t="str">
         <x:v>Joint continuous SBP and R-R trend and variability predicted tilt-induced syncope in 1155 patients</x:v>
       </x:c>
-      <x:c r="E4" s="84" t="str">
+      <x:c r="E4" s="109" t="str">
         <x:v>peer-reviewed cohort and algorithm study</x:v>
       </x:c>
-      <x:c r="F4" s="84" t="str">
+      <x:c r="F4" s="109" t="str">
         <x:v>https://pubmed.ncbi.nlm.nih.gov/17954394/</x:v>
       </x:c>
-      <x:c r="G4" s="84" t="str">
+      <x:c r="G4" s="109" t="str">
         <x:v>2007</x:v>
       </x:c>
-      <x:c r="H4" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I4" s="84" t="str">
+      <x:c r="H4" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I4" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J4" s="84" t="str">
+      <x:c r="J4" s="109" t="str">
         <x:v>Reported sensitivity 95% and specificity 93%; not venipuncture validation</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="84" t="str">
+      <x:c r="A5" s="109" t="str">
         <x:v>CLN04</x:v>
       </x:c>
-      <x:c r="B5" s="84" t="str">
+      <x:c r="B5" s="109" t="str">
         <x:v>clinical</x:v>
       </x:c>
-      <x:c r="C5" s="84" t="str">
+      <x:c r="C5" s="109" t="str">
         <x:v>Painful vascular instrumentation</x:v>
       </x:c>
-      <x:c r="D5" s="84" t="str">
+      <x:c r="D5" s="109" t="str">
         <x:v>Painful intravascular instrumentation reduced orthostatic tolerance in a controlled physiology study</x:v>
       </x:c>
-      <x:c r="E5" s="84" t="str">
+      <x:c r="E5" s="109" t="str">
         <x:v>peer-reviewed physiology study</x:v>
       </x:c>
-      <x:c r="F5" s="84" t="str">
+      <x:c r="F5" s="109" t="str">
         <x:v>https://pubmed.ncbi.nlm.nih.gov/37589875/</x:v>
       </x:c>
-      <x:c r="G5" s="84" t="str">
+      <x:c r="G5" s="109" t="str">
         <x:v>2023</x:v>
       </x:c>
-      <x:c r="H5" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I5" s="84" t="str">
+      <x:c r="H5" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I5" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J5" s="84" t="str">
+      <x:c r="J5" s="109" t="str">
         <x:v>Supports procedure-specific validation</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="84" t="str">
+      <x:c r="A6" s="109" t="str">
         <x:v>CLN05</x:v>
       </x:c>
-      <x:c r="B6" s="84" t="str">
+      <x:c r="B6" s="109" t="str">
         <x:v>clinical</x:v>
       </x:c>
-      <x:c r="C6" s="84" t="str">
+      <x:c r="C6" s="109" t="str">
         <x:v>Blood and injection response</x:v>
       </x:c>
-      <x:c r="D6" s="84" t="str">
+      <x:c r="D6" s="109" t="str">
         <x:v>Blood-draw and injection stimuli were evaluated with self-report, BP, and HRV</x:v>
       </x:c>
-      <x:c r="E6" s="84" t="str">
+      <x:c r="E6" s="109" t="str">
         <x:v>peer-reviewed study</x:v>
       </x:c>
-      <x:c r="F6" s="84" t="str">
+      <x:c r="F6" s="109" t="str">
         <x:v>https://pubmed.ncbi.nlm.nih.gov/22416882/</x:v>
       </x:c>
-      <x:c r="G6" s="84" t="str">
+      <x:c r="G6" s="109" t="str">
         <x:v>2012</x:v>
       </x:c>
-      <x:c r="H6" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I6" s="84" t="str">
+      <x:c r="H6" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I6" s="109" t="str">
         <x:v>medium</x:v>
       </x:c>
-      <x:c r="J6" s="84" t="str">
+      <x:c r="J6" s="109" t="str">
         <x:v>Supports synchronized symptom and physiology labels</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="84" t="str">
+      <x:c r="A7" s="109" t="str">
         <x:v>CLN06</x:v>
       </x:c>
-      <x:c r="B7" s="84" t="str">
+      <x:c r="B7" s="109" t="str">
         <x:v>clinical</x:v>
       </x:c>
-      <x:c r="C7" s="84" t="str">
+      <x:c r="C7" s="109" t="str">
         <x:v>Syncope pathophysiology</x:v>
       </x:c>
-      <x:c r="D7" s="84" t="str">
+      <x:c r="D7" s="109" t="str">
         <x:v>Contemporary review describes hemodynamic and autonomic mechanisms of syncopal reactions</x:v>
       </x:c>
-      <x:c r="E7" s="84" t="str">
+      <x:c r="E7" s="109" t="str">
         <x:v>peer-reviewed review</x:v>
       </x:c>
-      <x:c r="F7" s="84" t="str">
+      <x:c r="F7" s="109" t="str">
         <x:v>https://pubmed.ncbi.nlm.nih.gov/39822686/</x:v>
       </x:c>
-      <x:c r="G7" s="84" t="str">
+      <x:c r="G7" s="109" t="str">
         <x:v>2025</x:v>
       </x:c>
-      <x:c r="H7" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I7" s="84" t="str">
+      <x:c r="H7" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I7" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J7" s="84" t="str">
+      <x:c r="J7" s="109" t="str">
         <x:v>Mechanism background</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="84" t="str">
+      <x:c r="A8" s="109" t="str">
         <x:v>CLN07</x:v>
       </x:c>
-      <x:c r="B8" s="84" t="str">
+      <x:c r="B8" s="109" t="str">
         <x:v>clinical</x:v>
       </x:c>
-      <x:c r="C8" s="84" t="str">
+      <x:c r="C8" s="109" t="str">
         <x:v>Counterpressure and hemodynamics</x:v>
       </x:c>
-      <x:c r="D8" s="84" t="str">
+      <x:c r="D8" s="109" t="str">
         <x:v>SBP, DBP, MAP, HR, stroke volume, cardiac output, and resistance are relevant hemodynamic outcomes</x:v>
       </x:c>
-      <x:c r="E8" s="84" t="str">
+      <x:c r="E8" s="109" t="str">
         <x:v>peer-reviewed systematic review</x:v>
       </x:c>
-      <x:c r="F8" s="84" t="str">
+      <x:c r="F8" s="109" t="str">
         <x:v>https://pubmed.ncbi.nlm.nih.gov/36312294/</x:v>
       </x:c>
-      <x:c r="G8" s="84" t="str">
+      <x:c r="G8" s="109" t="str">
         <x:v>2022</x:v>
       </x:c>
-      <x:c r="H8" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I8" s="84" t="str">
+      <x:c r="H8" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I8" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J8" s="84" t="str">
+      <x:c r="J8" s="109" t="str">
         <x:v>Supports the reference-measurement set</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="84" t="str">
+      <x:c r="A9" s="109" t="str">
         <x:v>CLN08</x:v>
       </x:c>
-      <x:c r="B9" s="84" t="str">
+      <x:c r="B9" s="109" t="str">
         <x:v>clinical</x:v>
       </x:c>
-      <x:c r="C9" s="84" t="str">
+      <x:c r="C9" s="109" t="str">
         <x:v>Wearable PPG accuracy</x:v>
       </x:c>
-      <x:c r="D9" s="84" t="str">
+      <x:c r="D9" s="109" t="str">
         <x:v>Wearable PPG accuracy and application limits vary by device and use context</x:v>
       </x:c>
-      <x:c r="E9" s="84" t="str">
+      <x:c r="E9" s="109" t="str">
         <x:v>peer-reviewed scoping review</x:v>
       </x:c>
-      <x:c r="F9" s="84" t="str">
+      <x:c r="F9" s="109" t="str">
         <x:v>https://pubmed.ncbi.nlm.nih.gov/36288566/</x:v>
       </x:c>
-      <x:c r="G9" s="84" t="str">
+      <x:c r="G9" s="109" t="str">
         <x:v>2023</x:v>
       </x:c>
-      <x:c r="H9" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I9" s="84" t="str">
+      <x:c r="H9" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I9" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J9" s="84" t="str">
+      <x:c r="J9" s="109" t="str">
         <x:v>Device generation and task matter</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="84" t="str">
+      <x:c r="A10" s="109" t="str">
         <x:v>CLN09</x:v>
       </x:c>
-      <x:c r="B10" s="84" t="str">
+      <x:c r="B10" s="109" t="str">
         <x:v>clinical</x:v>
       </x:c>
-      <x:c r="C10" s="84" t="str">
+      <x:c r="C10" s="109" t="str">
         <x:v>PRV versus HRV</x:v>
       </x:c>
-      <x:c r="D10" s="84" t="str">
+      <x:c r="D10" s="109" t="str">
         <x:v>PPG-derived PRV is not automatically interchangeable with ECG-derived HRV</x:v>
       </x:c>
-      <x:c r="E10" s="84" t="str">
+      <x:c r="E10" s="109" t="str">
         <x:v>peer-reviewed clinical study</x:v>
       </x:c>
-      <x:c r="F10" s="84" t="str">
+      <x:c r="F10" s="109" t="str">
         <x:v>https://pubmed.ncbi.nlm.nih.gov/40809286/</x:v>
       </x:c>
-      <x:c r="G10" s="84" t="str">
+      <x:c r="G10" s="109" t="str">
         <x:v>2025</x:v>
       </x:c>
-      <x:c r="H10" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I10" s="84" t="str">
+      <x:c r="H10" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I10" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J10" s="84" t="str">
+      <x:c r="J10" s="109" t="str">
         <x:v>931 adults; report signal source explicitly</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="84" t="str">
+      <x:c r="A11" s="109" t="str">
         <x:v>CLN10</x:v>
       </x:c>
-      <x:c r="B11" s="84" t="str">
+      <x:c r="B11" s="109" t="str">
         <x:v>clinical</x:v>
       </x:c>
-      <x:c r="C11" s="84" t="str">
+      <x:c r="C11" s="109" t="str">
         <x:v>Hemodynamic mechanism of VVS</x:v>
       </x:c>
-      <x:c r="D11" s="84" t="str">
+      <x:c r="D11" s="109" t="str">
         <x:v>Reduced stroke volume and cardioinhibition contributed to the BP decrease before tilt-induced VVS</x:v>
       </x:c>
-      <x:c r="E11" s="84" t="str">
+      <x:c r="E11" s="109" t="str">
         <x:v>peer-reviewed cohort study</x:v>
       </x:c>
-      <x:c r="F11" s="84" t="str">
+      <x:c r="F11" s="109" t="str">
         <x:v>https://pubmed.ncbi.nlm.nih.gov/32460687/</x:v>
       </x:c>
-      <x:c r="G11" s="84" t="str">
+      <x:c r="G11" s="109" t="str">
         <x:v>2020</x:v>
       </x:c>
-      <x:c r="H11" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I11" s="84" t="str">
+      <x:c r="H11" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I11" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J11" s="84" t="str">
+      <x:c r="J11" s="109" t="str">
         <x:v>Continuous ECG and hemodynamics in 163 patients</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="84" t="str">
+      <x:c r="A12" s="109" t="str">
         <x:v>CLN11</x:v>
       </x:c>
-      <x:c r="B12" s="84" t="str">
+      <x:c r="B12" s="109" t="str">
         <x:v>clinical</x:v>
       </x:c>
-      <x:c r="C12" s="84" t="str">
+      <x:c r="C12" s="109" t="str">
         <x:v>Modern ECG and BP changes in syncope</x:v>
       </x:c>
-      <x:c r="D12" s="84" t="str">
+      <x:c r="D12" s="109" t="str">
         <x:v>Blood-pressure dynamics provided greater etiologic discrimination than ECG time-domain measures during tilt testing</x:v>
       </x:c>
-      <x:c r="E12" s="84" t="str">
+      <x:c r="E12" s="109" t="str">
         <x:v>peer-reviewed study</x:v>
       </x:c>
-      <x:c r="F12" s="84" t="str">
+      <x:c r="F12" s="109" t="str">
         <x:v>https://pubmed.ncbi.nlm.nih.gov/42245899/</x:v>
       </x:c>
-      <x:c r="G12" s="84" t="str">
+      <x:c r="G12" s="109" t="str">
         <x:v>2026</x:v>
       </x:c>
-      <x:c r="H12" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I12" s="84" t="str">
+      <x:c r="H12" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I12" s="109" t="str">
         <x:v>medium</x:v>
       </x:c>
-      <x:c r="J12" s="84" t="str">
+      <x:c r="J12" s="109" t="str">
         <x:v>Recent study; not venipuncture-specific</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="84" t="str">
+      <x:c r="A13" s="109" t="str">
         <x:v>CLN12</x:v>
       </x:c>
-      <x:c r="B13" s="84" t="str">
+      <x:c r="B13" s="109" t="str">
         <x:v>clinical</x:v>
       </x:c>
-      <x:c r="C13" s="84" t="str">
+      <x:c r="C13" s="109" t="str">
         <x:v>HRV and VVS risk</x:v>
       </x:c>
-      <x:c r="D13" s="84" t="str">
+      <x:c r="D13" s="109" t="str">
         <x:v>Holter-derived HR and HRV metrics showed only moderate predictive ability for VVS</x:v>
       </x:c>
-      <x:c r="E13" s="84" t="str">
+      <x:c r="E13" s="109" t="str">
         <x:v>peer-reviewed retrospective study</x:v>
       </x:c>
-      <x:c r="F13" s="84" t="str">
+      <x:c r="F13" s="109" t="str">
         <x:v>https://pubmed.ncbi.nlm.nih.gov/41647805/</x:v>
       </x:c>
-      <x:c r="G13" s="84" t="str">
+      <x:c r="G13" s="109" t="str">
         <x:v>2025</x:v>
       </x:c>
-      <x:c r="H13" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I13" s="84" t="str">
+      <x:c r="H13" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I13" s="109" t="str">
         <x:v>medium</x:v>
       </x:c>
-      <x:c r="J13" s="84" t="str">
+      <x:c r="J13" s="109" t="str">
         <x:v>Supports multimodal rather than HRV-only design</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="84" t="str">
+      <x:c r="A14" s="109" t="str">
         <x:v>VVS01</x:v>
       </x:c>
-      <x:c r="B14" s="84" t="str">
+      <x:c r="B14" s="109" t="str">
         <x:v>clinical</x:v>
       </x:c>
-      <x:c r="C14" s="84" t="str">
+      <x:c r="C14" s="109" t="str">
         <x:v>Smartwatch PPG VVS prediction</x:v>
       </x:c>
-      <x:c r="D14" s="84" t="str">
+      <x:c r="D14" s="109" t="str">
         <x:v>Galaxy Watch 6 raw 25 Hz PPG with a five-minute model window predicted HUT VVS in 132 patients</x:v>
       </x:c>
-      <x:c r="E14" s="84" t="str">
+      <x:c r="E14" s="109" t="str">
         <x:v>peer-reviewed prospective machine-learning study</x:v>
       </x:c>
-      <x:c r="F14" s="84" t="str">
+      <x:c r="F14" s="109" t="str">
         <x:v>https://academic.oup.com/ehjdh/article/7/4/ztag053/8586837</x:v>
       </x:c>
-      <x:c r="G14" s="84" t="str">
+      <x:c r="G14" s="109" t="str">
         <x:v>2026</x:v>
       </x:c>
-      <x:c r="H14" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I14" s="84" t="str">
+      <x:c r="H14" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I14" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J14" s="84" t="str">
+      <x:c r="J14" s="109" t="str">
         <x:v>AUROC 0.91; specificity 0.64 at sensitivity 0.90; controlled HUT and nitroglycerin limit generalization</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="84" t="str">
+      <x:c r="A15" s="109" t="str">
         <x:v>BP01</x:v>
       </x:c>
-      <x:c r="B15" s="84" t="str">
+      <x:c r="B15" s="109" t="str">
         <x:v>clinical</x:v>
       </x:c>
-      <x:c r="C15" s="84" t="str">
+      <x:c r="C15" s="109" t="str">
         <x:v>Wearable cuffless BP</x:v>
       </x:c>
-      <x:c r="D15" s="84" t="str">
+      <x:c r="D15" s="109" t="str">
         <x:v>Earlier validation literature showed heterogeneous devices and incomplete conformity with clinical validation expectations</x:v>
       </x:c>
-      <x:c r="E15" s="84" t="str">
+      <x:c r="E15" s="109" t="str">
         <x:v>peer-reviewed systematic review and meta-analysis</x:v>
       </x:c>
-      <x:c r="F15" s="84" t="str">
+      <x:c r="F15" s="109" t="str">
         <x:v>https://pubmed.ncbi.nlm.nih.gov/36713001/</x:v>
       </x:c>
-      <x:c r="G15" s="84" t="str">
+      <x:c r="G15" s="109" t="str">
         <x:v>2022</x:v>
       </x:c>
-      <x:c r="H15" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I15" s="84" t="str">
+      <x:c r="H15" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I15" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J15" s="84" t="str">
+      <x:c r="J15" s="109" t="str">
         <x:v>Cuffless claims require endpoint-specific validation</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="84" t="str">
+      <x:c r="A16" s="109" t="str">
         <x:v>BP02</x:v>
       </x:c>
-      <x:c r="B16" s="84" t="str">
+      <x:c r="B16" s="109" t="str">
         <x:v>clinical</x:v>
       </x:c>
-      <x:c r="C16" s="84" t="str">
+      <x:c r="C16" s="109" t="str">
         <x:v>Continuous wearable cuffless BP</x:v>
       </x:c>
-      <x:c r="D16" s="84" t="str">
+      <x:c r="D16" s="109" t="str">
         <x:v>Recent meta-analysis found remaining accuracy and comparability concerns against ambulatory BP references</x:v>
       </x:c>
-      <x:c r="E16" s="84" t="str">
+      <x:c r="E16" s="109" t="str">
         <x:v>peer-reviewed systematic review and meta-analysis</x:v>
       </x:c>
-      <x:c r="F16" s="84" t="str">
+      <x:c r="F16" s="109" t="str">
         <x:v>https://pubmed.ncbi.nlm.nih.gov/41321467/</x:v>
       </x:c>
-      <x:c r="G16" s="84" t="str">
+      <x:c r="G16" s="109" t="str">
         <x:v>2025</x:v>
       </x:c>
-      <x:c r="H16" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I16" s="84" t="str">
+      <x:c r="H16" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I16" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J16" s="84" t="str">
+      <x:c r="J16" s="109" t="str">
         <x:v>Methods and calibration vary across products</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="84" t="str">
+      <x:c r="A17" s="109" t="str">
         <x:v>OPT01</x:v>
       </x:c>
-      <x:c r="B17" s="84" t="str">
+      <x:c r="B17" s="109" t="str">
         <x:v>clinical</x:v>
       </x:c>
-      <x:c r="C17" s="84" t="str">
+      <x:c r="C17" s="109" t="str">
         <x:v>Skin pigmentation and optical sensing</x:v>
       </x:c>
-      <x:c r="D17" s="84" t="str">
+      <x:c r="D17" s="109" t="str">
         <x:v>SpO2 and wearable pulse-rate accuracy must be evaluated across objective pigmentation groups</x:v>
       </x:c>
-      <x:c r="E17" s="84" t="str">
+      <x:c r="E17" s="109" t="str">
         <x:v>peer-reviewed systematic review and meta-analysis</x:v>
       </x:c>
-      <x:c r="F17" s="84" t="str">
+      <x:c r="F17" s="109" t="str">
         <x:v>https://pubmed.ncbi.nlm.nih.gov/39388258/</x:v>
       </x:c>
-      <x:c r="G17" s="84" t="str">
+      <x:c r="G17" s="109" t="str">
         <x:v>2024</x:v>
       </x:c>
-      <x:c r="H17" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I17" s="84" t="str">
+      <x:c r="H17" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I17" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J17" s="84" t="str">
+      <x:c r="J17" s="109" t="str">
         <x:v>Wide pulse-rate limits of agreement and SpO2 concerns</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="84" t="str">
+      <x:c r="A18" s="109" t="str">
         <x:v>OPT02</x:v>
       </x:c>
-      <x:c r="B18" s="84" t="str">
+      <x:c r="B18" s="109" t="str">
         <x:v>clinical</x:v>
       </x:c>
-      <x:c r="C18" s="84" t="str">
+      <x:c r="C18" s="109" t="str">
         <x:v>Skin pigmentation during exercise</x:v>
       </x:c>
-      <x:c r="D18" s="84" t="str">
+      <x:c r="D18" s="109" t="str">
         <x:v>Objectively measured pigmentation was evaluated against Apple Watch and other PPG devices during rest, exercise, and recovery</x:v>
       </x:c>
-      <x:c r="E18" s="84" t="str">
+      <x:c r="E18" s="109" t="str">
         <x:v>peer-reviewed validation study</x:v>
       </x:c>
-      <x:c r="F18" s="84" t="str">
+      <x:c r="F18" s="109" t="str">
         <x:v>https://pubmed.ncbi.nlm.nih.gov/40968160/</x:v>
       </x:c>
-      <x:c r="G18" s="84" t="str">
+      <x:c r="G18" s="109" t="str">
         <x:v>2026</x:v>
       </x:c>
-      <x:c r="H18" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I18" s="84" t="str">
+      <x:c r="H18" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I18" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J18" s="84" t="str">
+      <x:c r="J18" s="109" t="str">
         <x:v>Supports objective pigmentation measurement rather than race labels</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="84" t="str">
+      <x:c r="A19" s="109" t="str">
         <x:v>VAL01</x:v>
       </x:c>
-      <x:c r="B19" s="84" t="str">
+      <x:c r="B19" s="109" t="str">
         <x:v>validation</x:v>
       </x:c>
-      <x:c r="C19" s="84" t="str">
+      <x:c r="C19" s="109" t="str">
         <x:v>Apple Watch, Polar, and Fitbit</x:v>
       </x:c>
-      <x:c r="D19" s="84" t="str">
+      <x:c r="D19" s="109" t="str">
         <x:v>Apple Watch 6 produced the most accurate HR among the three devices across tested activities</x:v>
       </x:c>
-      <x:c r="E19" s="84" t="str">
+      <x:c r="E19" s="109" t="str">
         <x:v>peer-reviewed validation study</x:v>
       </x:c>
-      <x:c r="F19" s="84" t="str">
+      <x:c r="F19" s="109" t="str">
         <x:v>https://pubmed.ncbi.nlm.nih.gov/34957939/</x:v>
       </x:c>
-      <x:c r="G19" s="84" t="str">
+      <x:c r="G19" s="109" t="str">
         <x:v>2023</x:v>
       </x:c>
-      <x:c r="H19" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I19" s="84" t="str">
+      <x:c r="H19" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I19" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J19" s="84" t="str">
+      <x:c r="J19" s="109" t="str">
         <x:v>Older generations and exercise tasks; energy expenditure was poor</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="84" t="str">
+      <x:c r="A20" s="109" t="str">
         <x:v>VAL02</x:v>
       </x:c>
-      <x:c r="B20" s="84" t="str">
+      <x:c r="B20" s="109" t="str">
         <x:v>validation</x:v>
       </x:c>
-      <x:c r="C20" s="84" t="str">
+      <x:c r="C20" s="109" t="str">
         <x:v>Transient-state wearable HR</x:v>
       </x:c>
-      <x:c r="D20" s="84" t="str">
+      <x:c r="D20" s="109" t="str">
         <x:v>Fitbit, Garmin, WHOOP, Withings, and EmbracePlus HR accuracy declined during rapid transitions</x:v>
       </x:c>
-      <x:c r="E20" s="84" t="str">
+      <x:c r="E20" s="109" t="str">
         <x:v>peer-reviewed validation study</x:v>
       </x:c>
-      <x:c r="F20" s="84" t="str">
+      <x:c r="F20" s="109" t="str">
         <x:v>https://pubmed.ncbi.nlm.nih.gov/41157371/</x:v>
       </x:c>
-      <x:c r="G20" s="84" t="str">
+      <x:c r="G20" s="109" t="str">
         <x:v>2025</x:v>
       </x:c>
-      <x:c r="H20" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I20" s="84" t="str">
+      <x:c r="H20" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I20" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J20" s="84" t="str">
+      <x:c r="J20" s="109" t="str">
         <x:v>Acute changes need context-specific validation</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="84" t="str">
+      <x:c r="A21" s="109" t="str">
         <x:v>VAL03</x:v>
       </x:c>
-      <x:c r="B21" s="84" t="str">
+      <x:c r="B21" s="109" t="str">
         <x:v>validation</x:v>
       </x:c>
-      <x:c r="C21" s="84" t="str">
+      <x:c r="C21" s="109" t="str">
         <x:v>Empatica EmbracePlus SpO2</x:v>
       </x:c>
-      <x:c r="D21" s="84" t="str">
+      <x:c r="D21" s="109" t="str">
         <x:v>Controlled hypoxia study reported ARMS 2.4% and included dark-pigmentation participants</x:v>
       </x:c>
-      <x:c r="E21" s="84" t="str">
+      <x:c r="E21" s="109" t="str">
         <x:v>peer-reviewed prospective validation study</x:v>
       </x:c>
-      <x:c r="F21" s="84" t="str">
+      <x:c r="F21" s="109" t="str">
         <x:v>https://pubmed.ncbi.nlm.nih.gov/38111608/</x:v>
       </x:c>
-      <x:c r="G21" s="84" t="str">
+      <x:c r="G21" s="109" t="str">
         <x:v>2023</x:v>
       </x:c>
-      <x:c r="H21" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I21" s="84" t="str">
+      <x:c r="H21" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I21" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J21" s="84" t="str">
+      <x:c r="J21" s="109" t="str">
         <x:v>No-motion and high-perfusion conditions; manufacturer-authored</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="84" t="str">
+      <x:c r="A22" s="109" t="str">
         <x:v>VAL04</x:v>
       </x:c>
-      <x:c r="B22" s="84" t="str">
+      <x:c r="B22" s="109" t="str">
         <x:v>validation</x:v>
       </x:c>
-      <x:c r="C22" s="84" t="str">
+      <x:c r="C22" s="109" t="str">
         <x:v>Empatica continuous pulse rate</x:v>
       </x:c>
-      <x:c r="D22" s="84" t="str">
+      <x:c r="D22" s="109" t="str">
         <x:v>Multicenter evaluation reported clinical-grade continuous pulse-rate performance across motion and demographic subgroups</x:v>
       </x:c>
-      <x:c r="E22" s="84" t="str">
+      <x:c r="E22" s="109" t="str">
         <x:v>peer-reviewed validation study</x:v>
       </x:c>
-      <x:c r="F22" s="84" t="str">
+      <x:c r="F22" s="109" t="str">
         <x:v>https://pubmed.ncbi.nlm.nih.gov/39670276/</x:v>
       </x:c>
-      <x:c r="G22" s="84" t="str">
+      <x:c r="G22" s="109" t="str">
         <x:v>2024</x:v>
       </x:c>
-      <x:c r="H22" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I22" s="84" t="str">
+      <x:c r="H22" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I22" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J22" s="84" t="str">
+      <x:c r="J22" s="109" t="str">
         <x:v>Manufacturer conflicts disclosed</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="84" t="str">
+      <x:c r="A23" s="109" t="str">
         <x:v>VAL05</x:v>
       </x:c>
-      <x:c r="B23" s="84" t="str">
+      <x:c r="B23" s="109" t="str">
         <x:v>validation</x:v>
       </x:c>
-      <x:c r="C23" s="84" t="str">
+      <x:c r="C23" s="109" t="str">
         <x:v>Empatica and consumer PPG</x:v>
       </x:c>
-      <x:c r="D23" s="84" t="str">
+      <x:c r="D23" s="109" t="str">
         <x:v>Research-grade EmbracePlus did not uniformly outperform consumer devices across laboratory conditions</x:v>
       </x:c>
-      <x:c r="E23" s="84" t="str">
+      <x:c r="E23" s="109" t="str">
         <x:v>peer-reviewed comparative validation study</x:v>
       </x:c>
-      <x:c r="F23" s="84" t="str">
+      <x:c r="F23" s="109" t="str">
         <x:v>https://pubmed.ncbi.nlm.nih.gov/39905563/</x:v>
       </x:c>
-      <x:c r="G23" s="84" t="str">
+      <x:c r="G23" s="109" t="str">
         <x:v>2025</x:v>
       </x:c>
-      <x:c r="H23" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I23" s="84" t="str">
+      <x:c r="H23" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I23" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J23" s="84" t="str">
+      <x:c r="J23" s="109" t="str">
         <x:v>Device grade does not replace use-case validation</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="84" t="str">
+      <x:c r="A24" s="109" t="str">
         <x:v>VAL06</x:v>
       </x:c>
-      <x:c r="B24" s="84" t="str">
+      <x:c r="B24" s="109" t="str">
         <x:v>validation</x:v>
       </x:c>
-      <x:c r="C24" s="84" t="str">
+      <x:c r="C24" s="109" t="str">
         <x:v>BioButton hospital monitoring</x:v>
       </x:c>
-      <x:c r="D24" s="84" t="str">
+      <x:c r="D24" s="109" t="str">
         <x:v>BioButton supported high-frequency trend monitoring in 11977 patient encounters</x:v>
       </x:c>
-      <x:c r="E24" s="84" t="str">
+      <x:c r="E24" s="109" t="str">
         <x:v>peer-reviewed retrospective observational study</x:v>
       </x:c>
-      <x:c r="F24" s="84" t="str">
+      <x:c r="F24" s="109" t="str">
         <x:v>https://pubmed.ncbi.nlm.nih.gov/39200889/</x:v>
       </x:c>
-      <x:c r="G24" s="84" t="str">
+      <x:c r="G24" s="109" t="str">
         <x:v>2024</x:v>
       </x:c>
-      <x:c r="H24" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I24" s="84" t="str">
+      <x:c r="H24" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I24" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J24" s="84" t="str">
+      <x:c r="J24" s="109" t="str">
         <x:v>HR and RR are rest measures; manufacturer conflicts disclosed</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="84" t="str">
+      <x:c r="A25" s="109" t="str">
         <x:v>VAL07</x:v>
       </x:c>
-      <x:c r="B25" s="84" t="str">
+      <x:c r="B25" s="109" t="str">
         <x:v>validation</x:v>
       </x:c>
-      <x:c r="C25" s="84" t="str">
+      <x:c r="C25" s="109" t="str">
         <x:v>VitalPatch under motion and hypoxia</x:v>
       </x:c>
-      <x:c r="D25" s="84" t="str">
+      <x:c r="D25" s="109" t="str">
         <x:v>VitalPatch HR met the prespecified error limit; RR errors exceeded the limit for some movements</x:v>
       </x:c>
-      <x:c r="E25" s="84" t="str">
+      <x:c r="E25" s="109" t="str">
         <x:v>peer-reviewed controlled validation study</x:v>
       </x:c>
-      <x:c r="F25" s="84" t="str">
+      <x:c r="F25" s="109" t="str">
         <x:v>https://pubmed.ncbi.nlm.nih.gov/34524087/</x:v>
       </x:c>
-      <x:c r="G25" s="84" t="str">
+      <x:c r="G25" s="109" t="str">
         <x:v>2021</x:v>
       </x:c>
-      <x:c r="H25" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I25" s="84" t="str">
+      <x:c r="H25" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I25" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J25" s="84" t="str">
+      <x:c r="J25" s="109" t="str">
         <x:v>Healthy controlled protocol</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="84" t="str">
+      <x:c r="A26" s="109" t="str">
         <x:v>VAL08</x:v>
       </x:c>
-      <x:c r="B26" s="84" t="str">
+      <x:c r="B26" s="109" t="str">
         <x:v>validation</x:v>
       </x:c>
-      <x:c r="C26" s="84" t="str">
+      <x:c r="C26" s="109" t="str">
         <x:v>VitalPatch sensor performance</x:v>
       </x:c>
-      <x:c r="D26" s="84" t="str">
+      <x:c r="D26" s="109" t="str">
         <x:v>Bench and laboratory testing reported ECG, HR, breathing-rate, temperature, posture, step, and fall-detection performance</x:v>
       </x:c>
-      <x:c r="E26" s="84" t="str">
+      <x:c r="E26" s="109" t="str">
         <x:v>peer-reviewed device validation study</x:v>
       </x:c>
-      <x:c r="F26" s="84" t="str">
+      <x:c r="F26" s="109" t="str">
         <x:v>https://pubmed.ncbi.nlm.nih.gov/30440706/</x:v>
       </x:c>
-      <x:c r="G26" s="84" t="str">
+      <x:c r="G26" s="109" t="str">
         <x:v>2018</x:v>
       </x:c>
-      <x:c r="H26" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I26" s="84" t="str">
+      <x:c r="H26" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I26" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J26" s="84" t="str">
+      <x:c r="J26" s="109" t="str">
         <x:v>Stationary and laboratory conditions</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" s="84" t="str">
+      <x:c r="A27" s="109" t="str">
         <x:v>VAL09</x:v>
       </x:c>
-      <x:c r="B27" s="84" t="str">
+      <x:c r="B27" s="109" t="str">
         <x:v>validation</x:v>
       </x:c>
-      <x:c r="C27" s="84" t="str">
+      <x:c r="C27" s="109" t="str">
         <x:v>ActiGraph LEAP activity</x:v>
       </x:c>
-      <x:c r="D27" s="84" t="str">
+      <x:c r="D27" s="109" t="str">
         <x:v>LEAP activity measurements showed acceptable-to-excellent agreement with GT9X Link over seven days</x:v>
       </x:c>
-      <x:c r="E27" s="84" t="str">
+      <x:c r="E27" s="109" t="str">
         <x:v>peer-reviewed concurrent-validation study</x:v>
       </x:c>
-      <x:c r="F27" s="84" t="str">
+      <x:c r="F27" s="109" t="str">
         <x:v>https://pubmed.ncbi.nlm.nih.gov/41716605/</x:v>
       </x:c>
-      <x:c r="G27" s="84" t="str">
+      <x:c r="G27" s="109" t="str">
         <x:v>2026</x:v>
       </x:c>
-      <x:c r="H27" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I27" s="84" t="str">
+      <x:c r="H27" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I27" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J27" s="84" t="str">
+      <x:c r="J27" s="109" t="str">
         <x:v>Validates activity, not acute PPG or presyncope</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="84" t="str">
+      <x:c r="A28" s="109" t="str">
         <x:v>VAL10</x:v>
       </x:c>
-      <x:c r="B28" s="84" t="str">
+      <x:c r="B28" s="109" t="str">
         <x:v>validation</x:v>
       </x:c>
-      <x:c r="C28" s="84" t="str">
+      <x:c r="C28" s="109" t="str">
         <x:v>Biostrap raw PPG</x:v>
       </x:c>
-      <x:c r="D28" s="84" t="str">
+      <x:c r="D28" s="109" t="str">
         <x:v>Biostrap raw PPG was used for longitudinal peripheral vasoconstriction biomarkers</x:v>
       </x:c>
-      <x:c r="E28" s="84" t="str">
+      <x:c r="E28" s="109" t="str">
         <x:v>peer-reviewed feasibility and validation study</x:v>
       </x:c>
-      <x:c r="F28" s="84" t="str">
+      <x:c r="F28" s="109" t="str">
         <x:v>https://pubmed.ncbi.nlm.nih.gov/41494152/</x:v>
       </x:c>
-      <x:c r="G28" s="84" t="str">
+      <x:c r="G28" s="109" t="str">
         <x:v>2025</x:v>
       </x:c>
-      <x:c r="H28" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I28" s="84" t="str">
+      <x:c r="H28" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I28" s="109" t="str">
         <x:v>medium</x:v>
       </x:c>
-      <x:c r="J28" s="84" t="str">
+      <x:c r="J28" s="109" t="str">
         <x:v>Small sickle-cell cohort; not VVS</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
-      <x:c r="A29" s="84" t="str">
+      <x:c r="A29" s="109" t="str">
         <x:v>VAL11</x:v>
       </x:c>
-      <x:c r="B29" s="84" t="str">
+      <x:c r="B29" s="109" t="str">
         <x:v>validation</x:v>
       </x:c>
-      <x:c r="C29" s="84" t="str">
+      <x:c r="C29" s="109" t="str">
         <x:v>Masimo W1 ECG</x:v>
       </x:c>
-      <x:c r="D29" s="84" t="str">
+      <x:c r="D29" s="109" t="str">
         <x:v>Spot-check W1 ECG showed high AF and normal-rhythm classification performance against 12-lead ECG</x:v>
       </x:c>
-      <x:c r="E29" s="84" t="str">
+      <x:c r="E29" s="109" t="str">
         <x:v>peer-reviewed prospective diagnostic study</x:v>
       </x:c>
-      <x:c r="F29" s="84" t="str">
+      <x:c r="F29" s="109" t="str">
         <x:v>https://pubmed.ncbi.nlm.nih.gov/42038677/</x:v>
       </x:c>
-      <x:c r="G29" s="84" t="str">
+      <x:c r="G29" s="109" t="str">
         <x:v>2026</x:v>
       </x:c>
-      <x:c r="H29" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I29" s="84" t="str">
+      <x:c r="H29" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I29" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J29" s="84" t="str">
+      <x:c r="J29" s="109" t="str">
         <x:v>Rhythm classification is not presyncope prediction</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
-      <x:c r="A30" s="84" t="str">
+      <x:c r="A30" s="109" t="str">
         <x:v>VAL12</x:v>
       </x:c>
-      <x:c r="B30" s="84" t="str">
+      <x:c r="B30" s="109" t="str">
         <x:v>validation</x:v>
       </x:c>
-      <x:c r="C30" s="84" t="str">
+      <x:c r="C30" s="109" t="str">
         <x:v>Short-term PPG HRV</x:v>
       </x:c>
-      <x:c r="D30" s="84" t="str">
+      <x:c r="D30" s="109" t="str">
         <x:v>Selected wrist PPG HRV indices agreed with ECG under controlled rest but entropy and short-term metrics were weaker</x:v>
       </x:c>
-      <x:c r="E30" s="84" t="str">
+      <x:c r="E30" s="109" t="str">
         <x:v>peer-reviewed validation study</x:v>
       </x:c>
-      <x:c r="F30" s="84" t="str">
+      <x:c r="F30" s="109" t="str">
         <x:v>https://pubmed.ncbi.nlm.nih.gov/42151374/</x:v>
       </x:c>
-      <x:c r="G30" s="84" t="str">
+      <x:c r="G30" s="109" t="str">
         <x:v>2026</x:v>
       </x:c>
-      <x:c r="H30" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I30" s="84" t="str">
+      <x:c r="H30" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I30" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J30" s="84" t="str">
+      <x:c r="J30" s="109" t="str">
         <x:v>Reinforces metric-specific validation</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
-      <x:c r="A31" s="84" t="str">
+      <x:c r="A31" s="109" t="str">
         <x:v>REG01</x:v>
       </x:c>
-      <x:c r="B31" s="84" t="str">
+      <x:c r="B31" s="109" t="str">
         <x:v>regulatory</x:v>
       </x:c>
-      <x:c r="C31" s="84" t="str">
+      <x:c r="C31" s="109" t="str">
         <x:v>Cuffless BP</x:v>
       </x:c>
-      <x:c r="D31" s="84" t="str">
+      <x:c r="D31" s="109" t="str">
         <x:v>FDA draft recommends clinical performance testing for cuffless non-invasive BP devices</x:v>
       </x:c>
-      <x:c r="E31" s="84" t="str">
+      <x:c r="E31" s="109" t="str">
         <x:v>FDA draft guidance</x:v>
       </x:c>
-      <x:c r="F31" s="84" t="str">
+      <x:c r="F31" s="109" t="str">
         <x:v>https://www.fda.gov/regulatory-information/search-fda-guidance-documents/cuffless-non-invasive-blood-pressure-measuring-devices-clinical-performance-testing-and-evaluation</x:v>
       </x:c>
-      <x:c r="G31" s="84" t="str">
+      <x:c r="G31" s="109" t="str">
         <x:v>2026-01</x:v>
       </x:c>
-      <x:c r="H31" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I31" s="84" t="str">
+      <x:c r="H31" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I31" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J31" s="84" t="str">
+      <x:c r="J31" s="109" t="str">
         <x:v>Draft and nonbinding; current regulatory thinking</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
-      <x:c r="A32" s="84" t="str">
+      <x:c r="A32" s="109" t="str">
         <x:v>REG02</x:v>
       </x:c>
-      <x:c r="B32" s="84" t="str">
+      <x:c r="B32" s="109" t="str">
         <x:v>regulatory</x:v>
       </x:c>
-      <x:c r="C32" s="84" t="str">
+      <x:c r="C32" s="109" t="str">
         <x:v>Continuous cuffless BP</x:v>
       </x:c>
-      <x:c r="D32" s="84" t="str">
+      <x:c r="D32" s="109" t="str">
         <x:v>Fast BP changes require a simultaneous continuous reference with appropriate time resolution</x:v>
       </x:c>
-      <x:c r="E32" s="84" t="str">
+      <x:c r="E32" s="109" t="str">
         <x:v>FDA recognized-standards note</x:v>
       </x:c>
-      <x:c r="F32" s="84" t="str">
+      <x:c r="F32" s="109" t="str">
         <x:v>https://www.accessdata.fda.gov/scripts/cdrh/cfdocs/cfstandards/detail.cfm?standard__identification_no=42370</x:v>
       </x:c>
-      <x:c r="G32" s="84" t="str">
+      <x:c r="G32" s="109" t="str">
         <x:v>current in 2026</x:v>
       </x:c>
-      <x:c r="H32" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I32" s="84" t="str">
+      <x:c r="H32" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I32" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J32" s="84" t="str">
+      <x:c r="J32" s="109" t="str">
         <x:v>FDA partially recognizes IEEE 1708-2014</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
-      <x:c r="A33" s="84" t="str">
+      <x:c r="A33" s="109" t="str">
         <x:v>REG03</x:v>
       </x:c>
-      <x:c r="B33" s="84" t="str">
+      <x:c r="B33" s="109" t="str">
         <x:v>regulatory</x:v>
       </x:c>
-      <x:c r="C33" s="84" t="str">
+      <x:c r="C33" s="109" t="str">
         <x:v>Pulse oximetry</x:v>
       </x:c>
-      <x:c r="D33" s="84" t="str">
+      <x:c r="D33" s="109" t="str">
         <x:v>Skin pigmentation and low perfusion can affect pulse-oximeter accuracy</x:v>
       </x:c>
-      <x:c r="E33" s="84" t="str">
+      <x:c r="E33" s="109" t="str">
         <x:v>FDA regulatory-science study</x:v>
       </x:c>
-      <x:c r="F33" s="84" t="str">
+      <x:c r="F33" s="109" t="str">
         <x:v>https://www.fda.gov/science-research/advancing-regulatory-science/prospective-clinical-study-pulse-oximeter-errors-adult-hospitalized-patients-varying-skin</x:v>
       </x:c>
-      <x:c r="G33" s="84" t="str">
+      <x:c r="G33" s="109" t="str">
         <x:v>current</x:v>
       </x:c>
-      <x:c r="H33" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I33" s="84" t="str">
+      <x:c r="H33" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I33" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J33" s="84" t="str">
+      <x:c r="J33" s="109" t="str">
         <x:v>Consumer wellness SpO2 is not automatically clinical grade</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
-      <x:c r="A34" s="84" t="str">
+      <x:c r="A34" s="109" t="str">
         <x:v>REG04</x:v>
       </x:c>
-      <x:c r="B34" s="84" t="str">
+      <x:c r="B34" s="109" t="str">
         <x:v>regulatory</x:v>
       </x:c>
-      <x:c r="C34" s="84" t="str">
+      <x:c r="C34" s="109" t="str">
         <x:v>Optical wearables</x:v>
       </x:c>
-      <x:c r="D34" s="84" t="str">
+      <x:c r="D34" s="109" t="str">
         <x:v>Melanin can affect biomedical optical devices including PPG wearables</x:v>
       </x:c>
-      <x:c r="E34" s="84" t="str">
+      <x:c r="E34" s="109" t="str">
         <x:v>FDA science forum</x:v>
       </x:c>
-      <x:c r="F34" s="84" t="str">
+      <x:c r="F34" s="109" t="str">
         <x:v>https://www.fda.gov/science-research/fda-science-forum/impact-skin-pigmentation-performance-biomedical-optics-devices</x:v>
       </x:c>
-      <x:c r="G34" s="84" t="str">
+      <x:c r="G34" s="109" t="str">
         <x:v>2023</x:v>
       </x:c>
-      <x:c r="H34" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I34" s="84" t="str">
+      <x:c r="H34" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I34" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J34" s="84" t="str">
+      <x:c r="J34" s="109" t="str">
         <x:v>Use objective pigmentation rather than race labels</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
-      <x:c r="A35" s="84" t="str">
+      <x:c r="A35" s="109" t="str">
         <x:v>APL01</x:v>
       </x:c>
-      <x:c r="B35" s="84" t="str">
+      <x:c r="B35" s="109" t="str">
         <x:v>product</x:v>
       </x:c>
-      <x:c r="C35" s="84" t="str">
+      <x:c r="C35" s="109" t="str">
         <x:v>Apple Watch Series 11</x:v>
       </x:c>
-      <x:c r="D35" s="84" t="str">
+      <x:c r="D35" s="109" t="str">
         <x:v>Electrical and optical heart sensors, blood oxygen, temperature, accelerometer, and gyroscope</x:v>
       </x:c>
-      <x:c r="E35" s="84" t="str">
+      <x:c r="E35" s="109" t="str">
         <x:v>official product specifications</x:v>
       </x:c>
-      <x:c r="F35" s="84" t="str">
+      <x:c r="F35" s="109" t="str">
         <x:v>https://www.apple.com/apple-watch-series-11/specs/</x:v>
       </x:c>
-      <x:c r="G35" s="84" t="str">
+      <x:c r="G35" s="109" t="str">
         <x:v>2025 model</x:v>
       </x:c>
-      <x:c r="H35" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I35" s="84" t="str">
+      <x:c r="H35" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I35" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J35" s="84" t="str">
+      <x:c r="J35" s="109" t="str">
         <x:v>Feature and region availability can vary</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
-      <x:c r="A36" s="84" t="str">
+      <x:c r="A36" s="109" t="str">
         <x:v>APL02</x:v>
       </x:c>
-      <x:c r="B36" s="84" t="str">
+      <x:c r="B36" s="109" t="str">
         <x:v>data</x:v>
       </x:c>
-      <x:c r="C36" s="84" t="str">
+      <x:c r="C36" s="109" t="str">
         <x:v>Apple Health</x:v>
       </x:c>
-      <x:c r="D36" s="84" t="str">
+      <x:c r="D36" s="109" t="str">
         <x:v>HealthKit provides authorized health-data types and application access</x:v>
       </x:c>
-      <x:c r="E36" s="84" t="str">
+      <x:c r="E36" s="109" t="str">
         <x:v>official developer documentation</x:v>
       </x:c>
-      <x:c r="F36" s="84" t="str">
+      <x:c r="F36" s="109" t="str">
         <x:v>https://developer.apple.com/documentation/healthkit</x:v>
       </x:c>
-      <x:c r="G36" s="84" t="str">
+      <x:c r="G36" s="109" t="str">
         <x:v>current</x:v>
       </x:c>
-      <x:c r="H36" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I36" s="84" t="str">
+      <x:c r="H36" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I36" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J36" s="84" t="str">
+      <x:c r="J36" s="109" t="str">
         <x:v>Does not imply raw PPG access</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
-      <x:c r="A37" s="84" t="str">
+      <x:c r="A37" s="109" t="str">
         <x:v>APL04</x:v>
       </x:c>
-      <x:c r="B37" s="84" t="str">
+      <x:c r="B37" s="109" t="str">
         <x:v>data</x:v>
       </x:c>
-      <x:c r="C37" s="84" t="str">
+      <x:c r="C37" s="109" t="str">
         <x:v>Apple Health</x:v>
       </x:c>
-      <x:c r="D37" s="84" t="str">
+      <x:c r="D37" s="109" t="str">
         <x:v>Users can export health and fitness data in XML</x:v>
       </x:c>
-      <x:c r="E37" s="84" t="str">
+      <x:c r="E37" s="109" t="str">
         <x:v>official support</x:v>
       </x:c>
-      <x:c r="F37" s="84" t="str">
+      <x:c r="F37" s="109" t="str">
         <x:v>https://support.apple.com/guide/iphone/share-your-health-data-iph5ede58c3d/26/ios/26</x:v>
       </x:c>
-      <x:c r="G37" s="84" t="str">
+      <x:c r="G37" s="109" t="str">
         <x:v>iOS 26</x:v>
       </x:c>
-      <x:c r="H37" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I37" s="84" t="str">
+      <x:c r="H37" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I37" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J37" s="84" t="str">
+      <x:c r="J37" s="109" t="str">
         <x:v>Manual historical export</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
-      <x:c r="A38" s="84" t="str">
+      <x:c r="A38" s="109" t="str">
         <x:v>APL05</x:v>
       </x:c>
-      <x:c r="B38" s="84" t="str">
+      <x:c r="B38" s="109" t="str">
         <x:v>product</x:v>
       </x:c>
-      <x:c r="C38" s="84" t="str">
+      <x:c r="C38" s="109" t="str">
         <x:v>Apple hypertension notifications</x:v>
       </x:c>
-      <x:c r="D38" s="84" t="str">
+      <x:c r="D38" s="109" t="str">
         <x:v>Feature analyzes optical-heart patterns over approximately 30 days and is not a BP measurement</x:v>
       </x:c>
-      <x:c r="E38" s="84" t="str">
+      <x:c r="E38" s="109" t="str">
         <x:v>official support</x:v>
       </x:c>
-      <x:c r="F38" s="84" t="str">
+      <x:c r="F38" s="109" t="str">
         <x:v>https://support.apple.com/en-ie/117296</x:v>
       </x:c>
-      <x:c r="G38" s="84" t="str">
+      <x:c r="G38" s="109" t="str">
         <x:v>current</x:v>
       </x:c>
-      <x:c r="H38" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I38" s="84" t="str">
+      <x:c r="H38" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I38" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J38" s="84" t="str">
+      <x:c r="J38" s="109" t="str">
         <x:v>Not an acute BP stream</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
-      <x:c r="A39" s="84" t="str">
+      <x:c r="A39" s="109" t="str">
         <x:v>ACT01</x:v>
       </x:c>
-      <x:c r="B39" s="84" t="str">
+      <x:c r="B39" s="109" t="str">
         <x:v>product</x:v>
       </x:c>
-      <x:c r="C39" s="84" t="str">
+      <x:c r="C39" s="109" t="str">
         <x:v>ActiGraph LEAP</x:v>
       </x:c>
-      <x:c r="D39" s="84" t="str">
+      <x:c r="D39" s="109" t="str">
         <x:v>Multiwavelength PPG, accelerometer, gyroscope, skin temperature, barometer, long storage, and listed vital-sign measures</x:v>
       </x:c>
-      <x:c r="E39" s="84" t="str">
+      <x:c r="E39" s="109" t="str">
         <x:v>official product page</x:v>
       </x:c>
-      <x:c r="F39" s="84" t="str">
+      <x:c r="F39" s="109" t="str">
         <x:v>https://theactigraph.com/actigraph-leap</x:v>
       </x:c>
-      <x:c r="G39" s="84" t="str">
+      <x:c r="G39" s="109" t="str">
         <x:v>current</x:v>
       </x:c>
-      <x:c r="H39" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I39" s="84" t="str">
+      <x:c r="H39" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I39" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J39" s="84" t="str">
+      <x:c r="J39" s="109" t="str">
         <x:v>Some measures require scientific services; upper-arm BP is not a wrist signal</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
-      <x:c r="A40" s="84" t="str">
+      <x:c r="A40" s="109" t="str">
         <x:v>ACT02</x:v>
       </x:c>
-      <x:c r="B40" s="84" t="str">
+      <x:c r="B40" s="109" t="str">
         <x:v>data</x:v>
       </x:c>
-      <x:c r="C40" s="84" t="str">
+      <x:c r="C40" s="109" t="str">
         <x:v>ActiGraph LEAP</x:v>
       </x:c>
-      <x:c r="D40" s="84" t="str">
+      <x:c r="D40" s="109" t="str">
         <x:v>Raw data are available through CentrePoint and the Data Access API after transfer</x:v>
       </x:c>
-      <x:c r="E40" s="84" t="str">
+      <x:c r="E40" s="109" t="str">
         <x:v>official FAQ</x:v>
       </x:c>
-      <x:c r="F40" s="84" t="str">
+      <x:c r="F40" s="109" t="str">
         <x:v>https://blog.theactigraph.com/blog/leap-faq</x:v>
       </x:c>
-      <x:c r="G40" s="84" t="str">
+      <x:c r="G40" s="109" t="str">
         <x:v>current</x:v>
       </x:c>
-      <x:c r="H40" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I40" s="84" t="str">
+      <x:c r="H40" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I40" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J40" s="84" t="str">
+      <x:c r="J40" s="109" t="str">
         <x:v>Public material does not establish subsecond live latency</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
-      <x:c r="A41" s="84" t="str">
+      <x:c r="A41" s="109" t="str">
         <x:v>BIO01</x:v>
       </x:c>
-      <x:c r="B41" s="84" t="str">
+      <x:c r="B41" s="109" t="str">
         <x:v>product</x:v>
       </x:c>
-      <x:c r="C41" s="84" t="str">
+      <x:c r="C41" s="109" t="str">
         <x:v>Biostrap Kairos</x:v>
       </x:c>
-      <x:c r="D41" s="84" t="str">
+      <x:c r="D41" s="109" t="str">
         <x:v>Kairos provides HR, HRV, IBI, respiration, activity, and a research-oriented optical sensor</x:v>
       </x:c>
-      <x:c r="E41" s="84" t="str">
+      <x:c r="E41" s="109" t="str">
         <x:v>official product page</x:v>
       </x:c>
-      <x:c r="F41" s="84" t="str">
+      <x:c r="F41" s="109" t="str">
         <x:v>https://biostrap.com/</x:v>
       </x:c>
-      <x:c r="G41" s="84" t="str">
+      <x:c r="G41" s="109" t="str">
         <x:v>current</x:v>
       </x:c>
-      <x:c r="H41" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I41" s="84" t="str">
+      <x:c r="H41" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I41" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J41" s="84" t="str">
+      <x:c r="J41" s="109" t="str">
         <x:v>Current page does not list EDA, ECG, BP, or skin temperature</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
-      <x:c r="A42" s="84" t="str">
+      <x:c r="A42" s="109" t="str">
         <x:v>BIO02</x:v>
       </x:c>
-      <x:c r="B42" s="84" t="str">
+      <x:c r="B42" s="109" t="str">
         <x:v>data</x:v>
       </x:c>
-      <x:c r="C42" s="84" t="str">
+      <x:c r="C42" s="109" t="str">
         <x:v>Biostrap research platform</x:v>
       </x:c>
-      <x:c r="D42" s="84" t="str">
+      <x:c r="D42" s="109" t="str">
         <x:v>Researchers can access raw and processed PPG, gyroscope, and accelerometer data</x:v>
       </x:c>
-      <x:c r="E42" s="84" t="str">
+      <x:c r="E42" s="109" t="str">
         <x:v>official science page</x:v>
       </x:c>
-      <x:c r="F42" s="84" t="str">
+      <x:c r="F42" s="109" t="str">
         <x:v>https://biostrap.com/science/</x:v>
       </x:c>
-      <x:c r="G42" s="84" t="str">
+      <x:c r="G42" s="109" t="str">
         <x:v>current</x:v>
       </x:c>
-      <x:c r="H42" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I42" s="84" t="str">
+      <x:c r="H42" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I42" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J42" s="84" t="str">
+      <x:c r="J42" s="109" t="str">
         <x:v>Sampling configuration and latency require contract confirmation</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
-      <x:c r="A43" s="84" t="str">
+      <x:c r="A43" s="109" t="str">
         <x:v>BIO03</x:v>
       </x:c>
-      <x:c r="B43" s="84" t="str">
+      <x:c r="B43" s="109" t="str">
         <x:v>data</x:v>
       </x:c>
-      <x:c r="C43" s="84" t="str">
+      <x:c r="C43" s="109" t="str">
         <x:v>Biostrap RPM</x:v>
       </x:c>
-      <x:c r="D43" s="84" t="str">
+      <x:c r="D43" s="109" t="str">
         <x:v>Live dashboard, research mode, SDK, API, and raw or processed data pathways are offered</x:v>
       </x:c>
-      <x:c r="E43" s="84" t="str">
+      <x:c r="E43" s="109" t="str">
         <x:v>official platform page</x:v>
       </x:c>
-      <x:c r="F43" s="84" t="str">
+      <x:c r="F43" s="109" t="str">
         <x:v>https://biostrap.com/rpm/</x:v>
       </x:c>
-      <x:c r="G43" s="84" t="str">
+      <x:c r="G43" s="109" t="str">
         <x:v>current</x:v>
       </x:c>
-      <x:c r="H43" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I43" s="84" t="str">
+      <x:c r="H43" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I43" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J43" s="84" t="str">
+      <x:c r="J43" s="109" t="str">
         <x:v>Commercial terms and exact live semantics require diligence</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
-      <x:c r="A44" s="84" t="str">
+      <x:c r="A44" s="109" t="str">
         <x:v>VIT01</x:v>
       </x:c>
-      <x:c r="B44" s="84" t="str">
+      <x:c r="B44" s="109" t="str">
         <x:v>product</x:v>
       </x:c>
-      <x:c r="C44" s="84" t="str">
+      <x:c r="C44" s="109" t="str">
         <x:v>VitalPatch RTM</x:v>
       </x:c>
-      <x:c r="D44" s="84" t="str">
+      <x:c r="D44" s="109" t="str">
         <x:v>Continuous ECG, HR, HRV, R-R, respiration, skin/body temperature, activity, posture, and fall data</x:v>
       </x:c>
-      <x:c r="E44" s="84" t="str">
+      <x:c r="E44" s="109" t="str">
         <x:v>official instructions for use</x:v>
       </x:c>
-      <x:c r="F44" s="84" t="str">
+      <x:c r="F44" s="109" t="str">
         <x:v>https://vitalconnect.com/docs/ifu006/RevAC/IFU-06_RevAC_VitalPatch_InstructionsforUse%28final%29.pdf</x:v>
       </x:c>
-      <x:c r="G44" s="84" t="str">
+      <x:c r="G44" s="109" t="str">
         <x:v>2025-10</x:v>
       </x:c>
-      <x:c r="H44" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I44" s="84" t="str">
+      <x:c r="H44" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I44" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J44" s="84" t="str">
+      <x:c r="J44" s="109" t="str">
         <x:v>General-care adjunct monitor; not a standalone diagnostic or critical-care device</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
-      <x:c r="A45" s="84" t="str">
+      <x:c r="A45" s="109" t="str">
         <x:v>VIT02</x:v>
       </x:c>
-      <x:c r="B45" s="84" t="str">
+      <x:c r="B45" s="109" t="str">
         <x:v>data</x:v>
       </x:c>
-      <x:c r="C45" s="84" t="str">
+      <x:c r="C45" s="109" t="str">
         <x:v>VitalConnect platform</x:v>
       </x:c>
-      <x:c r="D45" s="84" t="str">
+      <x:c r="D45" s="109" t="str">
         <x:v>VitalPatch data can flow through Relay Software Library APIs and VistaCenter supports live and historical ECG and CSV</x:v>
       </x:c>
-      <x:c r="E45" s="84" t="str">
+      <x:c r="E45" s="109" t="str">
         <x:v>official platform instructions</x:v>
       </x:c>
-      <x:c r="F45" s="84" t="str">
+      <x:c r="F45" s="109" t="str">
         <x:v>https://vitalconnect.com/docs/ifu027/RevY/IFU-27_RevY_VistaCenter_3.5.3%28final%29.pdf</x:v>
       </x:c>
-      <x:c r="G45" s="84" t="str">
+      <x:c r="G45" s="109" t="str">
         <x:v>2026-01</x:v>
       </x:c>
-      <x:c r="H45" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I45" s="84" t="str">
+      <x:c r="H45" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I45" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J45" s="84" t="str">
+      <x:c r="J45" s="109" t="str">
         <x:v>Exact contracted channels vary</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
-      <x:c r="A46" s="84" t="str">
+      <x:c r="A46" s="109" t="str">
         <x:v>GOO01</x:v>
       </x:c>
-      <x:c r="B46" s="84" t="str">
+      <x:c r="B46" s="109" t="str">
         <x:v>product</x:v>
       </x:c>
-      <x:c r="C46" s="84" t="str">
+      <x:c r="C46" s="109" t="str">
         <x:v>Google Pixel Watch 4</x:v>
       </x:c>
-      <x:c r="D46" s="84" t="str">
+      <x:c r="D46" s="109" t="str">
         <x:v>ECG electrodes, optical HR, accelerometer, gyroscope, cEDA, and temperature sensors</x:v>
       </x:c>
-      <x:c r="E46" s="84" t="str">
+      <x:c r="E46" s="109" t="str">
         <x:v>official support</x:v>
       </x:c>
-      <x:c r="F46" s="84" t="str">
+      <x:c r="F46" s="109" t="str">
         <x:v>https://support.google.com/googlepixelwatch/answer/12651869?hl=en-154</x:v>
       </x:c>
-      <x:c r="G46" s="84" t="str">
+      <x:c r="G46" s="109" t="str">
         <x:v>current model</x:v>
       </x:c>
-      <x:c r="H46" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I46" s="84" t="str">
+      <x:c r="H46" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I46" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J46" s="84" t="str">
+      <x:c r="J46" s="109" t="str">
         <x:v>Hardware does not imply raw API access</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
-      <x:c r="A47" s="84" t="str">
+      <x:c r="A47" s="109" t="str">
         <x:v>GOO03</x:v>
       </x:c>
-      <x:c r="B47" s="84" t="str">
+      <x:c r="B47" s="109" t="str">
         <x:v>data</x:v>
       </x:c>
-      <x:c r="C47" s="84" t="str">
+      <x:c r="C47" s="109" t="str">
         <x:v>Wear OS Health Services</x:v>
       </x:c>
-      <x:c r="D47" s="84" t="str">
+      <x:c r="D47" s="109" t="str">
         <x:v>Exercise HR is approximately one sample per second and passive monitoring may be batched</x:v>
       </x:c>
-      <x:c r="E47" s="84" t="str">
+      <x:c r="E47" s="109" t="str">
         <x:v>official developer documentation</x:v>
       </x:c>
-      <x:c r="F47" s="84" t="str">
+      <x:c r="F47" s="109" t="str">
         <x:v>https://developer.android.com/health-and-fitness/health-services/compatibility?authuser=09</x:v>
       </x:c>
-      <x:c r="G47" s="84" t="str">
+      <x:c r="G47" s="109" t="str">
         <x:v>updated 2026</x:v>
       </x:c>
-      <x:c r="H47" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I47" s="84" t="str">
+      <x:c r="H47" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I47" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J47" s="84" t="str">
+      <x:c r="J47" s="109" t="str">
         <x:v>Processed HR rather than raw PPG</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
-      <x:c r="A48" s="84" t="str">
+      <x:c r="A48" s="109" t="str">
         <x:v>GOO04</x:v>
       </x:c>
-      <x:c r="B48" s="84" t="str">
+      <x:c r="B48" s="109" t="str">
         <x:v>data</x:v>
       </x:c>
-      <x:c r="C48" s="84" t="str">
+      <x:c r="C48" s="109" t="str">
         <x:v>Fitbit Web API</x:v>
       </x:c>
-      <x:c r="D48" s="84" t="str">
+      <x:c r="D48" s="109" t="str">
         <x:v>Intraday HR supports one-second or one-minute detail with access restrictions</x:v>
       </x:c>
-      <x:c r="E48" s="84" t="str">
+      <x:c r="E48" s="109" t="str">
         <x:v>official developer documentation</x:v>
       </x:c>
-      <x:c r="F48" s="84" t="str">
+      <x:c r="F48" s="109" t="str">
         <x:v>https://dev.fitbit.com/build/reference/web-api/intraday/get-heartrate-intraday-by-date-range/</x:v>
       </x:c>
-      <x:c r="G48" s="84" t="str">
+      <x:c r="G48" s="109" t="str">
         <x:v>current</x:v>
       </x:c>
-      <x:c r="H48" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I48" s="84" t="str">
+      <x:c r="H48" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I48" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J48" s="84" t="str">
+      <x:c r="J48" s="109" t="str">
         <x:v>Third-party access to other users requires approval</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
-      <x:c r="A49" s="84" t="str">
+      <x:c r="A49" s="109" t="str">
         <x:v>FIT01</x:v>
       </x:c>
-      <x:c r="B49" s="84" t="str">
+      <x:c r="B49" s="109" t="str">
         <x:v>product</x:v>
       </x:c>
-      <x:c r="C49" s="84" t="str">
+      <x:c r="C49" s="109" t="str">
         <x:v>Fitbit Sense 2</x:v>
       </x:c>
-      <x:c r="D49" s="84" t="str">
+      <x:c r="D49" s="109" t="str">
         <x:v>Continuous EDA, ECG, HR, skin-temperature, and SpO2 features</x:v>
       </x:c>
-      <x:c r="E49" s="84" t="str">
+      <x:c r="E49" s="109" t="str">
         <x:v>official product page</x:v>
       </x:c>
-      <x:c r="F49" s="84" t="str">
+      <x:c r="F49" s="109" t="str">
         <x:v>https://store.google.com/product/fitbit_sense_2?hl=en-US</x:v>
       </x:c>
-      <x:c r="G49" s="84" t="str">
+      <x:c r="G49" s="109" t="str">
         <x:v>current</x:v>
       </x:c>
-      <x:c r="H49" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I49" s="84" t="str">
+      <x:c r="H49" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I49" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J49" s="84" t="str">
+      <x:c r="J49" s="109" t="str">
         <x:v>Several metrics are spot or sleep based</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
-      <x:c r="A50" s="84" t="str">
+      <x:c r="A50" s="109" t="str">
         <x:v>FIT03</x:v>
       </x:c>
-      <x:c r="B50" s="84" t="str">
+      <x:c r="B50" s="109" t="str">
         <x:v>data</x:v>
       </x:c>
-      <x:c r="C50" s="84" t="str">
+      <x:c r="C50" s="109" t="str">
         <x:v>Fitbit</x:v>
       </x:c>
-      <x:c r="D50" s="84" t="str">
+      <x:c r="D50" s="109" t="str">
         <x:v>Account archive and recent-data export include HR and activity</x:v>
       </x:c>
-      <x:c r="E50" s="84" t="str">
+      <x:c r="E50" s="109" t="str">
         <x:v>official support</x:v>
       </x:c>
-      <x:c r="F50" s="84" t="str">
+      <x:c r="F50" s="109" t="str">
         <x:v>https://support.google.com/googlehealth/answer/14236615?hl=en</x:v>
       </x:c>
-      <x:c r="G50" s="84" t="str">
+      <x:c r="G50" s="109" t="str">
         <x:v>current</x:v>
       </x:c>
-      <x:c r="H50" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I50" s="84" t="str">
+      <x:c r="H50" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I50" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J50" s="84" t="str">
+      <x:c r="J50" s="109" t="str">
         <x:v>Historical manual export</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
-      <x:c r="A51" s="84" t="str">
+      <x:c r="A51" s="109" t="str">
         <x:v>FIT04</x:v>
       </x:c>
-      <x:c r="B51" s="84" t="str">
+      <x:c r="B51" s="109" t="str">
         <x:v>data</x:v>
       </x:c>
-      <x:c r="C51" s="84" t="str">
+      <x:c r="C51" s="109" t="str">
         <x:v>Fitbit Web API</x:v>
       </x:c>
-      <x:c r="D51" s="84" t="str">
+      <x:c r="D51" s="109" t="str">
         <x:v>Processed health endpoints include intraday HR and ECG-related records</x:v>
       </x:c>
-      <x:c r="E51" s="84" t="str">
+      <x:c r="E51" s="109" t="str">
         <x:v>official developer documentation</x:v>
       </x:c>
-      <x:c r="F51" s="84" t="str">
+      <x:c r="F51" s="109" t="str">
         <x:v>https://dev.fitbit.com/build/reference/web-api/explore/</x:v>
       </x:c>
-      <x:c r="G51" s="84" t="str">
+      <x:c r="G51" s="109" t="str">
         <x:v>current</x:v>
       </x:c>
-      <x:c r="H51" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I51" s="84" t="str">
+      <x:c r="H51" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I51" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J51" s="84" t="str">
+      <x:c r="J51" s="109" t="str">
         <x:v>Access scopes and review apply</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
-      <x:c r="A52" s="84" t="str">
+      <x:c r="A52" s="109" t="str">
         <x:v>GAR01</x:v>
       </x:c>
-      <x:c r="B52" s="84" t="str">
+      <x:c r="B52" s="109" t="str">
         <x:v>product</x:v>
       </x:c>
-      <x:c r="C52" s="84" t="str">
+      <x:c r="C52" s="109" t="str">
         <x:v>Garmin Venu 4</x:v>
       </x:c>
-      <x:c r="D52" s="84" t="str">
+      <x:c r="D52" s="109" t="str">
         <x:v>HR, HRV, respiration, temperature, Pulse Ox, and ECG features</x:v>
       </x:c>
-      <x:c r="E52" s="84" t="str">
+      <x:c r="E52" s="109" t="str">
         <x:v>official newsroom</x:v>
       </x:c>
-      <x:c r="F52" s="84" t="str">
+      <x:c r="F52" s="109" t="str">
         <x:v>https://www.garmin.com/en-US/newsroom/press-release/sports-fitness/take-steps-towards-a-healthier-lifestyle-with-the-venu-4-from-garmin/</x:v>
       </x:c>
-      <x:c r="G52" s="84" t="str">
+      <x:c r="G52" s="109" t="str">
         <x:v>2025 model</x:v>
       </x:c>
-      <x:c r="H52" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I52" s="84" t="str">
+      <x:c r="H52" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I52" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J52" s="84" t="str">
+      <x:c r="J52" s="109" t="str">
         <x:v>ECG and Pulse Ox availability vary</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
-      <x:c r="A53" s="84" t="str">
+      <x:c r="A53" s="109" t="str">
         <x:v>GAR03</x:v>
       </x:c>
-      <x:c r="B53" s="84" t="str">
+      <x:c r="B53" s="109" t="str">
         <x:v>data</x:v>
       </x:c>
-      <x:c r="C53" s="84" t="str">
+      <x:c r="C53" s="109" t="str">
         <x:v>Garmin Health SDK</x:v>
       </x:c>
-      <x:c r="D53" s="84" t="str">
+      <x:c r="D53" s="109" t="str">
         <x:v>Real-time HR, beat-to-beat, accelerometer, Pulse Ox, respiration, and other processed streams</x:v>
       </x:c>
-      <x:c r="E53" s="84" t="str">
+      <x:c r="E53" s="109" t="str">
         <x:v>official developer documentation</x:v>
       </x:c>
-      <x:c r="F53" s="84" t="str">
+      <x:c r="F53" s="109" t="str">
         <x:v>https://developer.garmin.com/health-sdk/</x:v>
       </x:c>
-      <x:c r="G53" s="84" t="str">
+      <x:c r="G53" s="109" t="str">
         <x:v>current</x:v>
       </x:c>
-      <x:c r="H53" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I53" s="84" t="str">
+      <x:c r="H53" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I53" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J53" s="84" t="str">
+      <x:c r="J53" s="109" t="str">
         <x:v>Enterprise partner and license conditions</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
-      <x:c r="A54" s="84" t="str">
+      <x:c r="A54" s="109" t="str">
         <x:v>GAR04</x:v>
       </x:c>
-      <x:c r="B54" s="84" t="str">
+      <x:c r="B54" s="109" t="str">
         <x:v>data</x:v>
       </x:c>
-      <x:c r="C54" s="84" t="str">
+      <x:c r="C54" s="109" t="str">
         <x:v>Garmin Health API</x:v>
       </x:c>
-      <x:c r="D54" s="84" t="str">
+      <x:c r="D54" s="109" t="str">
         <x:v>Cloud JSON access to heart, stress, Pulse Ox, respiration, and beat-to-beat summaries</x:v>
       </x:c>
-      <x:c r="E54" s="84" t="str">
+      <x:c r="E54" s="109" t="str">
         <x:v>official developer documentation</x:v>
       </x:c>
-      <x:c r="F54" s="84" t="str">
+      <x:c r="F54" s="109" t="str">
         <x:v>https://developer.garmin.com/gc-developer-program/health-api/</x:v>
       </x:c>
-      <x:c r="G54" s="84" t="str">
+      <x:c r="G54" s="109" t="str">
         <x:v>current</x:v>
       </x:c>
-      <x:c r="H54" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I54" s="84" t="str">
+      <x:c r="H54" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I54" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J54" s="84" t="str">
+      <x:c r="J54" s="109" t="str">
         <x:v>Post-sync API and approval requirements</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
-      <x:c r="A55" s="84" t="str">
+      <x:c r="A55" s="109" t="str">
         <x:v>WHO01</x:v>
       </x:c>
-      <x:c r="B55" s="84" t="str">
+      <x:c r="B55" s="109" t="str">
         <x:v>product</x:v>
       </x:c>
-      <x:c r="C55" s="84" t="str">
+      <x:c r="C55" s="109" t="str">
         <x:v>WHOOP MG</x:v>
       </x:c>
-      <x:c r="D55" s="84" t="str">
+      <x:c r="D55" s="109" t="str">
         <x:v>24/7 HR and nightly HRV, RR, temperature, SpO2 plus on-demand ECG and BP insights</x:v>
       </x:c>
-      <x:c r="E55" s="84" t="str">
+      <x:c r="E55" s="109" t="str">
         <x:v>official support</x:v>
       </x:c>
-      <x:c r="F55" s="84" t="str">
+      <x:c r="F55" s="109" t="str">
         <x:v>https://support.whoop.com/s/article/Membership-Features-Benefits?language=en_US</x:v>
       </x:c>
-      <x:c r="G55" s="84" t="str">
+      <x:c r="G55" s="109" t="str">
         <x:v>current</x:v>
       </x:c>
-      <x:c r="H55" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I55" s="84" t="str">
+      <x:c r="H55" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I55" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J55" s="84" t="str">
+      <x:c r="J55" s="109" t="str">
         <x:v>BP is a daily resting cuff-calibrated estimate</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
-      <x:c r="A56" s="84" t="str">
+      <x:c r="A56" s="109" t="str">
         <x:v>WHO03</x:v>
       </x:c>
-      <x:c r="B56" s="84" t="str">
+      <x:c r="B56" s="109" t="str">
         <x:v>data</x:v>
       </x:c>
-      <x:c r="C56" s="84" t="str">
+      <x:c r="C56" s="109" t="str">
         <x:v>WHOOP</x:v>
       </x:c>
-      <x:c r="D56" s="84" t="str">
+      <x:c r="D56" s="109" t="str">
         <x:v>CSV account export includes member records</x:v>
       </x:c>
-      <x:c r="E56" s="84" t="str">
+      <x:c r="E56" s="109" t="str">
         <x:v>official support</x:v>
       </x:c>
-      <x:c r="F56" s="84" t="str">
+      <x:c r="F56" s="109" t="str">
         <x:v>https://support.whoop.com/s/article/How-to-Export-Your-Data</x:v>
       </x:c>
-      <x:c r="G56" s="84" t="str">
+      <x:c r="G56" s="109" t="str">
         <x:v>current</x:v>
       </x:c>
-      <x:c r="H56" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I56" s="84" t="str">
+      <x:c r="H56" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I56" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J56" s="84" t="str">
+      <x:c r="J56" s="109" t="str">
         <x:v>Not raw continuous optical data</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
-      <x:c r="A57" s="84" t="str">
+      <x:c r="A57" s="109" t="str">
         <x:v>WHO04</x:v>
       </x:c>
-      <x:c r="B57" s="84" t="str">
+      <x:c r="B57" s="109" t="str">
         <x:v>data</x:v>
       </x:c>
-      <x:c r="C57" s="84" t="str">
+      <x:c r="C57" s="109" t="str">
         <x:v>WHOOP API</x:v>
       </x:c>
-      <x:c r="D57" s="84" t="str">
+      <x:c r="D57" s="109" t="str">
         <x:v>Recovery, cycle, workout, and sleep API resources are available</x:v>
       </x:c>
-      <x:c r="E57" s="84" t="str">
+      <x:c r="E57" s="109" t="str">
         <x:v>official developer documentation</x:v>
       </x:c>
-      <x:c r="F57" s="84" t="str">
+      <x:c r="F57" s="109" t="str">
         <x:v>https://developer.whoop.com/api/</x:v>
       </x:c>
-      <x:c r="G57" s="84" t="str">
+      <x:c r="G57" s="109" t="str">
         <x:v>current</x:v>
       </x:c>
-      <x:c r="H57" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I57" s="84" t="str">
+      <x:c r="H57" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I57" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J57" s="84" t="str">
+      <x:c r="J57" s="109" t="str">
         <x:v>Primarily aggregate and post-sync</x:v>
       </x:c>
     </x:row>
     <x:row r="58">
-      <x:c r="A58" s="84" t="str">
+      <x:c r="A58" s="109" t="str">
         <x:v>BBT01</x:v>
       </x:c>
-      <x:c r="B58" s="84" t="str">
+      <x:c r="B58" s="109" t="str">
         <x:v>product</x:v>
       </x:c>
-      <x:c r="C58" s="84" t="str">
+      <x:c r="C58" s="109" t="str">
         <x:v>BioButton Rechargeable</x:v>
       </x:c>
-      <x:c r="D58" s="84" t="str">
+      <x:c r="D58" s="109" t="str">
         <x:v>Collects resting HR, resting RR, skin temperature, and activity</x:v>
       </x:c>
-      <x:c r="E58" s="84" t="str">
+      <x:c r="E58" s="109" t="str">
         <x:v>official solution page</x:v>
       </x:c>
-      <x:c r="F58" s="84" t="str">
+      <x:c r="F58" s="109" t="str">
         <x:v>https://www.biointellisense.com/solutions/at-home-patient-monitoring/</x:v>
       </x:c>
-      <x:c r="G58" s="84" t="str">
+      <x:c r="G58" s="109" t="str">
         <x:v>current</x:v>
       </x:c>
-      <x:c r="H58" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I58" s="84" t="str">
+      <x:c r="H58" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I58" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J58" s="84" t="str">
+      <x:c r="J58" s="109" t="str">
         <x:v>Not an acute raw waveform device</x:v>
       </x:c>
     </x:row>
     <x:row r="59">
-      <x:c r="A59" s="84" t="str">
+      <x:c r="A59" s="109" t="str">
         <x:v>BBT02</x:v>
       </x:c>
-      <x:c r="B59" s="84" t="str">
+      <x:c r="B59" s="109" t="str">
         <x:v>regulatory</x:v>
       </x:c>
-      <x:c r="C59" s="84" t="str">
+      <x:c r="C59" s="109" t="str">
         <x:v>BioButton Rechargeable</x:v>
       </x:c>
-      <x:c r="D59" s="84" t="str">
+      <x:c r="D59" s="109" t="str">
         <x:v>IFU states HR and RR are not output during motion or activity</x:v>
       </x:c>
-      <x:c r="E59" s="84" t="str">
+      <x:c r="E59" s="109" t="str">
         <x:v>official instructions for use</x:v>
       </x:c>
-      <x:c r="F59" s="84" t="str">
+      <x:c r="F59" s="109" t="str">
         <x:v>https://www.biointellisense.com/wp-content/uploads/2026/05/IFU-BBR-2022-Ver.6.pdf</x:v>
       </x:c>
-      <x:c r="G59" s="84" t="str">
+      <x:c r="G59" s="109" t="str">
         <x:v>2026-05</x:v>
       </x:c>
-      <x:c r="H59" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I59" s="84" t="str">
+      <x:c r="H59" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I59" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J59" s="84" t="str">
+      <x:c r="J59" s="109" t="str">
         <x:v>Important exclusion for acute workflow use</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
-      <x:c r="A60" s="84" t="str">
+      <x:c r="A60" s="109" t="str">
         <x:v>MAS01</x:v>
       </x:c>
-      <x:c r="B60" s="84" t="str">
+      <x:c r="B60" s="109" t="str">
         <x:v>product</x:v>
       </x:c>
-      <x:c r="C60" s="84" t="str">
+      <x:c r="C60" s="109" t="str">
         <x:v>Masimo W1 Medical</x:v>
       </x:c>
-      <x:c r="D60" s="84" t="str">
+      <x:c r="D60" s="109" t="str">
         <x:v>Continuous real-time SpO2, pulse rate, perfusion index, HR, steps, and approximately 24-hour operation</x:v>
       </x:c>
-      <x:c r="E60" s="84" t="str">
+      <x:c r="E60" s="109" t="str">
         <x:v>official product page</x:v>
       </x:c>
-      <x:c r="F60" s="84" t="str">
+      <x:c r="F60" s="109" t="str">
         <x:v>https://professional.masimo.com/products/monitors/masimo-w1-medical-watch/</x:v>
       </x:c>
-      <x:c r="G60" s="84" t="str">
+      <x:c r="G60" s="109" t="str">
         <x:v>current</x:v>
       </x:c>
-      <x:c r="H60" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I60" s="84" t="str">
+      <x:c r="H60" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I60" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J60" s="84" t="str">
+      <x:c r="J60" s="109" t="str">
         <x:v>No public raw PPG research interface</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
-      <x:c r="A61" s="84" t="str">
+      <x:c r="A61" s="109" t="str">
         <x:v>ZIO01</x:v>
       </x:c>
-      <x:c r="B61" s="84" t="str">
+      <x:c r="B61" s="109" t="str">
         <x:v>product</x:v>
       </x:c>
-      <x:c r="C61" s="84" t="str">
+      <x:c r="C61" s="109" t="str">
         <x:v>iRhythm Zio AT</x:v>
       </x:c>
-      <x:c r="D61" s="84" t="str">
+      <x:c r="D61" s="109" t="str">
         <x:v>Continuous long-term ECG recording with symptomatic and asymptomatic event transmissions</x:v>
       </x:c>
-      <x:c r="E61" s="84" t="str">
+      <x:c r="E61" s="109" t="str">
         <x:v>official clinical reference manual</x:v>
       </x:c>
-      <x:c r="F61" s="84" t="str">
+      <x:c r="F61" s="109" t="str">
         <x:v>https://www.irhythmtech.com/content/dam/irhythm/united-states/ifus/2026/february/ALB0031.16%20ZIO%20AT%20CLINICAL%20REFERENCE%20MANUAL%20LTE.pdf</x:v>
       </x:c>
-      <x:c r="G61" s="84" t="str">
+      <x:c r="G61" s="109" t="str">
         <x:v>2026-02</x:v>
       </x:c>
-      <x:c r="H61" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I61" s="84" t="str">
+      <x:c r="H61" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I61" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J61" s="84" t="str">
+      <x:c r="J61" s="109" t="str">
         <x:v>Clinical service rather than open raw research stream</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
-      <x:c r="A62" s="84" t="str">
+      <x:c r="A62" s="109" t="str">
         <x:v>ZIO02</x:v>
       </x:c>
-      <x:c r="B62" s="84" t="str">
+      <x:c r="B62" s="109" t="str">
         <x:v>product</x:v>
       </x:c>
-      <x:c r="C62" s="84" t="str">
+      <x:c r="C62" s="109" t="str">
         <x:v>iRhythm Zio AT</x:v>
       </x:c>
-      <x:c r="D62" s="84" t="str">
+      <x:c r="D62" s="109" t="str">
         <x:v>Wireless gateway sends ECG data for processing and clinical reporting</x:v>
       </x:c>
-      <x:c r="E62" s="84" t="str">
+      <x:c r="E62" s="109" t="str">
         <x:v>official product page</x:v>
       </x:c>
-      <x:c r="F62" s="84" t="str">
+      <x:c r="F62" s="109" t="str">
         <x:v>https://www.irhythmtech.com/products-services/zio-at</x:v>
       </x:c>
-      <x:c r="G62" s="84" t="str">
+      <x:c r="G62" s="109" t="str">
         <x:v>current</x:v>
       </x:c>
-      <x:c r="H62" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I62" s="84" t="str">
+      <x:c r="H62" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I62" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J62" s="84" t="str">
+      <x:c r="J62" s="109" t="str">
         <x:v>Not intended for critical-care monitoring</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
-      <x:c r="A63" s="84" t="str">
+      <x:c r="A63" s="109" t="str">
         <x:v>SAM02</x:v>
       </x:c>
-      <x:c r="B63" s="84" t="str">
+      <x:c r="B63" s="109" t="str">
         <x:v>data</x:v>
       </x:c>
-      <x:c r="C63" s="84" t="str">
+      <x:c r="C63" s="109" t="str">
         <x:v>Samsung Health Sensor SDK</x:v>
       </x:c>
-      <x:c r="D63" s="84" t="str">
+      <x:c r="D63" s="109" t="str">
         <x:v>Continuous and on-demand sensor modes include Watch8 EDA</x:v>
       </x:c>
-      <x:c r="E63" s="84" t="str">
+      <x:c r="E63" s="109" t="str">
         <x:v>official developer documentation</x:v>
       </x:c>
-      <x:c r="F63" s="84" t="str">
+      <x:c r="F63" s="109" t="str">
         <x:v>https://developer.samsung.com/health/sensor/guide/introduction.html</x:v>
       </x:c>
-      <x:c r="G63" s="84" t="str">
+      <x:c r="G63" s="109" t="str">
         <x:v>current</x:v>
       </x:c>
-      <x:c r="H63" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I63" s="84" t="str">
+      <x:c r="H63" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I63" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J63" s="84" t="str">
+      <x:c r="J63" s="109" t="str">
         <x:v>Distribution partner restrictions apply</x:v>
       </x:c>
     </x:row>
     <x:row r="64">
-      <x:c r="A64" s="84" t="str">
+      <x:c r="A64" s="109" t="str">
         <x:v>SAM03</x:v>
       </x:c>
-      <x:c r="B64" s="84" t="str">
+      <x:c r="B64" s="109" t="str">
         <x:v>data</x:v>
       </x:c>
-      <x:c r="C64" s="84" t="str">
+      <x:c r="C64" s="109" t="str">
         <x:v>Samsung Health Sensor SDK</x:v>
       </x:c>
-      <x:c r="D64" s="84" t="str">
+      <x:c r="D64" s="109" t="str">
         <x:v>ACC 25 Hz, EDA 1 Hz, HR and IBI 1 Hz, raw PPG 25 Hz; ECG and SpO2 on demand</x:v>
       </x:c>
-      <x:c r="E64" s="84" t="str">
+      <x:c r="E64" s="109" t="str">
         <x:v>official developer documentation</x:v>
       </x:c>
-      <x:c r="F64" s="84" t="str">
+      <x:c r="F64" s="109" t="str">
         <x:v>https://developer.samsung.com/health/sensor/guide/data-specifications.html</x:v>
       </x:c>
-      <x:c r="G64" s="84" t="str">
+      <x:c r="G64" s="109" t="str">
         <x:v>current</x:v>
       </x:c>
-      <x:c r="H64" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I64" s="84" t="str">
+      <x:c r="H64" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I64" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J64" s="84" t="str">
+      <x:c r="J64" s="109" t="str">
         <x:v>Check exact runtime capabilities</x:v>
       </x:c>
     </x:row>
     <x:row r="65">
-      <x:c r="A65" s="84" t="str">
+      <x:c r="A65" s="109" t="str">
         <x:v>SAM04</x:v>
       </x:c>
-      <x:c r="B65" s="84" t="str">
+      <x:c r="B65" s="109" t="str">
         <x:v>product</x:v>
       </x:c>
-      <x:c r="C65" s="84" t="str">
+      <x:c r="C65" s="109" t="str">
         <x:v>Samsung BP</x:v>
       </x:c>
-      <x:c r="D65" s="84" t="str">
+      <x:c r="D65" s="109" t="str">
         <x:v>BP uses cuff calibration and periodic recalibration</x:v>
       </x:c>
-      <x:c r="E65" s="84" t="str">
+      <x:c r="E65" s="109" t="str">
         <x:v>official newsroom</x:v>
       </x:c>
-      <x:c r="F65" s="84" t="str">
+      <x:c r="F65" s="109" t="str">
         <x:v>https://news.samsung.com/us/samsung-blood-pressure-monitoring-feature-available/</x:v>
       </x:c>
-      <x:c r="G65" s="84" t="str">
+      <x:c r="G65" s="109" t="str">
         <x:v>2026</x:v>
       </x:c>
-      <x:c r="H65" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I65" s="84" t="str">
+      <x:c r="H65" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I65" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J65" s="84" t="str">
+      <x:c r="J65" s="109" t="str">
         <x:v>Not continuous beat-to-beat BP</x:v>
       </x:c>
     </x:row>
     <x:row r="66">
-      <x:c r="A66" s="84" t="str">
+      <x:c r="A66" s="109" t="str">
         <x:v>EMP01</x:v>
       </x:c>
-      <x:c r="B66" s="84" t="str">
+      <x:c r="B66" s="109" t="str">
         <x:v>product</x:v>
       </x:c>
-      <x:c r="C66" s="84" t="str">
+      <x:c r="C66" s="109" t="str">
         <x:v>Empatica EmbracePlus</x:v>
       </x:c>
-      <x:c r="D66" s="84" t="str">
+      <x:c r="D66" s="109" t="str">
         <x:v>EDA, four-channel PPG, accelerometer, gyroscope, temperature, event buttons, and continuous recording</x:v>
       </x:c>
-      <x:c r="E66" s="84" t="str">
+      <x:c r="E66" s="109" t="str">
         <x:v>official product page</x:v>
       </x:c>
-      <x:c r="F66" s="84" t="str">
+      <x:c r="F66" s="109" t="str">
         <x:v>https://www.empatica.com/en-us/embraceplus/</x:v>
       </x:c>
-      <x:c r="G66" s="84" t="str">
+      <x:c r="G66" s="109" t="str">
         <x:v>current</x:v>
       </x:c>
-      <x:c r="H66" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I66" s="84" t="str">
+      <x:c r="H66" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I66" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J66" s="84" t="str">
+      <x:c r="J66" s="109" t="str">
         <x:v>Research and medical platform</x:v>
       </x:c>
     </x:row>
     <x:row r="67">
-      <x:c r="A67" s="84" t="str">
+      <x:c r="A67" s="109" t="str">
         <x:v>EMP02</x:v>
       </x:c>
-      <x:c r="B67" s="84" t="str">
+      <x:c r="B67" s="109" t="str">
         <x:v>data</x:v>
       </x:c>
-      <x:c r="C67" s="84" t="str">
+      <x:c r="C67" s="109" t="str">
         <x:v>Empatica EmbracePlus</x:v>
       </x:c>
-      <x:c r="D67" s="84" t="str">
+      <x:c r="D67" s="109" t="str">
         <x:v>Continuous raw BVP, EDA, temperature, accelerometer, and tags are downloadable in Avro</x:v>
       </x:c>
-      <x:c r="E67" s="84" t="str">
+      <x:c r="E67" s="109" t="str">
         <x:v>official data documentation</x:v>
       </x:c>
-      <x:c r="F67" s="84" t="str">
+      <x:c r="F67" s="109" t="str">
         <x:v>https://www.empatica.com/rawdata/</x:v>
       </x:c>
-      <x:c r="G67" s="84" t="str">
+      <x:c r="G67" s="109" t="str">
         <x:v>current</x:v>
       </x:c>
-      <x:c r="H67" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I67" s="84" t="str">
+      <x:c r="H67" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I67" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J67" s="84" t="str">
+      <x:c r="J67" s="109" t="str">
         <x:v>No BP or ECG</x:v>
       </x:c>
     </x:row>
     <x:row r="68">
-      <x:c r="A68" s="84" t="str">
+      <x:c r="A68" s="109" t="str">
         <x:v>COR01</x:v>
       </x:c>
-      <x:c r="B68" s="84" t="str">
+      <x:c r="B68" s="109" t="str">
         <x:v>product</x:v>
       </x:c>
-      <x:c r="C68" s="84" t="str">
+      <x:c r="C68" s="109" t="str">
         <x:v>Corsano CardioWatch 287-2</x:v>
       </x:c>
-      <x:c r="D68" s="84" t="str">
+      <x:c r="D68" s="109" t="str">
         <x:v>Vendor claims continuous HR, RR, temperature, SpO2, cuffless BP, GSR, and raw multiwavelength PPG</x:v>
       </x:c>
-      <x:c r="E68" s="84" t="str">
+      <x:c r="E68" s="109" t="str">
         <x:v>official product page</x:v>
       </x:c>
-      <x:c r="F68" s="84" t="str">
+      <x:c r="F68" s="109" t="str">
         <x:v>https://corsano.com/products/bracelet-2/</x:v>
       </x:c>
-      <x:c r="G68" s="84" t="str">
+      <x:c r="G68" s="109" t="str">
         <x:v>current</x:v>
       </x:c>
-      <x:c r="H68" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I68" s="84" t="str">
+      <x:c r="H68" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I68" s="109" t="str">
         <x:v>medium</x:v>
       </x:c>
-      <x:c r="J68" s="84" t="str">
+      <x:c r="J68" s="109" t="str">
         <x:v>Endpoint configuration and regulatory scope require confirmation</x:v>
       </x:c>
     </x:row>
     <x:row r="69">
-      <x:c r="A69" s="84" t="str">
+      <x:c r="A69" s="109" t="str">
         <x:v>COR02</x:v>
       </x:c>
-      <x:c r="B69" s="84" t="str">
+      <x:c r="B69" s="109" t="str">
         <x:v>data</x:v>
       </x:c>
-      <x:c r="C69" s="84" t="str">
+      <x:c r="C69" s="109" t="str">
         <x:v>Corsano</x:v>
       </x:c>
-      <x:c r="D69" s="84" t="str">
+      <x:c r="D69" s="109" t="str">
         <x:v>Raw PPG is available in CSV export</x:v>
       </x:c>
-      <x:c r="E69" s="84" t="str">
+      <x:c r="E69" s="109" t="str">
         <x:v>official knowledge base</x:v>
       </x:c>
-      <x:c r="F69" s="84" t="str">
+      <x:c r="F69" s="109" t="str">
         <x:v>https://corsano.com/knowledge-base/content-of-exported-data-file/</x:v>
       </x:c>
-      <x:c r="G69" s="84" t="str">
+      <x:c r="G69" s="109" t="str">
         <x:v>current</x:v>
       </x:c>
-      <x:c r="H69" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I69" s="84" t="str">
+      <x:c r="H69" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I69" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J69" s="84" t="str">
+      <x:c r="J69" s="109" t="str">
         <x:v>Confirm exact firmware and schema</x:v>
       </x:c>
     </x:row>
     <x:row r="70">
-      <x:c r="A70" s="84" t="str">
+      <x:c r="A70" s="109" t="str">
         <x:v>COR03</x:v>
       </x:c>
-      <x:c r="B70" s="84" t="str">
+      <x:c r="B70" s="109" t="str">
         <x:v>data</x:v>
       </x:c>
-      <x:c r="C70" s="84" t="str">
+      <x:c r="C70" s="109" t="str">
         <x:v>Corsano API</x:v>
       </x:c>
-      <x:c r="D70" s="84" t="str">
+      <x:c r="D70" s="109" t="str">
         <x:v>REST and integration API routes include latest values and raw signals</x:v>
       </x:c>
-      <x:c r="E70" s="84" t="str">
+      <x:c r="E70" s="109" t="str">
         <x:v>official developer FAQ</x:v>
       </x:c>
-      <x:c r="F70" s="84" t="str">
+      <x:c r="F70" s="109" t="str">
         <x:v>https://developer.corsano.com/rest/faq/</x:v>
       </x:c>
-      <x:c r="G70" s="84" t="str">
+      <x:c r="G70" s="109" t="str">
         <x:v>current</x:v>
       </x:c>
-      <x:c r="H70" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I70" s="84" t="str">
+      <x:c r="H70" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I70" s="109" t="str">
         <x:v>medium</x:v>
       </x:c>
-      <x:c r="J70" s="84" t="str">
+      <x:c r="J70" s="109" t="str">
         <x:v>Obtain sample payloads and measured latency</x:v>
       </x:c>
     </x:row>
     <x:row r="71">
-      <x:c r="A71" s="84" t="str">
+      <x:c r="A71" s="109" t="str">
         <x:v>COR04</x:v>
       </x:c>
-      <x:c r="B71" s="84" t="str">
+      <x:c r="B71" s="109" t="str">
         <x:v>regulatory</x:v>
       </x:c>
-      <x:c r="C71" s="84" t="str">
+      <x:c r="C71" s="109" t="str">
         <x:v>Corsano CardioWatch 287-2</x:v>
       </x:c>
-      <x:c r="D71" s="84" t="str">
+      <x:c r="D71" s="109" t="str">
         <x:v>Current IFU defines warnings and intended-use boundaries</x:v>
       </x:c>
-      <x:c r="E71" s="84" t="str">
+      <x:c r="E71" s="109" t="str">
         <x:v>official instructions for use</x:v>
       </x:c>
-      <x:c r="F71" s="84" t="str">
+      <x:c r="F71" s="109" t="str">
         <x:v>https://corsano.com/wp-content/uploads/2026/03/EN-IFU-Corsano-CardioWatch-287-2-HCP_v6.pdf</x:v>
       </x:c>
-      <x:c r="G71" s="84" t="str">
+      <x:c r="G71" s="109" t="str">
         <x:v>2026-03</x:v>
       </x:c>
-      <x:c r="H71" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I71" s="84" t="str">
+      <x:c r="H71" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I71" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J71" s="84" t="str">
+      <x:c r="J71" s="109" t="str">
         <x:v>Use labeling and FDA databases rather than marketing alone</x:v>
       </x:c>
     </x:row>
     <x:row r="72">
-      <x:c r="A72" s="84" t="str">
+      <x:c r="A72" s="109" t="str">
         <x:v>HUA01</x:v>
       </x:c>
-      <x:c r="B72" s="84" t="str">
+      <x:c r="B72" s="109" t="str">
         <x:v>product</x:v>
       </x:c>
-      <x:c r="C72" s="84" t="str">
+      <x:c r="C72" s="109" t="str">
         <x:v>Huawei Watch D2</x:v>
       </x:c>
-      <x:c r="D72" s="84" t="str">
+      <x:c r="D72" s="109" t="str">
         <x:v>Inflatable wrist cuff, oscillometric BP and ABPM, ECG, and PPG features</x:v>
       </x:c>
-      <x:c r="E72" s="84" t="str">
+      <x:c r="E72" s="109" t="str">
         <x:v>official product page</x:v>
       </x:c>
-      <x:c r="F72" s="84" t="str">
+      <x:c r="F72" s="109" t="str">
         <x:v>https://consumer.huawei.com/uk/wearables/watch-d2/</x:v>
       </x:c>
-      <x:c r="G72" s="84" t="str">
+      <x:c r="G72" s="109" t="str">
         <x:v>current</x:v>
       </x:c>
-      <x:c r="H72" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I72" s="84" t="str">
+      <x:c r="H72" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I72" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J72" s="84" t="str">
+      <x:c r="J72" s="109" t="str">
         <x:v>Region-specific product information</x:v>
       </x:c>
     </x:row>
     <x:row r="73">
-      <x:c r="A73" s="84" t="str">
+      <x:c r="A73" s="109" t="str">
         <x:v>HUA02</x:v>
       </x:c>
-      <x:c r="B73" s="84" t="str">
+      <x:c r="B73" s="109" t="str">
         <x:v>product</x:v>
       </x:c>
-      <x:c r="C73" s="84" t="str">
+      <x:c r="C73" s="109" t="str">
         <x:v>Huawei Watch D2</x:v>
       </x:c>
-      <x:c r="D73" s="84" t="str">
+      <x:c r="D73" s="109" t="str">
         <x:v>ABPM intervals are 15 to 60 minutes and venous-access cautions apply</x:v>
       </x:c>
-      <x:c r="E73" s="84" t="str">
+      <x:c r="E73" s="109" t="str">
         <x:v>official product detail</x:v>
       </x:c>
-      <x:c r="F73" s="84" t="str">
+      <x:c r="F73" s="109" t="str">
         <x:v>https://consumer.huawei.com/uk/wearables/watch-d2/?progId=304856</x:v>
       </x:c>
-      <x:c r="G73" s="84" t="str">
+      <x:c r="G73" s="109" t="str">
         <x:v>current</x:v>
       </x:c>
-      <x:c r="H73" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I73" s="84" t="str">
+      <x:c r="H73" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I73" s="109" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="J73" s="84" t="str">
+      <x:c r="J73" s="109" t="str">
         <x:v>Not a rapid continuous BP stream; use opposite the venipuncture arm</x:v>
       </x:c>
     </x:row>
     <x:row r="74">
-      <x:c r="A74" s="84" t="str">
+      <x:c r="A74" s="109" t="str">
         <x:v>HUA04</x:v>
       </x:c>
-      <x:c r="B74" s="84" t="str">
+      <x:c r="B74" s="109" t="str">
         <x:v>data</x:v>
       </x:c>
-      <x:c r="C74" s="84" t="str">
+      <x:c r="C74" s="109" t="str">
         <x:v>Huawei Health Kit</x:v>
       </x:c>
-      <x:c r="D74" s="84" t="str">
+      <x:c r="D74" s="109" t="str">
         <x:v>Health Kit is an authorized health-data integration platform</x:v>
       </x:c>
-      <x:c r="E74" s="84" t="str">
+      <x:c r="E74" s="109" t="str">
         <x:v>official developer page</x:v>
       </x:c>
-      <x:c r="F74" s="84" t="str">
+      <x:c r="F74" s="109" t="str">
         <x:v>https://developer.huawei.com/consumer/de/hms/huaweihealth/</x:v>
       </x:c>
-      <x:c r="G74" s="84" t="str">
+      <x:c r="G74" s="109" t="str">
         <x:v>current</x:v>
       </x:c>
-      <x:c r="H74" s="84" t="str">
-        <x:v>2026-07-23</x:v>
-      </x:c>
-      <x:c r="I74" s="84" t="str">
+      <x:c r="H74" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I74" s="109" t="str">
         <x:v>medium</x:v>
       </x:c>
-      <x:c r="J74" s="84" t="str">
+      <x:c r="J74" s="109" t="str">
         <x:v>Exact D2 fields, region, latency, and approval need confirmation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75" s="109" t="str">
+        <x:v>CLN13</x:v>
+      </x:c>
+      <x:c r="B75" s="109" t="str">
+        <x:v>clinical</x:v>
+      </x:c>
+      <x:c r="C75" s="109" t="str">
+        <x:v>AI prediction of adverse blood-donor reactions</x:v>
+      </x:c>
+      <x:c r="D75" s="109" t="str">
+        <x:v>A 2026 systematic review found 13 AI studies but no sufficient evidence for operational adoption; external validation, standardized outcomes, and real-world implementation were lacking</x:v>
+      </x:c>
+      <x:c r="E75" s="109" t="str">
+        <x:v>peer-reviewed systematic review</x:v>
+      </x:c>
+      <x:c r="F75" s="109" t="str">
+        <x:v>https://doi.org/10.1186/s12911-026-03584-0</x:v>
+      </x:c>
+      <x:c r="G75" s="109" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="H75" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I75" s="109" t="str">
+        <x:v>high</x:v>
+      </x:c>
+      <x:c r="J75" s="109" t="str">
+        <x:v>The review identified no mature multimodal operational approach and explicitly called for physiological and behavioral integration</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76">
+      <x:c r="A76" s="109" t="str">
+        <x:v>CLN14</x:v>
+      </x:c>
+      <x:c r="B76" s="109" t="str">
+        <x:v>clinical</x:v>
+      </x:c>
+      <x:c r="C76" s="109" t="str">
+        <x:v>Electrodermal activity before syncope</x:v>
+      </x:c>
+      <x:c r="D76" s="109" t="str">
+        <x:v>Among 53 patients with tilt-induced syncope, 62% showed an EDA increase 257 ± 357 seconds before syncope, while 25% had no detectable EDA</x:v>
+      </x:c>
+      <x:c r="E76" s="109" t="str">
+        <x:v>peer-reviewed retrospective physiology study</x:v>
+      </x:c>
+      <x:c r="F76" s="109" t="str">
+        <x:v>https://pubmed.ncbi.nlm.nih.gov/15316839/</x:v>
+      </x:c>
+      <x:c r="G76" s="109" t="str">
+        <x:v>2004</x:v>
+      </x:c>
+      <x:c r="H76" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I76" s="109" t="str">
+        <x:v>high</x:v>
+      </x:c>
+      <x:c r="J76" s="109" t="str">
+        <x:v>EDA often preceded measured BP or cerebral-flow change but was variable and is not a standalone detector</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77">
+      <x:c r="A77" s="109" t="str">
+        <x:v>CLN15</x:v>
+      </x:c>
+      <x:c r="B77" s="109" t="str">
+        <x:v>clinical</x:v>
+      </x:c>
+      <x:c r="C77" s="109" t="str">
+        <x:v>Raw-BP reflex-syncope detection</x:v>
+      </x:c>
+      <x:c r="D77" s="109" t="str">
+        <x:v>A convolutional network using raw BP in 1348 HUT patients reported AUROC 0.972 and mean detection 165.35 seconds before reflex syncope</x:v>
+      </x:c>
+      <x:c r="E77" s="109" t="str">
+        <x:v>peer-reviewed machine-learning study</x:v>
+      </x:c>
+      <x:c r="F77" s="109" t="str">
+        <x:v>https://pubmed.ncbi.nlm.nih.gov/40068530/</x:v>
+      </x:c>
+      <x:c r="G77" s="109" t="str">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="H77" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I77" s="109" t="str">
+        <x:v>high</x:v>
+      </x:c>
+      <x:c r="J77" s="109" t="str">
+        <x:v>Only 57 reflex-syncope cases and internal ten-fold cross-validation; reinforces the need for a continuous BP development reference</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78">
+      <x:c r="A78" s="109" t="str">
+        <x:v>CLN16</x:v>
+      </x:c>
+      <x:c r="B78" s="109" t="str">
+        <x:v>clinical</x:v>
+      </x:c>
+      <x:c r="C78" s="109" t="str">
+        <x:v>Multisignal early syncope prediction</x:v>
+      </x:c>
+      <x:c r="D78" s="109" t="str">
+        <x:v>A temporal convolutional autoencoder using HR, SBP, DBP, and high-frequency normalized R-R features reported recall 0.9838, specificity 0.9009, and mean warning time 523.69 seconds</x:v>
+      </x:c>
+      <x:c r="E78" s="109" t="str">
+        <x:v>peer-reviewed machine-learning study</x:v>
+      </x:c>
+      <x:c r="F78" s="109" t="str">
+        <x:v>https://pubmed.ncbi.nlm.nih.gov/42154182/</x:v>
+      </x:c>
+      <x:c r="G78" s="109" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="H78" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I78" s="109" t="str">
+        <x:v>high</x:v>
+      </x:c>
+      <x:c r="J78" s="109" t="str">
+        <x:v>Tilt-table dataset and repeated internal validation; not venipuncture or external validation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79">
+      <x:c r="A79" s="109" t="str">
+        <x:v>CLN17</x:v>
+      </x:c>
+      <x:c r="B79" s="109" t="str">
+        <x:v>clinical</x:v>
+      </x:c>
+      <x:c r="C79" s="109" t="str">
+        <x:v>Large HUT hemodynamic sequence</x:v>
+      </x:c>
+      <x:c r="D79" s="109" t="str">
+        <x:v>In 4873 HUT patients, the reported sequence before syncope or near-syncope was an HR rise followed by BP and HR decreases, with age and sex affecting test response</x:v>
+      </x:c>
+      <x:c r="E79" s="109" t="str">
+        <x:v>peer-reviewed cohort study</x:v>
+      </x:c>
+      <x:c r="F79" s="109" t="str">
+        <x:v>https://pubmed.ncbi.nlm.nih.gov/35097001/</x:v>
+      </x:c>
+      <x:c r="G79" s="109" t="str">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c r="H79" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I79" s="109" t="str">
+        <x:v>high</x:v>
+      </x:c>
+      <x:c r="J79" s="109" t="str">
+        <x:v>Drug-potentiated tilt testing is not equivalent to venipuncture</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80">
+      <x:c r="A80" s="109" t="str">
+        <x:v>CLN18</x:v>
+      </x:c>
+      <x:c r="B80" s="109" t="str">
+        <x:v>clinical</x:v>
+      </x:c>
+      <x:c r="C80" s="109" t="str">
+        <x:v>Timing of VVS prodromes</x:v>
+      </x:c>
+      <x:c r="D80" s="109" t="str">
+        <x:v>In 149 HUT patients, early symptoms occurred more than three minutes before syncope, nausea/weakness/sweating/dizziness occurred one to three minutes before, and blurred vision appeared in the final minute</x:v>
+      </x:c>
+      <x:c r="E80" s="109" t="str">
+        <x:v>peer-reviewed prospective physiology study</x:v>
+      </x:c>
+      <x:c r="F80" s="109" t="str">
+        <x:v>https://academic.oup.com/europace/article/11/9/1221/464641</x:v>
+      </x:c>
+      <x:c r="G80" s="109" t="str">
+        <x:v>2009</x:v>
+      </x:c>
+      <x:c r="H80" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I80" s="109" t="str">
+        <x:v>high</x:v>
+      </x:c>
+      <x:c r="J80" s="109" t="str">
+        <x:v>Useful for time-resolved symptom labels; nitroglycerin-potentiated HUT limits generalization</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81">
+      <x:c r="A81" s="109" t="str">
+        <x:v>CLN19</x:v>
+      </x:c>
+      <x:c r="B81" s="109" t="str">
+        <x:v>clinical</x:v>
+      </x:c>
+      <x:c r="C81" s="109" t="str">
+        <x:v>Standard donor VVR definitions</x:v>
+      </x:c>
+      <x:c r="D81" s="109" t="str">
+        <x:v>ISBT/IHN defines VVR by discomfort and weakness with symptoms such as anxiety, dizziness, nausea, sweating, pallor, pulse change, hypotension, and possible loss of consciousness</x:v>
+      </x:c>
+      <x:c r="E81" s="109" t="str">
+        <x:v>international hemovigilance standard</x:v>
+      </x:c>
+      <x:c r="F81" s="109" t="str">
+        <x:v>https://www.isbtweb.org/asset/EA4C5A03-D325-4893-AED40A4CF6A1C7FE/</x:v>
+      </x:c>
+      <x:c r="G81" s="109" t="str">
+        <x:v>2014</x:v>
+      </x:c>
+      <x:c r="H81" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I81" s="109" t="str">
+        <x:v>high</x:v>
+      </x:c>
+      <x:c r="J81" s="109" t="str">
+        <x:v>Use standardized no-LOC, LOC-duration, injury, and location categories while retaining separate Vitestro pain and anxiety labels</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82">
+      <x:c r="A82" s="109" t="str">
+        <x:v>CLN20</x:v>
+      </x:c>
+      <x:c r="B82" s="109" t="str">
+        <x:v>clinical</x:v>
+      </x:c>
+      <x:c r="C82" s="109" t="str">
+        <x:v>Blood Donation Reactions Inventory</x:v>
+      </x:c>
+      <x:c r="D82" s="109" t="str">
+        <x:v>A four-item BDRI was psychometrically validated as a brief measure of subjective mild prefaint symptoms</x:v>
+      </x:c>
+      <x:c r="E82" s="109" t="str">
+        <x:v>peer-reviewed psychometric validation study</x:v>
+      </x:c>
+      <x:c r="F82" s="109" t="str">
+        <x:v>https://doi.org/10.1111/j.1537-2995.2008.01831.x</x:v>
+      </x:c>
+      <x:c r="G82" s="109" t="str">
+        <x:v>2008</x:v>
+      </x:c>
+      <x:c r="H82" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I82" s="109" t="str">
+        <x:v>high</x:v>
+      </x:c>
+      <x:c r="J82" s="109" t="str">
+        <x:v>Use as a symptom label, not as the physiological ground truth</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83">
+      <x:c r="A83" s="109" t="str">
+        <x:v>VIS01</x:v>
+      </x:c>
+      <x:c r="B83" s="109" t="str">
+        <x:v>clinical</x:v>
+      </x:c>
+      <x:c r="C83" s="109" t="str">
+        <x:v>Facial action units before blood donation</x:v>
+      </x:c>
+      <x:c r="D83" s="109" t="str">
+        <x:v>Seventeen facial action units from 227 blood donors classified low versus high VVR with F1 0.82; eye-region intensity was most predictive</x:v>
+      </x:c>
+      <x:c r="E83" s="109" t="str">
+        <x:v>peer-reviewed machine-learning study</x:v>
+      </x:c>
+      <x:c r="F83" s="109" t="str">
+        <x:v>https://pubmed.ncbi.nlm.nih.gov/36836177/</x:v>
+      </x:c>
+      <x:c r="G83" s="109" t="str">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c r="H83" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I83" s="109" t="str">
+        <x:v>high</x:v>
+      </x:c>
+      <x:c r="J83" s="109" t="str">
+        <x:v>Direct blood-donation evidence but no independent external validation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84">
+      <x:c r="A84" s="109" t="str">
+        <x:v>VIS02</x:v>
+      </x:c>
+      <x:c r="B84" s="109" t="str">
+        <x:v>clinical</x:v>
+      </x:c>
+      <x:c r="C84" s="109" t="str">
+        <x:v>Anticipatory facial temperature</x:v>
+      </x:c>
+      <x:c r="D84" s="109" t="str">
+        <x:v>Facial thermal profiles from 193 donors classified later VVR with sensitivity 0.87, specificity 0.84, F1 0.86, and PR-AUC 0.93</x:v>
+      </x:c>
+      <x:c r="E84" s="109" t="str">
+        <x:v>peer-reviewed machine-learning study</x:v>
+      </x:c>
+      <x:c r="F84" s="109" t="str">
+        <x:v>https://pubmed.ncbi.nlm.nih.gov/37316637/</x:v>
+      </x:c>
+      <x:c r="G84" s="109" t="str">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c r="H84" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I84" s="109" t="str">
+        <x:v>high</x:v>
+      </x:c>
+      <x:c r="J84" s="109" t="str">
+        <x:v>Test set contained 39 participants; ambient control and specialized imaging are required</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85">
+      <x:c r="A85" s="109" t="str">
+        <x:v>VIS03</x:v>
+      </x:c>
+      <x:c r="B85" s="109" t="str">
+        <x:v>clinical</x:v>
+      </x:c>
+      <x:c r="C85" s="109" t="str">
+        <x:v>Short facial video before needle reactions</x:v>
+      </x:c>
+      <x:c r="D85" s="109" t="str">
+        <x:v>A 2D-CNN with recurrent layers analyzed facial video for VVR classification and reported that short clips could support faster real-time inference</x:v>
+      </x:c>
+      <x:c r="E85" s="109" t="str">
+        <x:v>peer-reviewed machine-learning study</x:v>
+      </x:c>
+      <x:c r="F85" s="109" t="str">
+        <x:v>https://pmc.ncbi.nlm.nih.gov/articles/PMC11760633/</x:v>
+      </x:c>
+      <x:c r="G85" s="109" t="str">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="H85" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I85" s="109" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="J85" s="109" t="str">
+        <x:v>Direct donor-video study; performance and demographic robustness require independent replication</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86">
+      <x:c r="A86" s="109" t="str">
+        <x:v>VIV01</x:v>
+      </x:c>
+      <x:c r="B86" s="109" t="str">
+        <x:v>product</x:v>
+      </x:c>
+      <x:c r="C86" s="109" t="str">
+        <x:v>Vivalink VV330/VV350 Continuous ECG Platform</x:v>
+      </x:c>
+      <x:c r="D86" s="109" t="str">
+        <x:v>Reusable patch provides 128 Hz ECG, HR, HRV, R-R, respiration, skin temperature, posture, steps, and accelerometry with live streaming or recording</x:v>
+      </x:c>
+      <x:c r="E86" s="109" t="str">
+        <x:v>official product page</x:v>
+      </x:c>
+      <x:c r="F86" s="109" t="str">
+        <x:v>https://www.vivalink.com/wearable-ecg-monitor</x:v>
+      </x:c>
+      <x:c r="G86" s="109" t="str">
+        <x:v>current</x:v>
+      </x:c>
+      <x:c r="H86" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I86" s="109" t="str">
+        <x:v>high</x:v>
+      </x:c>
+      <x:c r="J86" s="109" t="str">
+        <x:v>FDA scope listed for ECG and HR; other channels and model-specific fields require contract confirmation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87">
+      <x:c r="A87" s="109" t="str">
+        <x:v>VIV02</x:v>
+      </x:c>
+      <x:c r="B87" s="109" t="str">
+        <x:v>data</x:v>
+      </x:c>
+      <x:c r="C87" s="109" t="str">
+        <x:v>Vivalink SDK</x:v>
+      </x:c>
+      <x:c r="D87" s="109" t="str">
+        <x:v>Mobile SDK, cloud web services, sample source code, APIs, and file downloads support direct application integration</x:v>
+      </x:c>
+      <x:c r="E87" s="109" t="str">
+        <x:v>official developer page</x:v>
+      </x:c>
+      <x:c r="F87" s="109" t="str">
+        <x:v>https://www.vivalink.com/vivalink-sdk</x:v>
+      </x:c>
+      <x:c r="G87" s="109" t="str">
+        <x:v>current</x:v>
+      </x:c>
+      <x:c r="H87" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I87" s="109" t="str">
+        <x:v>high</x:v>
+      </x:c>
+      <x:c r="J87" s="109" t="str">
+        <x:v>Obtain a versioned sample payload and verify local versus cloud latency</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88">
+      <x:c r="A88" s="109" t="str">
+        <x:v>VIV03</x:v>
+      </x:c>
+      <x:c r="B88" s="109" t="str">
+        <x:v>regulatory</x:v>
+      </x:c>
+      <x:c r="C88" s="109" t="str">
+        <x:v>Vivalink VV330</x:v>
+      </x:c>
+      <x:c r="D88" s="109" t="str">
+        <x:v>GUDID lists VV330 as commercially distributed and describes wireless ECG, accelerometer, R-R, and HR transmission</x:v>
+      </x:c>
+      <x:c r="E88" s="109" t="str">
+        <x:v>FDA GUDID record</x:v>
+      </x:c>
+      <x:c r="F88" s="109" t="str">
+        <x:v>https://accessgudid.nlm.nih.gov/devices/00865064000157</x:v>
+      </x:c>
+      <x:c r="G88" s="109" t="str">
+        <x:v>current</x:v>
+      </x:c>
+      <x:c r="H88" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I88" s="109" t="str">
+        <x:v>high</x:v>
+      </x:c>
+      <x:c r="J88" s="109" t="str">
+        <x:v>General-care recording platform; not a critical-care replacement</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89">
+      <x:c r="A89" s="109" t="str">
+        <x:v>VAL13</x:v>
+      </x:c>
+      <x:c r="B89" s="109" t="str">
+        <x:v>validation</x:v>
+      </x:c>
+      <x:c r="C89" s="109" t="str">
+        <x:v>Vivalink VV330</x:v>
+      </x:c>
+      <x:c r="D89" s="109" t="str">
+        <x:v>A published 2026 dataset used 128 Hz ECG, 50 Hz accelerometry, and 1 Hz HR from the Vivalink patch</x:v>
+      </x:c>
+      <x:c r="E89" s="109" t="str">
+        <x:v>peer-reviewed device-use study</x:v>
+      </x:c>
+      <x:c r="F89" s="109" t="str">
+        <x:v>https://pmc.ncbi.nlm.nih.gov/articles/PMC13082138/</x:v>
+      </x:c>
+      <x:c r="G89" s="109" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="H89" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I89" s="109" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="J89" s="109" t="str">
+        <x:v>Supports accessible raw ECG/motion data, not presyncope accuracy</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90">
+      <x:c r="A90" s="109" t="str">
+        <x:v>SIB01</x:v>
+      </x:c>
+      <x:c r="B90" s="109" t="str">
+        <x:v>product</x:v>
+      </x:c>
+      <x:c r="C90" s="109" t="str">
+        <x:v>Sibel ANNE One</x:v>
+      </x:c>
+      <x:c r="D90" s="109" t="str">
+        <x:v>FDA-cleared dual-sensor platform streams real-time data and supports continuous adult monitoring</x:v>
+      </x:c>
+      <x:c r="E90" s="109" t="str">
+        <x:v>official product page</x:v>
+      </x:c>
+      <x:c r="F90" s="109" t="str">
+        <x:v>https://sibelhealth.com/clinical-care/</x:v>
+      </x:c>
+      <x:c r="G90" s="109" t="str">
+        <x:v>current</x:v>
+      </x:c>
+      <x:c r="H90" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I90" s="109" t="str">
+        <x:v>high</x:v>
+      </x:c>
+      <x:c r="J90" s="109" t="str">
+        <x:v>Exact research export and SDK entitlements require a vendor contract</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91" s="109" t="str">
+        <x:v>SIB02</x:v>
+      </x:c>
+      <x:c r="B91" s="109" t="str">
+        <x:v>regulatory</x:v>
+      </x:c>
+      <x:c r="C91" s="109" t="str">
+        <x:v>Sibel ANNE One</x:v>
+      </x:c>
+      <x:c r="D91" s="109" t="str">
+        <x:v>FDA 510(k) K223711 lists ANNE One as a physiological-signal transmitter and receiver</x:v>
+      </x:c>
+      <x:c r="E91" s="109" t="str">
+        <x:v>FDA 510(k) record</x:v>
+      </x:c>
+      <x:c r="F91" s="109" t="str">
+        <x:v>https://www.accessdata.fda.gov/scripts/cdrh/cfdocs/cfpmn/pmn.cfm?ID=K223711</x:v>
+      </x:c>
+      <x:c r="G91" s="109" t="str">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c r="H91" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I91" s="109" t="str">
+        <x:v>high</x:v>
+      </x:c>
+      <x:c r="J91" s="109" t="str">
+        <x:v>Verify the exact intended-use configuration for the adult Vitestro study</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92">
+      <x:c r="A92" s="109" t="str">
+        <x:v>SIB03</x:v>
+      </x:c>
+      <x:c r="B92" s="109" t="str">
+        <x:v>data</x:v>
+      </x:c>
+      <x:c r="C92" s="109" t="str">
+        <x:v>Sibel ANNE One</x:v>
+      </x:c>
+      <x:c r="D92" s="109" t="str">
+        <x:v>A peer-reviewed methods report documents synchronized 512 Hz ECG, 128 Hz finger PPG, 1 Hz skin temperature, and high-rate accelerometry</x:v>
+      </x:c>
+      <x:c r="E92" s="109" t="str">
+        <x:v>peer-reviewed device methods study</x:v>
+      </x:c>
+      <x:c r="F92" s="109" t="str">
+        <x:v>https://www.nature.com/articles/s41746-024-01287-2</x:v>
+      </x:c>
+      <x:c r="G92" s="109" t="str">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="H92" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I92" s="109" t="str">
+        <x:v>high</x:v>
+      </x:c>
+      <x:c r="J92" s="109" t="str">
+        <x:v>Research access was available in the study; public commercial API terms are not established</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93">
+      <x:c r="A93" s="109" t="str">
+        <x:v>VAL14</x:v>
+      </x:c>
+      <x:c r="B93" s="109" t="str">
+        <x:v>validation</x:v>
+      </x:c>
+      <x:c r="C93" s="109" t="str">
+        <x:v>Sibel ANNE One</x:v>
+      </x:c>
+      <x:c r="D93" s="109" t="str">
+        <x:v>ANNE One has been used as an FDA-cleared clinical-grade platform with raw synchronized chest ECG and finger PPG</x:v>
+      </x:c>
+      <x:c r="E93" s="109" t="str">
+        <x:v>peer-reviewed device-use study</x:v>
+      </x:c>
+      <x:c r="F93" s="109" t="str">
+        <x:v>https://www.nature.com/articles/s41746-024-01287-2</x:v>
+      </x:c>
+      <x:c r="G93" s="109" t="str">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="H93" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I93" s="109" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="J93" s="109" t="str">
+        <x:v>Study target was cardiorespiratory illness rather than presyncope</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94" s="109" t="str">
+        <x:v>BST01</x:v>
+      </x:c>
+      <x:c r="B94" s="109" t="str">
+        <x:v>regulatory</x:v>
+      </x:c>
+      <x:c r="C94" s="109" t="str">
+        <x:v>Medidata BioStamp nPoint</x:v>
+      </x:c>
+      <x:c r="D94" s="109" t="str">
+        <x:v>FDA 510(k) K173510 covers a wireless research and clinical remote-monitoring system with raw sensor processing and HR, HRV, posture, sleep, and respiratory outputs</x:v>
+      </x:c>
+      <x:c r="E94" s="109" t="str">
+        <x:v>FDA 510(k) record</x:v>
+      </x:c>
+      <x:c r="F94" s="109" t="str">
+        <x:v>https://www.accessdata.fda.gov/scripts/cdrh/cfdocs/cfpmn/pmn.cfm?ID=K173510</x:v>
+      </x:c>
+      <x:c r="G94" s="109" t="str">
+        <x:v>2018</x:v>
+      </x:c>
+      <x:c r="H94" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I94" s="109" t="str">
+        <x:v>high</x:v>
+      </x:c>
+      <x:c r="J94" s="109" t="str">
+        <x:v>Not intended for critical-care use</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95" s="109" t="str">
+        <x:v>BST02</x:v>
+      </x:c>
+      <x:c r="B95" s="109" t="str">
+        <x:v>data</x:v>
+      </x:c>
+      <x:c r="C95" s="109" t="str">
+        <x:v>Medidata Sensors</x:v>
+      </x:c>
+      <x:c r="D95" s="109" t="str">
+        <x:v>Sensor Cloud supports continuous and episodic trial-grade sensor integrations and endpoint-oriented data management</x:v>
+      </x:c>
+      <x:c r="E95" s="109" t="str">
+        <x:v>official platform page</x:v>
+      </x:c>
+      <x:c r="F95" s="109" t="str">
+        <x:v>https://www.medidata.com/en/patient-experience/wearable-sensors/</x:v>
+      </x:c>
+      <x:c r="G95" s="109" t="str">
+        <x:v>current</x:v>
+      </x:c>
+      <x:c r="H95" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I95" s="109" t="str">
+        <x:v>high</x:v>
+      </x:c>
+      <x:c r="J95" s="109" t="str">
+        <x:v>Public material does not establish a low-latency alert API</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96">
+      <x:c r="A96" s="109" t="str">
+        <x:v>VAL15</x:v>
+      </x:c>
+      <x:c r="B96" s="109" t="str">
+        <x:v>validation</x:v>
+      </x:c>
+      <x:c r="C96" s="109" t="str">
+        <x:v>BioStamp nPoint</x:v>
+      </x:c>
+      <x:c r="D96" s="109" t="str">
+        <x:v>A pivotal study describes continuous raw accelerometer, gyroscope, and biopotential data collection through a conformal wearable research system</x:v>
+      </x:c>
+      <x:c r="E96" s="109" t="str">
+        <x:v>peer-reviewed pivotal validation study</x:v>
+      </x:c>
+      <x:c r="F96" s="109" t="str">
+        <x:v>https://pmc.ncbi.nlm.nih.gov/articles/PMC7015390/</x:v>
+      </x:c>
+      <x:c r="G96" s="109" t="str">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c r="H96" s="109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="I96" s="109" t="str">
+        <x:v>high</x:v>
+      </x:c>
+      <x:c r="J96" s="109" t="str">
+        <x:v>Cloud transfer and daily charging are important operational constraints</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra99d70a493754b82"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re64cece4bdb94774"/>
   </x:tableParts>
 </x:worksheet>
 </file>